--- a/CG_Excel.xlsx
+++ b/CG_Excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StudentGeorgeTolkach\Desktop\CG_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9395AC25-C9AE-4771-A643-3EB09F85C284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E28E4ED-02B8-46D3-9CB1-3F8C56039463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{6C2DEF91-4A20-40A3-B57D-EFFA9F8BDB42}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6C2DEF91-4A20-40A3-B57D-EFFA9F8BDB42}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2197,8 +2197,8 @@
       <xdr:row>8</xdr:row>
       <xdr:rowOff>21988</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId54">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="3" name="Ink 2">
@@ -2217,7 +2217,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="3" name="Ink 2">
@@ -2262,8 +2262,8 @@
       <xdr:row>7</xdr:row>
       <xdr:rowOff>14402</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId56">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="4" name="Ink 3">
@@ -2282,7 +2282,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="4" name="Ink 3">
@@ -2327,8 +2327,8 @@
       <xdr:row>6</xdr:row>
       <xdr:rowOff>9696</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId58">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="5" name="Ink 4">
@@ -2347,7 +2347,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="5" name="Ink 4">
@@ -2392,8 +2392,8 @@
       <xdr:row>5</xdr:row>
       <xdr:rowOff>310</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId60">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="6" name="Ink 5">
@@ -2412,7 +2412,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="6" name="Ink 5">
@@ -2457,8 +2457,8 @@
       <xdr:row>8</xdr:row>
       <xdr:rowOff>37468</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId62">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="11" name="Ink 10">
@@ -2477,7 +2477,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="11" name="Ink 10">
@@ -2522,8 +2522,8 @@
       <xdr:row>8</xdr:row>
       <xdr:rowOff>42148</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId64">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="12" name="Ink 11">
@@ -2542,7 +2542,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="12" name="Ink 11">
@@ -2587,8 +2587,8 @@
       <xdr:row>8</xdr:row>
       <xdr:rowOff>38188</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId66">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="13" name="Ink 12">
@@ -2607,7 +2607,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="13" name="Ink 12">
@@ -2652,8 +2652,8 @@
       <xdr:row>9</xdr:row>
       <xdr:rowOff>5094</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId67">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="14" name="Ink 13">
@@ -2672,7 +2672,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="14" name="Ink 13">
@@ -2717,8 +2717,8 @@
       <xdr:row>9</xdr:row>
       <xdr:rowOff>184014</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId69">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="15" name="Ink 14">
@@ -2737,7 +2737,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="15" name="Ink 14">
@@ -2782,8 +2782,8 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>14147</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId71">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="16" name="Ink 15">
@@ -2802,7 +2802,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="16" name="Ink 15">
@@ -2847,8 +2847,8 @@
       <xdr:row>7</xdr:row>
       <xdr:rowOff>113042</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId73">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="26" name="Ink 25">
@@ -2867,7 +2867,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="26" name="Ink 25">
@@ -2912,8 +2912,8 @@
       <xdr:row>6</xdr:row>
       <xdr:rowOff>71616</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId75">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="27" name="Ink 26">
@@ -2932,7 +2932,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="27" name="Ink 26">
@@ -2977,8 +2977,8 @@
       <xdr:row>5</xdr:row>
       <xdr:rowOff>80230</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId77">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="28" name="Ink 27">
@@ -2997,7 +2997,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="28" name="Ink 27">
@@ -3042,8 +3042,8 @@
       <xdr:row>9</xdr:row>
       <xdr:rowOff>10854</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId79">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="37" name="Ink 36">
@@ -3062,7 +3062,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="37" name="Ink 36">
@@ -3107,8 +3107,8 @@
       <xdr:row>3</xdr:row>
       <xdr:rowOff>122297</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId81">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="99" name="Ink 98">
@@ -3127,7 +3127,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="99" name="Ink 98">
@@ -3172,8 +3172,8 @@
       <xdr:row>4</xdr:row>
       <xdr:rowOff>162644</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId83">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="102" name="Ink 101">
@@ -3192,7 +3192,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="102" name="Ink 101">
@@ -3237,8 +3237,8 @@
       <xdr:row>5</xdr:row>
       <xdr:rowOff>132790</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId85">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="103" name="Ink 102">
@@ -3257,7 +3257,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="103" name="Ink 102">
@@ -3302,8 +3302,8 @@
       <xdr:row>6</xdr:row>
       <xdr:rowOff>95016</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId87">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="104" name="Ink 103">
@@ -3322,7 +3322,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="104" name="Ink 103">
@@ -3367,8 +3367,8 @@
       <xdr:row>7</xdr:row>
       <xdr:rowOff>104042</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId89">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="105" name="Ink 104">
@@ -3387,7 +3387,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="105" name="Ink 104">
@@ -3432,8 +3432,8 @@
       <xdr:row>8</xdr:row>
       <xdr:rowOff>126748</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId91">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="106" name="Ink 105">
@@ -3452,7 +3452,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="106" name="Ink 105">
@@ -3497,8 +3497,8 @@
       <xdr:row>9</xdr:row>
       <xdr:rowOff>130014</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId93">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="107" name="Ink 106">
@@ -3517,7 +3517,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="107" name="Ink 106">
@@ -3562,8 +3562,8 @@
       <xdr:row>10</xdr:row>
       <xdr:rowOff>126080</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId95">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="108" name="Ink 107">
@@ -3582,7 +3582,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="108" name="Ink 107">
@@ -3627,8 +3627,8 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>110987</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId97">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="109" name="Ink 108">
@@ -3647,7 +3647,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="109" name="Ink 108">
@@ -3692,8 +3692,8 @@
       <xdr:row>12</xdr:row>
       <xdr:rowOff>128293</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId99">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="110" name="Ink 109">
@@ -3712,7 +3712,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="110" name="Ink 109">
@@ -3757,8 +3757,8 @@
       <xdr:row>13</xdr:row>
       <xdr:rowOff>134079</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId101">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="113" name="Ink 112">
@@ -3777,7 +3777,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="113" name="Ink 112">
@@ -3822,8 +3822,8 @@
       <xdr:row>14</xdr:row>
       <xdr:rowOff>132305</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId103">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="114" name="Ink 113">
@@ -3842,7 +3842,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="114" name="Ink 113">
@@ -3887,8 +3887,8 @@
       <xdr:row>15</xdr:row>
       <xdr:rowOff>105331</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId105">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="116" name="Ink 115">
@@ -3907,7 +3907,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="116" name="Ink 115">
@@ -3952,8 +3952,8 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>139197</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId107">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="117" name="Ink 116">
@@ -3972,7 +3972,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="117" name="Ink 116">
@@ -4017,8 +4017,8 @@
       <xdr:row>17</xdr:row>
       <xdr:rowOff>123023</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId109">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="129" name="Ink 128">
@@ -4037,7 +4037,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="129" name="Ink 128">
@@ -4082,8 +4082,8 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>112609</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId111">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="130" name="Ink 129">
@@ -4102,7 +4102,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="130" name="Ink 129">
@@ -4136,786 +4136,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>53677</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>31102</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>320</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>147022</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId113">
-          <xdr14:nvContentPartPr>
-            <xdr14:cNvPr id="151" name="Ink 150">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF4DE318-026E-6636-15B7-62DAB9FF5EED}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr14:cNvPr>
-            <xdr14:cNvContentPartPr/>
-          </xdr14:nvContentPartPr>
-          <xdr14:nvPr macro=""/>
-          <xdr14:xfrm>
-            <a:off x="5814766" y="4063864"/>
-            <a:ext cx="126360" cy="115920"/>
-          </xdr14:xfrm>
-        </xdr:contentPart>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="151" name="Ink 150">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF4DE318-026E-6636-15B7-62DAB9FF5EED}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr/>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId114"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="5796766" y="4045864"/>
-              <a:ext cx="162000" cy="151560"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>68797</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>5854</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>72362</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>145894</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId115">
-          <xdr14:nvContentPartPr>
-            <xdr14:cNvPr id="152" name="Ink 151">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B4D0DC1-955C-688A-6450-1383D63AF619}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr14:cNvPr>
-            <xdr14:cNvContentPartPr/>
-          </xdr14:nvContentPartPr>
-          <xdr14:nvPr macro=""/>
-          <xdr14:xfrm>
-            <a:off x="5829886" y="3654544"/>
-            <a:ext cx="187920" cy="140040"/>
-          </xdr14:xfrm>
-        </xdr:contentPart>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="152" name="Ink 151">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B4D0DC1-955C-688A-6450-1383D63AF619}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr/>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId116"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="5812246" y="3636904"/>
-              <a:ext cx="223560" cy="175680"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>30637</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>1738</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>92882</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>128818</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId117">
-          <xdr14:nvContentPartPr>
-            <xdr14:cNvPr id="153" name="Ink 152">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FBED1FB6-7CB4-4C4C-635D-90C50B776D3D}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr14:cNvPr>
-            <xdr14:cNvContentPartPr/>
-          </xdr14:nvContentPartPr>
-          <xdr14:nvPr macro=""/>
-          <xdr14:xfrm>
-            <a:off x="5791726" y="3842464"/>
-            <a:ext cx="246600" cy="127080"/>
-          </xdr14:xfrm>
-        </xdr:contentPart>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="153" name="Ink 152">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FBED1FB6-7CB4-4C4C-635D-90C50B776D3D}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr/>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId118"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="5773726" y="3824824"/>
-              <a:ext cx="282240" cy="162720"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>138115</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>161422</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>48</xdr:col>
-      <xdr:colOff>148485</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>61546</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId119">
-          <xdr14:nvContentPartPr>
-            <xdr14:cNvPr id="154" name="Ink 153">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1448CB3F-4312-EB7C-3AC4-2A5C2128BC1F}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr14:cNvPr>
-            <xdr14:cNvContentPartPr/>
-          </xdr14:nvContentPartPr>
-          <xdr14:nvPr macro=""/>
-          <xdr14:xfrm>
-            <a:off x="8664526" y="4194184"/>
-            <a:ext cx="379080" cy="92160"/>
-          </xdr14:xfrm>
-        </xdr:contentPart>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="154" name="Ink 153">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1448CB3F-4312-EB7C-3AC4-2A5C2128BC1F}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr/>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId120"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="8646526" y="4176544"/>
-              <a:ext cx="414720" cy="127800"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>36</xdr:col>
-      <xdr:colOff>161143</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>24826</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>118233</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>169186</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId121">
-          <xdr14:nvContentPartPr>
-            <xdr14:cNvPr id="155" name="Ink 154">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87E88C0F-05E9-DE13-A08D-2DD1F71307C7}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr14:cNvPr>
-            <xdr14:cNvContentPartPr/>
-          </xdr14:nvContentPartPr>
-          <xdr14:nvPr macro=""/>
-          <xdr14:xfrm>
-            <a:off x="6844006" y="4249624"/>
-            <a:ext cx="325800" cy="144360"/>
-          </xdr14:xfrm>
-        </xdr:contentPart>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="155" name="Ink 154">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87E88C0F-05E9-DE13-A08D-2DD1F71307C7}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr/>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId122"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="6826006" y="4231624"/>
-              <a:ext cx="361440" cy="180000"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>76357</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>63706</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>111242</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>163786</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId123">
-          <xdr14:nvContentPartPr>
-            <xdr14:cNvPr id="156" name="Ink 155">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13A06F2F-977F-A9BC-F0ED-0FC5CF47EE42}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr14:cNvPr>
-            <xdr14:cNvContentPartPr/>
-          </xdr14:nvContentPartPr>
-          <xdr14:nvPr macro=""/>
-          <xdr14:xfrm>
-            <a:off x="5837446" y="4288504"/>
-            <a:ext cx="219240" cy="100080"/>
-          </xdr14:xfrm>
-        </xdr:contentPart>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="156" name="Ink 155">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13A06F2F-977F-A9BC-F0ED-0FC5CF47EE42}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr/>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId124"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="5819806" y="4270504"/>
-              <a:ext cx="254880" cy="135720"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>7435</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>178437</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>72920</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>38444</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId125">
-          <xdr14:nvContentPartPr>
-            <xdr14:cNvPr id="157" name="Ink 156">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44C0C900-EE38-2C21-730F-7EE65A78FC61}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr14:cNvPr>
-            <xdr14:cNvContentPartPr/>
-          </xdr14:nvContentPartPr>
-          <xdr14:nvPr macro=""/>
-          <xdr14:xfrm>
-            <a:off x="8533846" y="4979344"/>
-            <a:ext cx="249840" cy="244080"/>
-          </xdr14:xfrm>
-        </xdr:contentPart>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="157" name="Ink 156">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44C0C900-EE38-2C21-730F-7EE65A78FC61}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr/>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId126"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="8516206" y="4961704"/>
-              <a:ext cx="285480" cy="279720"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>61237</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>153346</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>128162</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>145989</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId127">
-          <xdr14:nvContentPartPr>
-            <xdr14:cNvPr id="158" name="Ink 157">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C548F4C3-34D5-6F74-05EA-9A25E588FC5A}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr14:cNvPr>
-            <xdr14:cNvContentPartPr/>
-          </xdr14:nvContentPartPr>
-          <xdr14:nvPr macro=""/>
-          <xdr14:xfrm>
-            <a:off x="5822326" y="4378144"/>
-            <a:ext cx="251280" cy="184680"/>
-          </xdr14:xfrm>
-        </xdr:contentPart>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="158" name="Ink 157">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C548F4C3-34D5-6F74-05EA-9A25E588FC5A}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr/>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId128"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="5804686" y="4360144"/>
-              <a:ext cx="286920" cy="220320"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>92093</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>82160</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>71538</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>161360</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId129">
-          <xdr14:nvContentPartPr>
-            <xdr14:cNvPr id="159" name="Ink 158">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51B9F352-DD2D-EAC5-BB54-6846D3F9EB57}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr14:cNvPr>
-            <xdr14:cNvContentPartPr/>
-          </xdr14:nvContentPartPr>
-          <xdr14:nvPr macro=""/>
-          <xdr14:xfrm>
-            <a:off x="6406246" y="5075104"/>
-            <a:ext cx="163800" cy="79200"/>
-          </xdr14:xfrm>
-        </xdr:contentPart>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="159" name="Ink 158">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51B9F352-DD2D-EAC5-BB54-6846D3F9EB57}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr/>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId130"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="6388246" y="5057464"/>
-              <a:ext cx="199440" cy="114840"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>61237</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>91629</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>56488</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>104073</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId131">
-          <xdr14:nvContentPartPr>
-            <xdr14:cNvPr id="160" name="Ink 159">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC7A85A2-B314-1946-6AAB-F6D8479119B5}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr14:cNvPr>
-            <xdr14:cNvContentPartPr/>
-          </xdr14:nvContentPartPr>
-          <xdr14:nvPr macro=""/>
-          <xdr14:xfrm>
-            <a:off x="5822326" y="4508464"/>
-            <a:ext cx="363960" cy="204480"/>
-          </xdr14:xfrm>
-        </xdr:contentPart>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="160" name="Ink 159">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC7A85A2-B314-1946-6AAB-F6D8479119B5}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr/>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId132"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="5804686" y="4490824"/>
-              <a:ext cx="399600" cy="240120"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>43</xdr:col>
-      <xdr:colOff>38139</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>58244</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>44</xdr:col>
-      <xdr:colOff>8224</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>176684</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId133">
-          <xdr14:nvContentPartPr>
-            <xdr14:cNvPr id="161" name="Ink 160">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F71994E-EA3D-37E0-0126-AFB806BAF19B}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr14:cNvPr>
-            <xdr14:cNvContentPartPr/>
-          </xdr14:nvContentPartPr>
-          <xdr14:nvPr macro=""/>
-          <xdr14:xfrm>
-            <a:off x="8011486" y="5243224"/>
-            <a:ext cx="154440" cy="118440"/>
-          </xdr14:xfrm>
-        </xdr:contentPart>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="161" name="Ink 160">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F71994E-EA3D-37E0-0126-AFB806BAF19B}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr/>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId134"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="7993846" y="5225584"/>
-              <a:ext cx="190080" cy="154080"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>91837</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>100412</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>175322</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>94855</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId135">
-          <xdr14:nvContentPartPr>
-            <xdr14:cNvPr id="167" name="Ink 166">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C76D213C-346B-93A5-9769-5A82E6D9C20C}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr14:cNvPr>
-            <xdr14:cNvContentPartPr/>
-          </xdr14:nvContentPartPr>
-          <xdr14:nvPr macro=""/>
-          <xdr14:xfrm>
-            <a:off x="5852926" y="5669464"/>
-            <a:ext cx="267840" cy="186480"/>
-          </xdr14:xfrm>
-        </xdr:contentPart>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="167" name="Ink 166">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C76D213C-346B-93A5-9769-5A82E6D9C20C}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr/>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId136"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="5835286" y="5651824"/>
-              <a:ext cx="303480" cy="222120"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>34</xdr:col>
       <xdr:colOff>7555</xdr:colOff>
       <xdr:row>34</xdr:row>
@@ -4927,9 +4147,9 @@
       <xdr:row>35</xdr:row>
       <xdr:rowOff>123751</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId137">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId113">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="185" name="Ink 184">
               <a:extLst>
@@ -4947,7 +4167,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="185" name="Ink 184">
@@ -4992,8 +4212,8 @@
       <xdr:row>38</xdr:row>
       <xdr:rowOff>43786</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId139">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="187" name="Ink 186">
@@ -5012,7 +4232,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="187" name="Ink 186">
@@ -5057,8 +4277,8 @@
       <xdr:row>38</xdr:row>
       <xdr:rowOff>154306</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId141">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="190" name="Ink 189">
@@ -5077,7 +4297,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="190" name="Ink 189">
@@ -5122,8 +4342,8 @@
       <xdr:row>12</xdr:row>
       <xdr:rowOff>107966</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId143">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="191" name="Ink 190">
@@ -5142,7 +4362,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="191" name="Ink 190">
@@ -5187,8 +4407,8 @@
       <xdr:row>9</xdr:row>
       <xdr:rowOff>134795</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId145">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="195" name="Ink 194">
@@ -5207,7 +4427,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="195" name="Ink 194">
@@ -5252,8 +4472,8 @@
       <xdr:row>12</xdr:row>
       <xdr:rowOff>19848</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId147">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="198" name="Ink 197">
@@ -5272,7 +4492,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="198" name="Ink 197">
@@ -5317,8 +4537,8 @@
       <xdr:row>9</xdr:row>
       <xdr:rowOff>139917</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId149">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="201" name="Ink 200">
@@ -5337,7 +4557,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="201" name="Ink 200">
@@ -5382,8 +4602,8 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>153831</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId151">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="204" name="Ink 203">
@@ -5402,7 +4622,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="204" name="Ink 203">
@@ -5447,8 +4667,8 @@
       <xdr:row>10</xdr:row>
       <xdr:rowOff>171174</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId153">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="205" name="Ink 204">
@@ -5467,7 +4687,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="205" name="Ink 204">
@@ -5512,8 +4732,8 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>84757</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId155">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="212" name="Ink 211">
@@ -5532,7 +4752,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="212" name="Ink 211">
@@ -5577,8 +4797,8 @@
       <xdr:row>14</xdr:row>
       <xdr:rowOff>179922</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId157">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="216" name="Ink 215">
@@ -5597,7 +4817,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="216" name="Ink 215">
@@ -5642,8 +4862,8 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>145597</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId159">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="217" name="Ink 216">
@@ -5662,7 +4882,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="217" name="Ink 216">
@@ -5707,8 +4927,8 @@
       <xdr:row>6</xdr:row>
       <xdr:rowOff>53983</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId161">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="229" name="Ink 228">
@@ -5727,7 +4947,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="229" name="Ink 228">
@@ -5772,8 +4992,8 @@
       <xdr:row>5</xdr:row>
       <xdr:rowOff>9406</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId163">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="269" name="Ink 268">
@@ -5792,7 +5012,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="269" name="Ink 268">
@@ -5837,8 +5057,8 @@
       <xdr:row>2</xdr:row>
       <xdr:rowOff>31194</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId165">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="270" name="Ink 269">
@@ -5857,7 +5077,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="270" name="Ink 269">
@@ -5902,8 +5122,8 @@
       <xdr:row>24</xdr:row>
       <xdr:rowOff>7492</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId167">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="271" name="Ink 270">
@@ -5922,7 +5142,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="271" name="Ink 270">
@@ -5967,8 +5187,8 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>135183</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId169">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="284" name="Ink 283">
@@ -5987,7 +5207,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="284" name="Ink 283">
@@ -6032,8 +5252,8 @@
       <xdr:row>2</xdr:row>
       <xdr:rowOff>126594</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId171">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="285" name="Ink 284">
@@ -6052,7 +5272,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="285" name="Ink 284">
@@ -6097,8 +5317,8 @@
       <xdr:row>2</xdr:row>
       <xdr:rowOff>154674</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId173">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="286" name="Ink 285">
@@ -6117,7 +5337,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="286" name="Ink 285">
@@ -6162,8 +5382,8 @@
       <xdr:row>1</xdr:row>
       <xdr:rowOff>28017</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId175">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="292" name="Ink 291">
@@ -6182,7 +5402,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="292" name="Ink 291">
@@ -6227,8 +5447,8 @@
       <xdr:row>1</xdr:row>
       <xdr:rowOff>67977</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId177">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="293" name="Ink 292">
@@ -6247,7 +5467,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="293" name="Ink 292">
@@ -6292,8 +5512,8 @@
       <xdr:row>25</xdr:row>
       <xdr:rowOff>48829</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId179">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="298" name="Ink 297">
@@ -6312,7 +5532,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="298" name="Ink 297">
@@ -6357,8 +5577,8 @@
       <xdr:row>24</xdr:row>
       <xdr:rowOff>142852</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId181">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="299" name="Ink 298">
@@ -6377,7 +5597,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="299" name="Ink 298">
@@ -6422,8 +5642,8 @@
       <xdr:row>22</xdr:row>
       <xdr:rowOff>126418</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId183">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="305" name="Ink 304">
@@ -6442,7 +5662,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="305" name="Ink 304">
@@ -6487,8 +5707,8 @@
       <xdr:row>22</xdr:row>
       <xdr:rowOff>103018</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId185">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="306" name="Ink 305">
@@ -6507,7 +5727,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="306" name="Ink 305">
@@ -6552,8 +5772,8 @@
       <xdr:row>7</xdr:row>
       <xdr:rowOff>188560</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId187">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="307" name="Ink 306">
@@ -6572,7 +5792,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="307" name="Ink 306">
@@ -6617,8 +5837,8 @@
       <xdr:row>4</xdr:row>
       <xdr:rowOff>37549</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId189">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="308" name="Ink 307">
@@ -6637,7 +5857,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="308" name="Ink 307">
@@ -6682,8 +5902,8 @@
       <xdr:row>8</xdr:row>
       <xdr:rowOff>31537</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId191">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="311" name="Ink 310">
@@ -6702,7 +5922,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="311" name="Ink 310">
@@ -6747,8 +5967,8 @@
       <xdr:row>4</xdr:row>
       <xdr:rowOff>20269</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId193">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="314" name="Ink 313">
@@ -6767,7 +5987,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="314" name="Ink 313">
@@ -6812,8 +6032,8 @@
       <xdr:row>8</xdr:row>
       <xdr:rowOff>25854</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId195">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="317" name="Ink 316">
@@ -6832,7 +6052,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="317" name="Ink 316">
@@ -6877,8 +6097,8 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>82906</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId197">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="330" name="Ink 329">
@@ -6897,7 +6117,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="330" name="Ink 329">
@@ -6942,8 +6162,8 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>80072</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId199">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="331" name="Ink 330">
@@ -6962,7 +6182,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="331" name="Ink 330">
@@ -7007,8 +6227,8 @@
       <xdr:row>15</xdr:row>
       <xdr:rowOff>136295</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId201">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="335" name="Ink 334">
@@ -7027,7 +6247,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="335" name="Ink 334">
@@ -7072,8 +6292,8 @@
       <xdr:row>19</xdr:row>
       <xdr:rowOff>183923</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId203">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="338" name="Ink 337">
@@ -7092,7 +6312,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="338" name="Ink 337">
@@ -7137,8 +6357,8 @@
       <xdr:row>19</xdr:row>
       <xdr:rowOff>160163</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId205">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="340" name="Ink 339">
@@ -7157,7 +6377,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="340" name="Ink 339">
@@ -7202,8 +6422,8 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>90620</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId207">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="344" name="Ink 343">
@@ -7222,7 +6442,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="344" name="Ink 343">
@@ -7267,8 +6487,8 @@
       <xdr:row>27</xdr:row>
       <xdr:rowOff>139501</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId209">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="345" name="Ink 344">
@@ -7287,7 +6507,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="345" name="Ink 344">
@@ -7332,8 +6552,8 @@
       <xdr:row>30</xdr:row>
       <xdr:rowOff>172072</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId211">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="346" name="Ink 345">
@@ -7352,7 +6572,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="346" name="Ink 345">
@@ -7397,8 +6617,8 @@
       <xdr:row>30</xdr:row>
       <xdr:rowOff>168112</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId213">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="349" name="Ink 348">
@@ -7417,7 +6637,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="349" name="Ink 348">
@@ -7462,8 +6682,8 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>40438</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId215">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="350" name="Ink 349">
@@ -7482,7 +6702,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="350" name="Ink 349">
@@ -7527,8 +6747,8 @@
       <xdr:row>26</xdr:row>
       <xdr:rowOff>166203</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId217">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="351" name="Ink 350">
@@ -7547,7 +6767,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="351" name="Ink 350">
@@ -7592,8 +6812,8 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>96238</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId219">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="352" name="Ink 351">
@@ -7612,7 +6832,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="352" name="Ink 351">
@@ -7657,8 +6877,8 @@
       <xdr:row>26</xdr:row>
       <xdr:rowOff>122283</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId221">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="356" name="Ink 355">
@@ -7677,7 +6897,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="356" name="Ink 355">
@@ -7722,8 +6942,8 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>115318</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId223">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="359" name="Ink 358">
@@ -7742,7 +6962,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="359" name="Ink 358">
@@ -7787,8 +7007,8 @@
       <xdr:row>29</xdr:row>
       <xdr:rowOff>130735</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId225">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="360" name="Ink 359">
@@ -7807,7 +7027,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="360" name="Ink 359">
@@ -7852,8 +7072,8 @@
       <xdr:row>31</xdr:row>
       <xdr:rowOff>172729</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId227">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="361" name="Ink 360">
@@ -7872,7 +7092,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="361" name="Ink 360">
@@ -7917,8 +7137,8 @@
       <xdr:row>29</xdr:row>
       <xdr:rowOff>176095</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId229">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="368" name="Ink 367">
@@ -7937,7 +7157,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="368" name="Ink 367">
@@ -7982,8 +7202,8 @@
       <xdr:row>31</xdr:row>
       <xdr:rowOff>107569</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId231">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="369" name="Ink 368">
@@ -8002,7 +7222,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="369" name="Ink 368">
@@ -8047,8 +7267,8 @@
       <xdr:row>26</xdr:row>
       <xdr:rowOff>140825</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId233">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="383" name="Ink 382">
@@ -8067,7 +7287,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="383" name="Ink 382">
@@ -8112,8 +7332,8 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>39900</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId235">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="384" name="Ink 383">
@@ -8132,7 +7352,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="384" name="Ink 383">
@@ -8177,8 +7397,8 @@
       <xdr:row>31</xdr:row>
       <xdr:rowOff>128271</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId237">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="389" name="Ink 388">
@@ -8197,7 +7417,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="389" name="Ink 388">
@@ -8242,8 +7462,8 @@
       <xdr:row>30</xdr:row>
       <xdr:rowOff>26454</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId239">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="390" name="Ink 389">
@@ -8262,7 +7482,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="390" name="Ink 389">
@@ -8307,8 +7527,8 @@
       <xdr:row>27</xdr:row>
       <xdr:rowOff>7203</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId241">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="404" name="Ink 403">
@@ -8327,7 +7547,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="404" name="Ink 403">
@@ -8372,8 +7592,8 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>82740</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId243">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="406" name="Ink 405">
@@ -8392,7 +7612,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="406" name="Ink 405">
@@ -8437,8 +7657,8 @@
       <xdr:row>30</xdr:row>
       <xdr:rowOff>36174</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId245">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="407" name="Ink 406">
@@ -8457,7 +7677,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="407" name="Ink 406">
@@ -8502,8 +7722,8 @@
       <xdr:row>31</xdr:row>
       <xdr:rowOff>108111</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId247">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="410" name="Ink 409">
@@ -8522,7 +7742,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="410" name="Ink 409">
@@ -8567,8 +7787,8 @@
       <xdr:row>31</xdr:row>
       <xdr:rowOff>163911</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId249">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="415" name="Ink 414">
@@ -8587,7 +7807,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="415" name="Ink 414">
@@ -8632,8 +7852,8 @@
       <xdr:row>30</xdr:row>
       <xdr:rowOff>31494</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId251">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="416" name="Ink 415">
@@ -8652,7 +7872,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="416" name="Ink 415">
@@ -8697,8 +7917,8 @@
       <xdr:row>34</xdr:row>
       <xdr:rowOff>172369</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId253">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="422" name="Ink 421">
@@ -8717,7 +7937,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="422" name="Ink 421">
@@ -8804,387 +8024,11 @@
       <inkml:brushProperty name="color" value="#33CCFF"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 62 24575,'7'-5'0,"1"-1"0,1 2 0,-1-1 0,1 1 0,0 0 0,0 1 0,0 0 0,0 0 0,11 0 0,-5-1 0,-5 1 0,59-10 0,-66 13 0,0-1 0,0 1 0,0 0 0,0 0 0,0 0 0,1 0 0,-1 1 0,0-1 0,0 1 0,0 0 0,0 0 0,0 1 0,0-1 0,0 1 0,-1-1 0,1 1 0,5 4 0,-7-5 0,0 0 0,-1 0 0,1 1 0,0-1 0,0 1 0,-1-1 0,1 1 0,-1-1 0,1 0 0,-1 1 0,0-1 0,1 1 0,-1 0 0,0-1 0,0 0 0,0 1 0,0-1 0,0 2 0,0-2 0,0 0 0,-1 1 0,0 1 0,0 2 0,-1-1 0,1 0 0,-1 0 0,0-1 0,-1 2 0,1-2 0,-5 7 0,-4 2 0,0-1 0,-25 19 0,34-27 0,0-2 0,0 0 0,1 1 0,-1-1 0,0 1 0,0 0 0,1 0 0,-1 0 0,1 0 0,0-1 0,-2 5 0,3-5 0,0-1 0,0 1 0,0-1 0,0 0 0,0 1 0,0-1 0,0 0 0,0 1 0,0-1 0,0 1 0,0-1 0,0 0 0,0 2 0,1-2 0,-1 0 0,0 1 0,0-1 0,0 0 0,1 1 0,-1-1 0,0 0 0,1 1 0,-1-1 0,0 0 0,0 0 0,1 1 0,-1-1 0,0 0 0,1 0 0,-1 0 0,1 0 0,-1 1 0,0-1 0,1 0 0,-1 0 0,0 0 0,1 0 0,56 4 0,-53-4 0,1-2 0,4 2 0,1-1 0,-1 1 0,1 1 0,-1 1 0,1-1 0,13 4 0,-21-4 0,1 0 0,-1 1 0,0 0 0,0-1 0,0 0 0,0 1 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,-1 0 0,1 1 0,-1-1 0,0 0 0,0 1 0,1 0 0,-1-1 0,-1 1 0,1-1 0,0 2 0,-1-2 0,1 0 0,-1 2 0,0-1 0,1-1 0,-1 1 0,0 0 0,-1 3 0,0-1 5,1-2 0,-1 0 0,0 1 0,0-1 0,0 0 0,0 1 0,-1-2 0,1 1 0,-1 1 0,0-1 0,0-1 0,0 2 0,0-2 0,0 0 0,0 0 0,-1 0 0,1 1 0,-1-1 0,1 0 0,-1 0 0,0-1 0,1 2 0,-7 0 0,-3 3-302,0-2 0,-1 0 0,0 1 0,-16 0 0,3 0-6529</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 55 24575,'7'-4'0,"1"-1"0,1 1 0,-1 0 0,1 0 0,0 0 0,0 2 0,0-1 0,0 0 0,11 1 0,-5-2 0,-5 1 0,59-8 0,-66 11 0,0-1 0,0 1 0,0 0 0,0 0 0,0 0 0,1 0 0,-1 1 0,0-1 0,0 1 0,0 0 0,0 0 0,0 0 0,0 0 0,0 1 0,-1-1 0,1 1 0,5 3 0,-7-4 0,0 0 0,-1 0 0,1 1 0,0-2 0,0 2 0,-1-1 0,1 1 0,-1-1 0,1 0 0,-1 0 0,0 0 0,1 1 0,-1 0 0,0-1 0,0 0 0,0 0 0,0 0 0,0 2 0,0-2 0,0 0 0,-1 1 0,0 0 0,0 3 0,-1-2 0,1 1 0,-1-1 0,0 0 0,-1 2 0,1-3 0,-5 7 0,-4 2 0,0-1 0,-25 16 0,34-23 0,0-2 0,0 0 0,1 1 0,-1-2 0,0 2 0,0 0 0,1 0 0,-1 0 0,1-1 0,0 0 0,-2 5 0,3-5 0,0-1 0,0 0 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 1 0,0-1 0,0 1 0,0-1 0,0 0 0,0 2 0,1-2 0,-1 0 0,0 1 0,0-1 0,0 0 0,1 1 0,-1-1 0,0 0 0,1 1 0,-1-1 0,0 0 0,0 0 0,1 0 0,-1 0 0,0 0 0,1 0 0,-1 0 0,1 0 0,-1 1 0,0-1 0,1 0 0,-1 0 0,0 0 0,1 0 0,56 4 0,-53-4 0,1-2 0,4 2 0,1-1 0,-1 1 0,1 1 0,-1 1 0,1-1 0,13 3 0,-21-3 0,1 0 0,-1 1 0,0 0 0,0-2 0,0 1 0,0 1 0,0 0 0,0 0 0,0 0 0,0-1 0,0 1 0,-1 0 0,1 1 0,-1-2 0,0 1 0,0 1 0,1-1 0,-1 0 0,-1 1 0,1-1 0,0 1 0,-1-1 0,1 0 0,-1 1 0,0 0 0,1-1 0,-1 1 0,0-1 0,-1 4 0,0-2 5,1-1 0,-1-1 0,0 2 0,0-1 0,0-1 0,0 2 0,-1-2 0,1 0 0,-1 2 0,0-1 0,0-2 0,0 3 0,0-2 0,0-1 0,0 1 0,-1 0 0,1 1 0,-1-2 0,1 1 0,-1 0 0,0-1 0,1 2 0,-7-1 0,-3 4-302,0-3 0,-1 1 0,0 0 0,-16 1 0,3-1-6529</inkml:trace>
 </inkml:ink>
 </file>
 
 <file path=xl/ink/ink100.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:46:13.227"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.1" units="cm"/>
-      <inkml:brushProperty name="height" value="0.1" units="cm"/>
-      <inkml:brushProperty name="color" value="#008C3A"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">632 97 9830,'4'2'116,"0"0"-1,-1 1 1,1-1 0,-1 1-1,0-1 1,0 1-1,0 0 1,0 0 0,-1 1-1,1-1 1,-1 0-1,1 1 1,-1 0 0,2 4-1,3 3 118,276 456 7469,-204-329-6204,-37-63-930,-15-24 32,2-2 0,49 63-1,-6-45 542,-63-55-1095</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1248.15">1206 22 9830,'6'2'133,"-1"0"-1,0 0 0,0 0 1,0 1-1,-1 0 1,1 0-1,-1 0 1,1 0-1,-1 1 0,0-1 1,0 1-1,-1 0 1,6 8-1,-5-8 19,26 31 451,-2 0 0,-1 2 0,-2 1 0,23 47 0,-47-84-578,0 0-1,-1 0 1,1 0 0,-1 0-1,1 1 1,-1-1 0,1 0-1,-1 0 1,0 0 0,0 1-1,1-1 1,-1 0 0,0 0-1,0 0 1,0 1 0,0-1-1,-1 0 1,1 0 0,0 1 0,0-1-1,-1 0 1,1 0 0,-1 0-1,1 0 1,-1 1 0,1-1-1,-1 0 1,-1 1 0,0-1 19,0 1 1,0-1 0,0 1 0,-1-1-1,1 0 1,0 0 0,-1 0-1,1 0 1,-1-1 0,1 1-1,-1-1 1,-4 1 0,-10 0 179,0-2 0,0 1 0,-19-5 0,33 5-186,0 0-19,0 0 0,0-1 0,0 1-1,0-1 1,0 0 0,1 0 0,-1 0 0,0 0-1,0-1 1,1 1 0,-1-1 0,0 1-1,1-1 1,0 0 0,-1 0 0,1 0 0,0 0-1,0-1 1,0 1 0,0 0 0,1-1-1,-1 1 1,-1-4 0,3 3-26,-1 1-1,1-1 1,-1 1-1,1-1 1,0 1-1,0-1 1,1 1-1,-1-1 1,0 1-1,1-1 1,-1 1 0,1-1-1,0 1 1,0 0-1,0-1 1,0 1-1,0 0 1,1 0-1,-1 0 1,1-1-1,-1 2 1,1-1 0,0 0-1,-1 0 1,1 0-1,0 1 1,4-3-1,2-2-13,-1 0-1,1 0 0,-1-1 1,-1 0-1,1-1 1,-1 1-1,0-1 0,7-14 1,-11 17-9,0 1-1,-1-1 1,1 1 0,-1-1 0,0 1-1,-1-1 1,1 0 0,-1 1 0,0-1-1,0 0 1,0 1 0,0-1 0,-1 0-1,0 1 1,0-1 0,0 1 0,-1-1-1,1 1 1,-1 0 0,-4-7 0,3 6 17,0 0 0,0 0 0,-1 0 1,0 1-1,0-1 0,0 1 1,-1 0-1,1 0 0,-1 0 1,0 1-1,-6-4 0,-10-3 42</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3290.54">1281 971 9830,'5'8'611,"9"16"373,7 17-120,8 13 120,4 11-120,-5-1-591,-6-8 0,-7-13-273</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3789.02">1481 1121 9830,'4'0'273,"6"0"0,1-5 0,3 0 0,3-1 0,-1 6 0,-3 7 1,-8 6 112,-6 6-113,-1 3 0,7 3 337,7-3-337,7-6 0,3-5 1,2-5-1,-2-3-273</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6327.66">58 72 9830,'7'0'136,"-1"1"0,0-1 0,1 1 0,-1 0 0,0 0 0,1 1 0,-1 0 0,0 0 0,0 1 0,-1-1 0,1 1-1,0 0 1,-1 1 0,6 4 0,-9-6-79,1 1 0,0 0-1,-1 0 1,1 0-1,-1 0 1,0 0 0,0 1-1,0-1 1,0 1-1,-1-1 1,1 1 0,-1 0-1,0 0 1,0-1-1,-1 1 1,1 0 0,-1 0-1,1 0 1,-1 0-1,-1 0 1,1 0 0,0-1-1,-1 1 1,-1 6-1,-2-1 96,0 0-1,-1 0 1,1 0 0,-2-1-1,1 0 1,-1 0-1,-1 0 1,1-1-1,-1 0 1,0 0-1,-1-1 1,0 0 0,-15 10-1,10-7-6,1 0 0,0 1 0,1 1-1,-13 15 1,23-26-118,0 1-1,0 0 0,1 0 1,-1 0-1,1 0 0,-1 0 0,1 0 1,-1-1-1,1 1 0,-1 0 1,1 1-1,0-1 0,-1 0 1,1 0-1,0 0 0,0 0 0,0 0 1,0 0-1,0 0 0,0 0 1,0 0-1,0 0 0,1 0 1,-1 0-1,0 0 0,1 0 0,-1 0 1,0 0-1,1 0 0,1 2 1,0-1 38,0 0 1,0 0 0,1 0 0,-1 0 0,1-1 0,0 1 0,-1-1-1,1 1 1,0-1 0,6 1 0,7 3 262,0-2 1,31 3-1,-40-5-248,0 0 0,0 0-1,0-1 1,0 0 0,0 0-1,1-1 1,-1 0 0,0 0-1,0 0 1,0-1-1,-1 0 1,1-1 0,0 0-1,-1 0 1,8-4 0,1-9 11</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6935.56">283 97 9830,'2'18'444,"0"0"1,2 0-1,0-1 1,11 30-1,-9-29-236,-3-9-87,0-1 1,0 0-1,1 0 1,0 0-1,1 0 1,0-1 0,0 1-1,9 9 1,-13-16-113,1 1 1,-1-1-1,1 0 1,-1 0 0,1 0-1,-1 1 1,1-2-1,0 1 1,0 0 0,0 0-1,-1 0 1,1-1-1,0 1 1,0-1-1,0 0 1,0 1 0,0-1-1,0 0 1,0 0-1,0 0 1,0 0-1,0-1 1,0 1 0,0 0-1,0-1 1,0 0-1,-1 1 1,1-1-1,0 0 1,0 0 0,-1 0-1,1 0 1,0 0-1,-1 0 1,1-1-1,-1 1 1,1 0 0,-1-1-1,0 1 1,0-1-1,1 1 1,-1-1-1,1-2 1,4-5-125,-3 5 141,0 0 1,0 0 0,0 1-1,0-1 1,1 1 0,5-5-1,-8 7-13,-1 1 1,1 0-1,0-1 0,-1 1 0,1 0 1,-1 0-1,1 0 0,-1 0 0,1-1 0,0 1 1,-1 0-1,1 0 0,-1 0 0,1 0 0,0 0 1,-1 0-1,1 0 0,-1 1 0,1-1 0,0 0 1,-1 0-1,1 0 0,0 1 0,12 19 365,5 36 167,-8-22 4,26 56 1,-28-70-375,-1-3-140</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9532.21">108 1021 9830,'49'10'1420,"-13"-1"-928,-28-8-392,-1 0 1,0 0-1,1 1 1,-1 0-1,0 1 1,0-1 0,0 1-1,0 1 1,-1-1-1,1 1 1,8 6 0,-13-8-57,0 1 0,0-1 0,0 1 0,-1-1-1,1 1 1,0-1 0,-1 1 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,-1 0 0,0 0 0,0 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,-1 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,-1-1 0,-2 5 0,3-5-8,0-1 0,0 1 0,0-1 0,0 1 1,0-1-1,0 1 0,1 0 0,-1 0 0,0-1 0,1 1 0,0 0 0,-1 0 0,1 0 0,0 0 0,0-1 0,0 1 0,0 0 1,0 0-1,1 0 0,-1 0 0,0-1 0,1 1 0,0 2 0,2-2 23,-1-1 0,0 1-1,0-1 1,1 0 0,-1 0 0,1 0 0,-1 0 0,1 0-1,-1-1 1,1 1 0,0-1 0,-1 0 0,1 1 0,0-1-1,-1 0 1,4-1 0,8 2 146,1-1 0,-1-1-1,29-5 1,-23 0-159</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10076.49">532 971 9830,'96'82'2837,"3"2"-1619,-89-73-1033,0-1-1,-1 2 1,0-1 0,-1 1 0,-1 0-1,12 24 1,-18-35-155,0 1 1,0-1-1,-1 1 1,1 0-1,0-1 1,-1 1-1,0-1 1,1 1-1,-1 0 1,0-1-1,0 1 1,0 0-1,0 0 1,0-1-1,0 1 1,0 0-1,0-1 1,-1 1-1,1 0 1,-1-1-1,1 1 1,-1-1-1,0 1 0,-1 2 1,0-3 14,1 1 0,-1-1 1,0 0-1,0 0 0,0 0 0,0 0 0,0 0 0,0-1 1,0 1-1,0-1 0,0 1 0,0-1 0,0 0 0,0 1 1,0-1-1,-4-1 0,-3 1 10,-1-1 0,1-1 0,0 1 0,0-1 0,0-1 0,1 0 0,-17-8 0,20 9-80,0-1 1,1 0 0,-1-1 0,1 1-1,0-1 1,0 1 0,0-1-1,0-1 1,1 1 0,-1 0-1,1-1 1,0 0 0,1 0-1,-1 0 1,1 0 0,0 0-1,0 0 1,0 0 0,-1-11-1,2 1-81,1-1-1,1 1 1,0-1-1,1 1 0,5-23 1,5-45-334,-12 78 449,0 1 0,0-1 1,-1 1-1,1-1 0,-1 1 1,0 0-1,-1-1 0,1 1 1,-1 0-1,0 0 0,0 0 0,0 0 1,0 0-1,-1 0 0,0 1 1,0-1-1,0 1 0,0-1 1,0 1-1,0 0 0,-1 1 0,0-1 1,-7-4-1,-5-1 21</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink101.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:49:19.092"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.1" units="cm"/>
-      <inkml:brushProperty name="height" value="0.1" units="cm"/>
-      <inkml:brushProperty name="color" value="#008C3A"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 1 9830,'10'0'218,"0"0"1,0 1-1,0 0 0,-1 0 1,1 1-1,0 1 0,-1-1 1,13 6-1,-18-6-170,-1 0 0,1 1 0,-1-1 0,0 0 0,1 1 0,-1 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,-1 0 0,0 1 0,1 0 0,-1-1 0,-1 1-1,1 0 1,-1 0 0,1 0 0,-1 0 0,0 0 0,0 0 0,0 4 0,-1 1 106,1-1 1,1 0-1,0 1 0,0-1 0,0 0 0,1 0 0,0-1 1,1 1-1,0-1 0,0 1 0,1-1 0,-1 0 1,1-1-1,1 1 0,-1-1 0,1 0 0,13 9 0,70 47 906,-29-22-539,-57-38-475,0 0 0,0 1 1,-1-1-1,1 0 0,-1 1 1,1 0-1,-1-1 0,0 1 1,0 0-1,-1 0 0,1 1 1,0-1-1,1 5 0,-3-7-22,0 1 1,0-1-1,0 0 0,0 1 0,0-1 1,0 0-1,0 1 0,-1-1 0,1 0 1,0 1-1,-1-1 0,1 0 0,-1 1 1,0-1-1,1 0 0,-1 0 0,0 0 0,0 0 1,1 1-1,-1-1 0,0 0 0,0-1 1,0 1-1,-1 0 0,1 0 0,0 0 1,0-1-1,0 1 0,0 0 0,-1-1 1,1 1-1,0-1 0,-1 1 0,1-1 0,0 0 1,-1 0-1,-2 1 0,-126 21 1706,99-18-1639</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink102.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:49:22.792"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.1" units="cm"/>
-      <inkml:brushProperty name="height" value="0.1" units="cm"/>
-      <inkml:brushProperty name="color" value="#008C3A"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 125 9830,'0'4'273,"4"6"113,1 6-113,5-1 0,0 2 0,-1 2 1,-3-2-274</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="889.37">450 25 9830,'-1'-1'22,"1"0"0,-1 0 0,0 0 0,0 0 0,1 0 0,-1 0 0,0 0 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,0 1 0,-1-1 0,1 1 0,0-1 0,0 1 0,0 0 0,-1-1 0,1 1 0,0 0 0,0 0 0,-2 0 0,-37-6 786,37 6-755,-7-1 93,-1 0 1,0 1 0,1 0-1,-1 0 1,0 1-1,1 1 1,-1 0 0,-11 4-1,19-5-104,0 0-1,-1 1 1,1 0 0,0-1-1,1 1 1,-1 0-1,0 1 1,0-1-1,1 0 1,-1 1 0,1-1-1,0 1 1,0 0-1,0 0 1,0 0-1,0 0 1,1 0 0,-1 0-1,1 0 1,0 1-1,0-1 1,0 0 0,0 1-1,1-1 1,-1 1-1,1-1 1,0 1-1,0 5 1,0-7-7,0 0-1,0 0 1,0 1-1,1-1 1,-1 0-1,1 0 1,-1 0 0,1 0-1,-1 0 1,1 0-1,0 0 1,0 0 0,0 0-1,0 0 1,1-1-1,-1 1 1,0 0-1,1-1 1,-1 1 0,1-1-1,-1 1 1,1-1-1,0 0 1,0 0 0,-1 0-1,1 0 1,0 0-1,0 0 1,0 0-1,0 0 1,0-1 0,0 1-1,1-1 1,-1 0-1,4 1 1,-1-1 13,0 0 1,1-1 0,-1 1-1,0-1 1,0 0-1,0 0 1,0-1 0,0 1-1,0-1 1,0 0-1,0-1 1,-1 1 0,7-5-1,-9 6-22,-1 0 0,1 0 0,0 0-1,0 0 1,-1 1 0,1-1 0,0 1 0,0-1 0,0 1-1,0 0 1,-1 0 0,1-1 0,0 1 0,0 1-1,0-1 1,0 0 0,0 0 0,0 1 0,-1-1-1,1 1 1,0-1 0,0 1 0,0 0 0,-1 0 0,1 0-1,-1 0 1,1 0 0,0 0 0,-1 0 0,0 0-1,1 1 1,-1-1 0,0 1 0,0-1 0,0 1 0,2 2-1,7 8 125,-1 2 0,0 0 0,8 18 0,-11-20-97,-2-6-3,-1 1-1,0-1 0,0 1 0,-1-1 0,1 1 0,-2 0 0,3 8 0,-4-13-30,0-1 0,0 1 0,-1 0 0,1-1 0,0 1 0,0 0 0,-1-1 0,1 1-1,-1-1 1,1 1 0,-1-1 0,0 1 0,0-1 0,0 1 0,1-1 0,-1 1 0,-1-1 0,1 0 0,0 0 0,0 0 0,0 0 0,-1 1 0,1-2 0,0 1-1,-1 0 1,1 0 0,-1 0 0,1-1 0,-1 1 0,1 0 0,-1-1 0,0 0 0,1 1 0,-1-1 0,-3 0 0,-51 4 305,30-5-294</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1402.46">50 125 9830,'0'4'273,"0"6"0,0 6 0,0 3 0,0 4 0,5 6 338,0 2-338,1 0 0,2-4 0,1-4 0,-2-1 0,-1-4-273</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink103.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:49:26.614"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.1" units="cm"/>
-      <inkml:brushProperty name="height" value="0.1" units="cm"/>
-      <inkml:brushProperty name="color" value="#008C3A"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 1 9830,'0'4'273,"0"6"0,0 5 0,0 5 0,0 2 0,0 3 0,0 1 1,0-5-274</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="841.68">200 26 9830,'0'4'273,"0"6"0,0 5 0,0 5 0,0 2 0,0 3 0,0 1 1,0 4 272,0 2-273,0-5-273</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink104.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:49:39.380"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.1" units="cm"/>
-      <inkml:brushProperty name="height" value="0.1" units="cm"/>
-      <inkml:brushProperty name="color" value="#008C3A"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 0 9830,'2'24'731,"1"-1"0,1 0 0,1-1 0,1 1 0,14 36-1,-4-12 33,280 821 8075,-175-481-6440,-105-325-2398,-3 1 0,-3 1 0,4 111 0,-14-148 0</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink105.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:49:43.388"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.1" units="cm"/>
-      <inkml:brushProperty name="height" value="0.1" units="cm"/>
-      <inkml:brushProperty name="color" value="#008C3A"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 1 9830,'20'-1'403,"0"2"0,0 0 0,0 1 1,0 1-1,-1 1 0,29 10 0,-41-12-315,0 1 1,-1 1 0,1-1-1,-1 1 1,0 0-1,0 0 1,-1 1 0,1 0-1,-1 0 1,0 0-1,0 0 1,0 1 0,-1 0-1,0 0 1,0 0-1,-1 1 1,0-1 0,0 1-1,0 0 1,-1 0-1,3 9 1,-4-12-27,0 0 0,-1 1-1,1-1 1,-1 0 0,0 1 0,0-1 0,0 0 0,0 1-1,-1-1 1,0 0 0,0 1 0,0-1 0,0 0-1,-1 0 1,0 0 0,1 0 0,-4 5 0,-2 0 141,-1 0 1,1 0 0,-1-1-1,-18 14 1,17-15-76,1-1 0,1 1-1,-1 0 1,1 1 0,0 0 0,1 0-1,-7 12 1,12-18-83,0 1 0,0-1 0,1 0-1,-1 0 1,1 1 0,0-1 0,-1 0-1,1 1 1,0-1 0,0 0 0,1 1-1,-1-1 1,0 0 0,1 1 0,-1-1 0,1 0-1,0 0 1,0 0 0,0 0 0,0 0-1,0 0 1,0 0 0,1 0 0,-1 0 0,1 0-1,-1 0 1,1-1 0,0 1 0,0-1-1,-1 1 1,1-1 0,0 0 0,0 0 0,0 0-1,4 2 1,9 5 280,1-1-1,-1 0 1,27 7-1,-34-12-226,26 8 430,69 10 1,-69-16-483</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="589.89">499 76 9830,'9'0'546,"15"0"273,21 0 274,15-5-230,6 0-317,-4-1-273,-8 6 113,-9 11 225,-13 8-338,-11 9 273,-5 9 65,-5 2-338,-5 2 273,-3 0-273,2 0 338,0-2-338,-1-8-273</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="898.8">699 275 9830,'4'0'273,"6"0"0,14 0 546,7 0-546,7 0 274,0 0-274,4 0 273,-2 0-273,-4 0 0,-3 0 0,-3 4 113,-7 2-386</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink106.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:51:52.368"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.1" units="cm"/>
-      <inkml:brushProperty name="height" value="0.1" units="cm"/>
-      <inkml:brushProperty name="color" value="#008C3A"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 0 9830,'2'1'75,"0"-1"1,0 1-1,0-1 1,0 1-1,0 0 0,0 0 1,0 0-1,-1 0 1,1 0-1,0 0 0,-1 0 1,1 0-1,0 1 1,-1-1-1,0 1 0,3 2 1,22 33 558,-17-24-262,12 19 96,2 0-1,1-2 1,1-1-1,1-1 1,2-1-1,32 24 1,-51-45-259,-1 1 1,0 1-1,0-1 0,12 17 1,-11-13-165</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink107.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:51:53.243"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.1" units="cm"/>
-      <inkml:brushProperty name="height" value="0.1" units="cm"/>
-      <inkml:brushProperty name="color" value="#008C3A"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 9830,'4'8'611,"10"8"-1,11 9 163,6 0-500,2 1 113,-1-5-113,-2-1 113,-1 0 0,-1 0 0,2 2 225,-3 6-65,-2 1-160,-6 1-113,-5-1 0,-2-5 0,2-2 114,-1-1-114,-4-4-273</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink108.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:51:55.731"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.1" units="cm"/>
-      <inkml:brushProperty name="height" value="0.1" units="cm"/>
-      <inkml:brushProperty name="color" value="#008C3A"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 9830,'4'0'273,"2"4"0,4 2 0,4 8 338,4 10-1,8 9 163,3 9-163,6 0 1,5 2 161,4-7-226,-1-1 65,-3-6-338,-5-9 0,-4-3 113,-3 3 225,-2 3-225,-5-3-386</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink109.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:51:56.582"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.1" units="cm"/>
-      <inkml:brushProperty name="height" value="0.1" units="cm"/>
-      <inkml:brushProperty name="color" value="#008C3A"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 0 9830,'0'9'546,"0"6"-273,4 10 338,10 9 161,7 7-161,8 9 373,8 5-211,2 2-163,3-10-64,2-3 227,-2-6-387,-3-4 0,-5-9-113,-7-4 0,-10-5-273</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink11.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-10T09:11:48.758"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.035" units="cm"/>
-      <inkml:brushProperty name="height" value="0.035" units="cm"/>
-      <inkml:brushProperty name="color" value="#33CCFF"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">38 0 24575,'-4'6'0,"0"-1"0,0 2 0,0-2 0,1 1 0,0 0 0,1 1 0,-1 0 0,1-1 0,0 1 0,0 0 0,1-1 0,-2 14 0,3-19 0,0 2 0,0-1 0,0-1 0,0 1 0,0 0 0,0 1 0,1-2 0,-1 1 0,1 0 0,-1-1 0,1 1 0,-1 1 0,1-2 0,0 1 0,0-1 0,0 1 0,0-1 0,0 1 0,2 2 0,-1-3 0,0 0 0,0 0 0,0-1 0,0 1 0,0 1 0,0-2 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,0 0 0,0 0 0,1 0 0,-1-1 0,0 1 0,0-2 0,0 2 0,0-1 0,3-1 0,32-21 0,-33 19 0,0 1 0,0 0 0,1 1 0,-1-2 0,1 2 0,0 0 0,0 0 0,0 1 0,5-3 0,-9 4 0,0 0 0,-1 1 0,1-1 0,0 0 0,0 0 0,0 1 0,-1-1 0,1 2 0,0-2 0,0 0 0,-1 1 0,1-1 0,0 1 0,-1 0 0,1-1 0,-1 1 0,1 0 0,-1-1 0,1 1 0,-1 0 0,1-1 0,-1 1 0,0 1 0,1-1 0,-1 0 0,0-1 0,0 1 0,1 0 0,-1 0 0,0 0 0,0 0 0,0-1 0,0 1 0,0 0 0,0 1 0,0-1 0,-1 0 0,1 0 0,-6 42 0,6-42 0,-7 36-111,-2 9-516,-18 62 0,19-87-6199</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink110.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:52:04.185"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.1" units="cm"/>
-      <inkml:brushProperty name="height" value="0.1" units="cm"/>
-      <inkml:brushProperty name="color" value="#008C3A"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 71 9830,'4'0'273,"6"0"0,1-4 0,3-2 0,3-4 113,3-4-420,-1-4 9,-1 0 0,-2 17 775,-5 13-500,-4 8-1,1 9 310,0 9-59,-3 1-250,-1-1-1,-1-7-249</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink111.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:52:05.329"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.1" units="cm"/>
-      <inkml:brushProperty name="height" value="0.1" units="cm"/>
-      <inkml:brushProperty name="color" value="#008C3A"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 1 9830,'0'4'273,"5"2"0,0 3 0,5 1 0,4-1 0,5-3 0,-2-6 1,1 1 112,-3 4-113,-3 6 0,-1 10 337,-1 9-64,2 0-272,-2 3 272,-2 1-273,-2-2 0,-3-6-273</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink112.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -9214,7 +8058,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink113.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink101.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -9243,7 +8087,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink114.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink102.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -9271,7 +8115,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink115.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink103.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -9299,7 +8143,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink116.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink104.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -9329,7 +8173,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink117.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink105.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -9359,7 +8203,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink118.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink106.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -9387,7 +8231,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink119.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink107.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -9415,35 +8259,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink12.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-10T09:11:51.707"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.035" units="cm"/>
-      <inkml:brushProperty name="height" value="0.035" units="cm"/>
-      <inkml:brushProperty name="color" value="#33CCFF"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">436 0 24575,'-33'0'0,"1"2"0,-50 10 0,66-8 0,-1 1 0,1 1 0,0 1 0,2 0 0,-1 1 0,-27 18 0,35-20 0,-8 4 0,2 2 0,-2 0 0,2 1 0,-14 16 0,25-27 0,0 1 0,0 0 0,0 0 0,0 1 0,1-2 0,-1 1 0,1 1 0,-1-1 0,1 1 0,0-1 0,0 2 0,1 4 0,0-7 0,0 0 0,0 1 0,0-1 0,0 0 0,0 1 0,1-1 0,-1 0 0,1 1 0,0-1 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0-1 0,1 2 0,-1-2 0,1 1 0,-1-1 0,1 0 0,-1 2 0,3-1 0,0 1 0,1 0 0,-1-1 0,1 2 0,-1-3 0,1 1 0,9 3 0,-12-5 0,0 1 0,0-1 0,0 1 0,0-1 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0-1 0,0 1 0,-1 0 0,1-1 0,0-1 0,0 2 0,0-1 0,0 0 0,-1 0 0,3-1 0,-3 1 0,-1-1 0,0 2 0,0-1 0,1 0 0,-1 0 0,0 1 0,0-1 0,0 0 0,0 1 0,0-2 0,0 1 0,0 0 0,0 1 0,0-1 0,0 0 0,0 1 0,0-1 0,0 0 0,-1-1 0,1 2 0,0-1 0,-1 0 0,1 1 0,0-1 0,-1 1 0,1-1 0,-1 0 0,1 1 0,-1-1 0,1 1 0,-1-2 0,1 2 0,-1 0 0,1-1 0,-1 1 0,-1-1 0,-22-20 0,14 16-227,-1-1-1,0 1 1,-1 1-1,1-1 1,-21-3-1,4 3-6598</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink120.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink108.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -9472,7 +8288,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink121.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink109.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -9501,7 +8317,35 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink122.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink11.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-10T09:11:48.758"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#33CCFF"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">38 0 24575,'-4'5'0,"0"0"0,0 1 0,0-1 0,1 0 0,0 0 0,1 2 0,-1-1 0,1-1 0,0 1 0,0 1 0,1-2 0,-2 13 0,3-17 0,0 2 0,0-2 0,0 0 0,0 1 0,0 0 0,0 0 0,1-1 0,-1 1 0,1 0 0,-1-1 0,1 1 0,-1 0 0,1-1 0,0 1 0,0-1 0,0 1 0,0-1 0,0 0 0,2 3 0,-1-3 0,0 0 0,0 0 0,0-1 0,0 1 0,0 0 0,0-1 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,0 0 0,0 0 0,1 0 0,-1-1 0,0 1 0,0-1 0,0 1 0,0-1 0,3-1 0,32-19 0,-33 18 0,0 0 0,0 0 0,1 2 0,-1-3 0,1 2 0,0 0 0,0 1 0,0 0 0,5-3 0,-9 4 0,0 0 0,-1 1 0,1-1 0,0 0 0,0 0 0,0 1 0,-1-1 0,1 2 0,0-2 0,0 0 0,-1 1 0,1-1 0,0 0 0,-1 1 0,1-1 0,-1 1 0,1 0 0,-1-1 0,1 1 0,-1 0 0,1-1 0,-1 1 0,0 1 0,1-1 0,-1-1 0,0 0 0,0 1 0,1 0 0,-1 0 0,0 0 0,0 0 0,0-1 0,0 1 0,0 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,-6 38 0,6-38 0,-7 32-111,-2 8-516,-18 55 0,19-77-6199</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink110.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -9530,7 +8374,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink123.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink111.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -9561,7 +8405,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink124.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink112.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -9589,7 +8433,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink125.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink113.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -9618,7 +8462,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink126.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink114.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -9647,7 +8491,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink127.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink115.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -9676,7 +8520,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink128.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink116.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -9700,25 +8544,53 @@
       <inkml:brushProperty name="color" value="#008C3A"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">699 349 9830,'1'6'172,"-1"-1"0,1 0-1,1 1 1,-1-1 0,1 0-1,0 0 1,0 0 0,0 0 0,1 0-1,-1-1 1,7 9 0,43 46 1043,-43-50-980,252 264 3054,-258-270-3218,0 0-1,-1 1 0,1 0 1,-1 0-1,0 0 0,0 0 1,0 0-1,0 0 0,-1 0 1,1 5-1,1 8-25</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="721.6">2646 399 9830,'4'5'386,"6"4"0,5 11 225,9 9 161,5 9-161,1 7-1,4-5-63,5 3 437,4-5-438,4-5 65,1-4-1,-2-2-223,-5-2-1,-6-5-113,-8-6-273</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="116509.7">175 724 9830,'0'5'273,"0"4"0,0 7 0,0 3 0,0 4 0,0-3-273</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="117136.13">375 724 9830,'0'5'273,"0"4"0,0 7 0,4 3 113,6 0-113,1 0 1,3-3-1,-1 0 0,-7-3 0,-13-3 273,-9-4-273,-11-2 273,-5-3-273,-1-1 0,5 0-273</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="117531.24">375 674 9830,'4'0'273,"10"0"273,7 0-273,4 0 0,6 0 274,2 0-274,0 0 0,-1 0 0,-7 0-273</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="114885.52">0 25 9830,'0'5'273,"0"9"273,0 7-273,0 8 273,0 8 1,0 2-274,4-2 113,2-7-386</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="115539.62">150 125 9830,'20'0'663,"36"2"144,-54-2-771,1 0 1,-1 1-1,0 0 0,0-1 0,1 1 0,-1 0 1,0 0-1,0 0 0,0 1 0,0-1 0,0 0 0,0 1 1,-1-1-1,1 1 0,0 0 0,-1-1 0,1 1 1,-1 0-1,1 0 0,0 3 0,58 106 1830,-59-110-1829,0 1-1,1 0 1,-1 0-1,0 0 1,0 0 0,0 1-1,-1-1 1,1 0 0,0 0-1,-1 0 1,0 1-1,1-1 1,-1 0 0,0 4-1,-1-5-12,1 0 0,0 0 0,-1 0 0,1 0 0,-1 0 0,1 0 1,-1 0-1,0 0 0,1 0 0,-1 0 0,0 0 0,1 0 0,-1-1 0,0 1 0,0 0 0,0-1 0,0 1 0,0 0 0,0-1 0,0 1 0,-1 0 0,-7 1 129,0 0-1,0 0 1,-1-1 0,1 0-1,-18-1 1,-13 3 265,22 2-372</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="122107.3">1024 175 9830,'0'-1'20,"1"-1"1,-1 1-1,1-1 0,0 1 1,0 0-1,-1-1 0,1 1 0,0 0 1,0-1-1,1 1 0,-1 0 1,0 0-1,0 0 0,1 0 0,-1 0 1,0 0-1,1 1 0,-1-1 1,1 0-1,-1 1 0,1-1 0,-1 1 1,3-1-1,41-11 721,-41 12-676,30-7 383,0 2-1,44-1 1,-68 6-328,0-1 0,0 2 1,0 0-1,0 0 0,0 1 0,0 0 1,0 0-1,0 1 0,-1 1 0,0 0 1,0 0-1,12 7 0,-19-9-69,0-1 0,0 1 0,0 0-1,0 0 1,0-1 0,-1 1 0,1 0 0,0 1-1,-1-1 1,0 0 0,0 0 0,1 0 0,-1 1-1,-1-1 1,1 1 0,0-1 0,-1 1-1,1-1 1,-1 1 0,0-1 0,1 1 0,-1-1-1,0 1 1,-1-1 0,1 1 0,0-1 0,-1 1-1,0-1 1,1 1 0,-1-1 0,0 1 0,0-1-1,0 0 1,-1 0 0,1 1 0,0-1 0,-3 2-1,-5 9 250,-2-1 0,1 0 0,-1 0 0,-20 15-1,30-27-294,-84 65 1042,58-46-746,1 1 1,0 1-1,-34 37 0,59-57-273,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 1 1,0-1-1,1 0 0,-1 1 0,0-1 0,1 0 0,-1 1 0,1-1 0,0 1 0,-1-1 0,1 1 0,0-1 0,0 1 0,0-1 0,0 4 0,1-4 8,0-1 0,0 1-1,0 0 1,0 0-1,0-1 1,0 1-1,0-1 1,0 1-1,1-1 1,-1 1-1,0-1 1,0 0-1,0 1 1,0-1-1,1 0 1,-1 0-1,0 0 1,0 0-1,0 0 1,1 0-1,0 0 1,11-2 17,0 0-1,0 0 1,20-8 0,9-5-127</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="122791.14">1822 250 9830,'-11'-5'149,"0"1"0,0 0 0,0 1 0,-1 0 0,0 1 0,1 0 0,-1 1 0,0 0 0,-15 1 0,23 0-96,0 0-1,0 0 1,1 0-1,-1 1 1,0-1-1,0 1 1,0 0-1,1 0 0,-1 1 1,0-1-1,1 1 1,-1-1-1,1 1 1,0 0-1,-1 1 1,1-1-1,0 1 1,0-1-1,1 1 1,-1 0-1,1 0 1,-1 0-1,1 0 1,0 0-1,0 1 0,0-1 1,0 0-1,1 1 1,0 0-1,-3 7 1,4-8-10,0-1 0,0 1 1,0 0-1,1 0 0,-1-1 0,1 1 1,-1 0-1,1-1 0,0 1 0,0 0 1,0-1-1,0 1 0,1-1 0,-1 0 1,1 1-1,-1-1 0,1 0 0,0 0 1,0 0-1,0 0 0,0 0 0,0 0 1,0-1-1,1 1 0,-1-1 0,0 1 1,1-1-1,-1 0 0,1 0 0,0 0 1,-1 0-1,1-1 0,4 2 0,-4-1-27,0-1 0,1 1 0,-1-1 0,0 1 0,0-1 0,0 0-1,0 0 1,0 0 0,1-1 0,-1 1 0,0-1 0,0 1 0,0-1 0,0 0-1,0-1 1,0 1 0,-1 0 0,1-1 0,0 1 0,0-1 0,-1 0-1,1 0 1,-1 0 0,0 0 0,0-1 0,0 1 0,0 0 0,0-1 0,0 0-1,1-3 1,2-9-161,5-6 427,-9 21-260,0 0 0,0-1 0,0 1 0,-1 0 0,1 0 0,0 0 0,0-1 0,0 1 0,0 0 0,0 0 0,0 0 1,0 1-1,-1-1 0,1 0 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,-1 1 0,1-1 0,0 1 0,0-1 0,-1 1 0,1-1 1,0 1-1,1 1 0,5 4 67,1 1 0,-1 0 0,0 0 0,0 1-1,-1 0 1,0 0 0,0 0 0,-1 1 0,0 0 0,0 0 0,5 17 0,-9-22-50,1-1 0,-1 1 0,0 0-1,0 0 1,0-1 0,0 1 0,-1 0 0,0 0-1,0 0 1,0 0 0,0 0 0,0 0-1,-1 0 1,0-1 0,1 1 0,-1 0 0,-1 0-1,1-1 1,-1 1 0,1 0 0,-1-1 0,0 0-1,0 1 1,-1-1 0,1 0 0,-1 0 0,1 0-1,-1-1 1,0 1 0,0 0 0,0-1 0,-7 4-1,-68 26 716,58-25-596,1 0 0,0 1 1,1 1-1,-22 15 0,22-10-126</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="124199.52">1298 949 9830,'42'-2'1267,"-32"0"-1118,1 1 0,-1 1 0,1 0 0,-1 0 0,1 1 0,0 0 0,-1 1 0,18 5 0,-27-6-112,0-1 1,0 1-1,0 0 0,0 0 0,-1 0 0,1 0 1,0 0-1,0 0 0,0 0 0,-1 0 0,1 0 1,-1 1-1,1-1 0,-1 0 0,1 0 0,-1 1 1,0-1-1,1 0 0,-1 0 0,0 1 0,0-1 1,0 0-1,0 1 0,0-1 0,0 0 0,-1 2 1,-10 41 540,5-25-364,6-14-137,-1 1 0,1-1-1,0 0 1,0 1-1,0-1 1,1 0-1,0 0 1,0 1-1,0-1 1,1 0-1,-1 0 1,1 0-1,1-1 1,-1 1-1,5 6 1,-4-5 44,0 0 0,0 0 0,0 0-1,-1 0 1,0 1 0,0-1 0,1 13 0,-3-17-77,0 1 1,0 0-1,-1 0 0,1-1 1,-1 1-1,0-1 0,0 1 1,0-1-1,0 1 0,0-1 1,-1 1-1,1-1 0,-1 0 1,1 0-1,-1 1 0,0-1 1,0-1-1,0 1 0,0 0 1,0 0-1,0-1 0,-1 1 1,1-1-1,-1 0 0,1 0 1,-1 1-1,1-2 0,-5 2 1,-5 2 95,-1 0 0,1-1 0,-1 0 0,-19 0 1,6-1-96</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="124760.33">1598 1199 9830,'72'-125'243,"-19"-14"-220,-53 139-3,1-1 0,-1 0 0,0 1 0,0-1 0,0 1 0,0-1 0,1 1 0,-1-1 0,0 0 0,1 1 0,-1-1 0,0 1 0,1-1 0,-1 1 0,1-1 1,-1 1-1,0 0 0,1-1 0,-1 1 0,1-1 0,-1 1 0,1 0 0,0 0 0,-1-1 0,1 1 0,-1 0 0,1 0 0,0 0 0,-1-1 0,1 1 0,-1 0 0,1 0 1,0 0-1,-1 0 0,1 0 0,0 0 0,1 2 28,-1-1-1,1 0 1,-1 0 0,0 1 0,1-1-1,-1 1 1,0-1 0,0 1 0,0 0 0,0-1-1,-1 1 1,2 2 0,19 64 756,-19-61-735,15 93 695,-14-74-720</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="242628.84">3345 874 9830,'0'4'273,"0"6"0,0 5 0,0 9 273,0 5-273,4 1 114,2 4 159,-1 1-273,-1-6-273</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="243241.4">3569 824 9830,'1'10'198,"0"0"0,1 0 0,0 0 0,0 0 0,1 0 0,0-1 0,1 1 0,0-1 0,0 0 0,1 0 0,0-1 0,9 12 0,-10-15-128,0 1 0,0-1 0,1 0 0,0-1 0,0 1-1,0-1 1,0 0 0,0 0 0,1-1 0,0 1 0,0-1 0,0 0 0,0-1 0,0 0 0,1 0 0,-1 0 0,1-1 0,-1 1 0,10-1-1,-13-1-7,-1 1-1,1-1 0,-1 0 0,1 1 0,-1 0 1,1 0-1,-1 0 0,0 0 0,1 0 0,-1 0 1,0 0-1,0 1 0,1-1 0,-1 1 0,-1 0 1,1 0-1,0-1 0,0 1 0,-1 0 0,1 1 1,-1-1-1,1 0 0,-1 0 0,0 1 0,0-1 1,0 0-1,0 1 0,0 3 0,4 10 174,-1 1 0,-1 0-1,2 22 1,-3-19-59,2 13 51,-2-6-181</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="241568.53">3370 0 9830,'0'5'273,"0"5"0,0 5 0,0 4 0,0 4 0,0 2 0,0 5 274,0 6-1,0-4-546</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="242128.69">3569 150 9830,'1'3'86,"0"0"-1,-1 0 0,1 0 1,0 0-1,0 0 1,1 0-1,-1 0 1,0 0-1,1 0 0,0-1 1,0 1-1,0-1 1,0 0-1,0 1 1,0-1-1,0 0 0,4 2 1,2 2 56,0 0 1,0-1 0,0 0-1,11 5 1,-9-7-10,0 1 0,0-2 1,0 1-1,0-1 0,0-1 0,0 0 0,1 0 1,-1-1-1,15-2 0,-21 2-126,-1 0 0,1-1 0,-1 1 0,1-1 0,-1 0 0,1 0 1,-1 0-1,0 0 0,1-1 0,-1 1 0,0-1 0,0 0 0,0 0 0,-1 0 0,1 0 0,0-1 0,-1 1 0,1-1 0,-1 1 0,0-1 0,0 0 1,0 0-1,0 0 0,0 0 0,-1 0 0,1 0 0,-1-1 0,0 1 0,0 0 0,1-6 0,-2 7 9,0 1-1,0-1 1,0 0 0,0 0-1,-1 0 1,1 1 0,0-1-1,-1 0 1,1 0-1,-1 1 1,0-1 0,1 0-1,-1 1 1,0-1 0,0 0-1,0 1 1,0 0-1,-1-1 1,1 1 0,-2-2-1,0 0 42,-2 0 0,1 0 0,0 0 0,0 1 0,-1-1 0,0 1 0,-6-2 0,-3 0 88,0 0 1,0 1-1,-1 1 0,-19-1 1,27 2-79,1 1 0,-1 1 0,0-1 0,0 1 0,0 1 0,1-1 0,-1 1 0,0 0 0,-9 5 0,-1 3-32</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="293211.57">2197 250 9830,'18'0'511,"-1"-1"-140,-1 1-1,1 1 1,25 5-1,-37-5-289,-1 0-1,1 1 1,-1-1 0,1 1-1,-1 0 1,0 1-1,0-1 1,0 1 0,0-1-1,0 1 1,0 0-1,-1 1 1,1-1-1,-1 1 1,0-1 0,5 9-1,-1 0 105,0 1 0,-1-1 1,-1 1-1,0 1 0,5 23 0,-8-33-127,-1 0 1,-1 1-1,1-1 1,-1 0-1,0 1 1,0-1-1,0 0 1,0 1-1,-1-1 1,1 0-1,-1 1 1,-1-1-1,1 0 1,0 0-1,-1 0 1,0 0-1,0 0 1,0 0-1,0-1 1,-1 1-1,1-1 1,-6 6-1,5-7 31,-40 41 647,43-42-706,-1 0 0,0 0 0,0 0 1,1 0-1,-1 0 0,0 0 1,1 0-1,-1 1 0,1-1 1,-1 0-1,1 0 0,0 1 1,0-1-1,-1 0 0,1 1 1,0 1-1,1-2-3,-1-1 0,1 1 0,-1 0 0,1 0 1,-1-1-1,1 1 0,0-1 0,-1 1 0,1 0 0,0-1 1,0 1-1,-1-1 0,1 1 0,0-1 0,0 0 0,0 1 1,0-1-1,-1 0 0,1 0 0,0 1 0,0-1 0,0 0 1,0 0-1,0 0 0,0 0 0,0 0 0,1 0 0,2-1-35,1 0-1,-1 0 1,0 0-1,1 0 1,-1 0-1,0-1 1,0 0-1,0 0 0,0 0 1,0 0-1,0-1 1,-1 0-1,1 1 1,4-6-1,12-10-14</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="293709.75">2571 250 9830,'-3'0'76,"0"1"-1,0 0 1,0 0-1,0 0 1,0 0-1,1 0 1,-1 1-1,0-1 0,1 1 1,-1 0-1,1 0 1,-1 0-1,1 0 1,0 0-1,0 0 1,0 1-1,0-1 1,0 1-1,-1 3 1,-28 53 665,28-51-628,0-1 0,0 1 0,1 0 0,1 0 0,-1 0 0,1 0 0,0 0 0,1 0 0,0 0 1,0 0-1,1 0 0,0 0 0,0 0 0,1 0 0,3 9 0,-3-13-55,0 1 1,0-1 0,1 0-1,0 0 1,0 0-1,0 0 1,0 0-1,0-1 1,1 1-1,-1-1 1,1 0-1,0 0 1,0 0 0,0-1-1,0 1 1,1-1-1,-1 0 1,1 0-1,-1-1 1,1 1-1,0-1 1,0 0-1,-1 0 1,1-1 0,0 1-1,5-1 1,-9 0-34,1 0 1,-1 0-1,0 0 1,1 0-1,-1 0 1,0 0 0,1 0-1,-1 0 1,0 0-1,0-1 1,1 1-1,-1-1 1,0 1 0,0-1-1,0 1 1,1-1-1,-1 0 1,0 1-1,0-1 1,0 0 0,0 0-1,0 0 1,0 0-1,-1 0 1,1 0-1,0 0 1,1-2 0,-2 2-3,0 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0-1 0,0 1 0,-1 0 1,1 0-1,-1 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,1 0 0,-1 1 0,0-1 0,0 0 1,1 0-1,-1 0 0,0 1 0,0-1 0,0 0 0,0 1 0,0-1 0,0 1 0,0-1 0,0 1 1,0-1-1,0 1 0,0 0 0,-2-1 0,-1 0 33,0 0-1,0 0 1,0 0 0,0 1-1,0-1 1,0 1-1,0 0 1,-6 0 0,-7 4-11</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="294348.33">2222 974 9830,'28'-1'715,"-17"0"-507,0 0 1,1 1-1,-1 1 0,19 3 1,-27-4-172,-1 1 1,1 0-1,-1 0 0,0 0 1,1 0-1,-1 0 1,0 0-1,0 1 1,0-1-1,1 1 1,-1-1-1,-1 1 1,1 0-1,0 0 1,0 0-1,-1 0 1,1 0-1,-1 0 0,0 0 1,1 0-1,-1 1 1,0-1-1,0 0 1,-1 1-1,2 3 1,1 8 161,0-1 0,1 0-1,1 0 1,0-1 0,0 1 0,1-1 0,9 13 0,-13-24-164,-1 1 0,0 0 0,0-1 0,1 1 0,-1 0 0,0 0-1,-1 0 1,1 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,-1 0 0,0 0 0,0 0-1,1 0 1,-1 0 0,-1 0 0,1 0 0,0 1 0,0-1 0,-1 0 0,1 0 0,-1 0-1,0 0 1,1 0 0,-1 0 0,0-1 0,-3 5 0,-4 4 10</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="294878.77">2596 1098 9830,'0'4'49,"0"-1"1,1 0-1,-1 0 0,1 0 1,0 0-1,0 0 0,0 0 1,0-1-1,0 1 0,1 0 0,-1 0 1,1-1-1,0 1 0,0-1 1,0 1-1,0-1 0,0 0 1,0 0-1,1 0 0,-1 0 1,1 0-1,-1-1 0,1 1 0,0-1 1,0 1-1,-1-1 0,1 0 1,0 0-1,0 0 0,0-1 1,0 1-1,0-1 0,1 0 0,-1 1 1,0-1-1,0-1 0,0 1 1,0 0-1,0-1 0,0 1 1,0-1-1,0 0 0,0 0 1,0-1-1,0 1 0,-1 0 0,1-1 1,0 1-1,-1-1 0,1 0 1,-1 0-1,0 0 0,0 0 1,0-1-1,0 1 0,0-1 0,3-4 1,-3 4-40,0-1-1,0 0 1,-1 0 0,1 1 0,-1-1 0,0 0-1,0 0 1,-1 0 0,1 0 0,-1 0-1,0-1 1,0 1 0,0 0 0,0 0 0,-1 0-1,0 0 1,0 0 0,0 0 0,0 0 0,0 0-1,-1 1 1,0-1 0,-3-6 0,3 7 28,0 1 0,0-1 0,0 1 0,-1 0-1,1 0 1,0 0 0,-1 0 0,1 0 0,-1 0 0,0 0 0,0 1 0,0 0 0,1-1 0,-1 1 0,-1 0 0,1 0 0,0 1 0,0-1 0,0 1 0,0-1 0,0 1 0,0 0 0,-1 0 0,1 1-1,0-1 1,0 1 0,0-1 0,0 1 0,0 0 0,0 0 0,-4 2 0,-3 3 116,0 0-1,1 1 1,-1 0 0,2 0-1,-1 1 1,1 0 0,0 1-1,-9 12 1,5-5-116</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">808 335 9830,'1'6'172,"-1"-1"0,1 0-1,1 0 1,0 0 0,0 0-1,0 0 1,1 0 0,-1 0 0,1-1-1,0 0 1,7 9 0,50 43 1043,-49-47-980,290 253 3054,-297-259-3218,-1 0-1,-1 1 0,2 0 1,-2 0-1,0-1 0,1 1 1,-1 0-1,0 0 0,0 0 1,0 4-1,1 9-25</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="721.6">3058 383 9830,'5'5'386,"6"4"0,6 10 225,11 9 161,6 8-161,0 8-1,6-6-63,5 3 437,4-4-438,6-5 65,0-4-1,-2-3-223,-5 0-1,-8-6-113,-9-6-273</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="116509.7">202 696 9830,'0'5'273,"0"3"0,0 8 0,0 2 0,0 4 0,0-3-273</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="117136.13">433 696 9830,'0'5'273,"0"3"0,0 8 0,5 2 113,7 0-113,0 0 1,4-2-1,-1-1 0,-8-2 0,-15-4 273,-10-3-273,-13-2 273,-6-3-273,-1-1 0,5 0-273</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="117531.24">433 648 9830,'5'0'273,"11"0"273,8 0-273,5 0 0,7 0 274,2 0-274,0 0 0,-1 0 0,-8 0-273</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="114885.52">0 24 9830,'0'5'273,"0"8"273,0 7-273,0 8 273,0 8 1,0 1-274,5-1 113,2-7-386</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="115539.62">173 120 9830,'23'0'663,"42"2"144,-63-2-771,2 0 1,-2 1-1,1 0 0,-1-1 0,1 1 0,0 0 1,-1 0-1,0 0 0,1 1 0,-1-1 0,0 0 0,1 1 1,-2-1-1,1 0 0,0 1 0,-1-1 0,2 1 1,-2 0-1,1 0 0,1 3 0,66 102 1830,-68-106-1829,0 0-1,2 1 1,-2 0-1,0 0 1,0 0 0,0 1-1,-1-1 1,1 0 0,0 0-1,-1 0 1,0 1-1,2-1 1,-2-1 0,0 5-1,-2-5-12,2 0 0,0 0 0,-1 0 0,1 0 0,-1 0 0,1 0 1,-1 0-1,0 0 0,1 0 0,-1 0 0,0 0 0,1 0 0,-2-1 0,1 1 0,0 0 0,0-1 0,0 1 0,0 0 0,-1-1 0,1 0 0,-1 1 0,-8 1 129,-1 0-1,1 0 1,-2-1 0,2 0-1,-21-1 1,-16 3 265,27 2-372</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="122107.3">1183 168 9830,'0'-1'20,"2"-1"1,-2 1-1,1-1 0,0 1 1,0 0-1,-1 0 0,1 0 0,0 0 1,0-1-1,2 1 0,-2 0 1,0 0-1,0 0 0,2 0 0,-2 0 1,0 0-1,1 1 0,-1-1 1,2 0-1,-2 1 0,1-1 0,-1 1 1,4-1-1,47-10 721,-47 11-676,34-7 383,0 2-1,51-1 1,-78 6-328,-1-1 0,1 2 1,-1 0-1,1 0 0,0 1 0,-1 0 1,1 0-1,-1 1 0,0 1 0,-1 0 1,0-1-1,15 8 0,-23-9-69,0-1 0,1 1 0,-1 0-1,0 0 1,1-1 0,-2 1 0,1-1 0,0 2-1,0-1 1,-1 0 0,0 0 0,1 0 0,-1 1-1,-1-1 1,1 1 0,1-1 0,-2 0-1,1 0 1,-1 1 0,0-1 0,1 1 0,-1-1-1,0 1 1,-1-1 0,1 1 0,0-1 0,-1 1-1,-1-2 1,2 2 0,-1-1 0,0 1 0,0-1-1,0 0 1,-1 0 0,0 1 0,1-1 0,-3 2-1,-7 8 250,-1 0 0,0-1 0,-1 1 0,-23 14-1,35-26-294,-97 62 1042,67-44-746,1 2 1,0 0-1,-40 35 0,69-54-273,0 0 0,0 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 1 1,0-1-1,1 0 0,-1 1 0,0-1 0,1 0 0,-2 1 0,2-1 0,0 1 0,-1-1 0,1 0 0,0 0 0,0 1 0,0-1 0,0 4 0,1-4 8,1-1 0,-1 1-1,0 0 1,0 0-1,0-1 1,0 1-1,0-1 1,1 1-1,0-1 1,-1 1-1,0-1 1,0 0-1,1 1 1,-1-1-1,1 0 1,-1 0-1,0 0 1,0 0-1,1 0 1,0 0-1,0 0 1,13-2 17,0 0-1,0 0 1,23-8 0,11-4-127</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="122791.14">2106 240 9830,'-13'-5'149,"0"2"0,0-1 0,1 1 0,-2 0 0,0 1 0,1 0 0,-1 1 0,1 0 0,-19 1 0,28 0-96,-1 0-1,1 0 1,0 0-1,-1 1 1,1-1-1,-1 1 1,1 0-1,0 0 0,-1 1 1,1-1-1,0 1 1,0-1-1,0 1 1,1 0-1,-2 1 1,2-2-1,-1 2 1,1-1-1,0 1 1,0 0-1,1 0 1,-2 0-1,2 0 1,0 0-1,-1 0 0,1 0 1,0 0-1,1 1 1,-1 0-1,-2 6 1,4-7-10,0-1 0,0 1 1,0 0-1,1 0 0,-1-1 0,1 1 1,-1 0-1,1-2 0,0 2 0,1 0 1,-1-1-1,0 1 0,1-1 0,-1 0 1,2 1-1,-2-1 0,1 0 0,0 0 1,1-1-1,-1 1 0,0 0 0,1 0 1,-1-1-1,1 1 0,0-1 0,-1 1 1,2-1-1,-2 0 0,1 0 0,1 0 1,-2 0-1,2-1 0,4 2 0,-5-1-27,1-1 0,0 1 0,0-1 0,-1 1 0,1-1 0,-1 0-1,1 0 1,-1 0 0,2-1 0,-2 1 0,1-1 0,-1 1 0,0-1 0,1 0-1,-1-1 1,1 1 0,-2 0 0,2-1 0,-1 1 0,1-1 0,-2 0-1,1 0 1,0 0 0,-1 0 0,0 0 0,1 0 0,-1 0 0,0-1 0,1 0-1,0-3 1,3-8-161,5-6 427,-9 20-260,-1 0 0,0-1 0,0 1 0,-1 0 0,1 0 0,0 0 0,0-1 0,1 1 0,-1 0 0,0 0 0,0 0 1,0 1-1,-1-1 0,1 0 0,1 0 0,-1 0 0,0 1 0,0-1 0,0 0 0,-1 1 0,1-1 0,0 1 0,1-1 0,-2 0 0,1 0 1,0 1-1,1 1 0,6 4 67,2 1 0,-2 0 0,0-1 0,0 2-1,-1 0 1,0-1 0,0 1 0,-2 1 0,1-1 0,0 1 0,6 16 0,-11-21-50,1-1 0,-1 1 0,0-1-1,0 1 1,1-1 0,-1 1 0,-1 0 0,0 0-1,0-1 1,0 1 0,0 0 0,0 0-1,-1 0 1,-1-1 0,2 1 0,-1-1 0,-1 1-1,1-1 1,-1 1 0,0 0 0,0-1 0,0 0-1,-1 0 1,0 0 0,1 0 0,-2 0 0,2 0-1,-2-1 1,1 1 0,-1 0 0,1-1 0,-9 3-1,-78 26 716,67-24-596,1 0 0,0 0 1,1 2-1,-25 14 0,25-10-126</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="124199.52">1500 912 9830,'49'-2'1267,"-38"0"-1118,2 1 0,-2 1 0,2 0 0,-1 0 0,0 1 0,1 0 0,-1 1 0,20 5 0,-31-6-112,0-1 1,0 1-1,1 0 0,-1 0 0,-1-1 0,1 1 1,0 0-1,0 0 0,0 0 0,-1 0 0,2 0 1,-2 1-1,1-1 0,-1 0 0,1 0 0,-1 1 1,0-1-1,1 0 0,-1 0 0,0 1 0,0-1 1,0 0-1,0 1 0,0-1 0,0 0 0,-1 1 1,-12 41 540,6-25-364,7-13-137,-1 1 0,1-2-1,0 1 1,0 1-1,0-1 1,1 0-1,0-1 1,1 2-1,-1-1 1,1 0-1,-1-1 1,1 1-1,2-1 1,-2 1-1,6 6 1,-4-6 44,-1 1 0,1 0 0,-1 0-1,0-1 1,-1 2 0,0-1 0,2 12 0,-4-16-77,0 1 1,0 0-1,-2 0 0,2-1 1,-1 0-1,0 0 0,0 1 1,0-1-1,0 1 0,0-1 1,-2 1-1,2-1 0,-1 0 1,1 0-1,-2 1 0,1-2 1,0 0-1,-1 1 0,1 0 1,0 0-1,-1-1 0,0 1 1,1-1-1,-2 0 0,2 0 1,-2 1-1,2-2 0,-6 2 1,-6 2 95,-1-1 0,1 0 0,-1 0 0,-22 0 1,7-1-96</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="124760.33">1847 1152 9830,'83'-120'243,"-22"-14"-220,-61 134-3,1-1 0,-1 1 0,0 0 0,0-1 0,0 1 0,0-1 0,2 1 0,-2-1 0,0 0 0,1 1 0,-1-1 0,0 1 0,1-1 0,-1 1 0,1-1 1,-1 1-1,0 0 0,1-1 0,-1 1 0,1-1 0,-1 1 0,1 0 0,1 0 0,-2-1 0,1 1 0,-1 0 0,1 0 0,0 0 0,-1-1 0,1 1 0,-1 0 0,1 0 1,1 0-1,-2 0 0,1 0 0,0 0 0,1 2 28,-1-1-1,2 0 1,-2 0 0,0 1 0,1-1-1,-1 1 1,1-1 0,-1 0 0,0 1 0,0-1-1,-1 1 1,2 2 0,23 61 756,-23-58-735,18 89 695,-17-71-720</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-186867.89">3866 840 9830,'0'4'273,"0"5"0,0 6 0,0 8 273,0 5-273,4 0 114,3 5 159,-1 1-273,-1-6-273</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-186255.33">4125 792 9830,'1'9'198,"0"1"0,1 0 0,1-1 0,-1 1 0,1-1 0,1 0 0,0 1 0,1-2 0,0 1 0,0 0 0,1-2 0,10 13 0,-11-16-128,0 2 0,-1-1 0,2 0 0,0-1 0,0 0-1,-1 0 1,1 0 0,0 0 0,1-1 0,0 1 0,0-1 0,0-1 0,0 0 0,-1 0 0,3 0 0,-2 0 0,1-1 0,-1 1 0,11-1-1,-15-1-7,0 1-1,0-1 0,0 0 0,0 1 0,-1 0 1,2 0-1,-2 0 0,0 0 0,2 0 0,-2 0 1,1 0-1,-1 0 0,1 0 0,0 1 0,-2 0 1,1 0-1,0-1 0,1 1 0,-2 0 0,1 1 1,-1-1-1,2 0 0,-2 0 0,0 1 0,0-2 1,0 1-1,0 1 0,1 3 0,3 9 174,0 2 0,-2-1-1,3 22 1,-3-19-59,1 13 51,-2-7-181</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-187928.2">3895 0 9830,'0'5'273,"0"4"0,0 6 0,0 3 0,0 4 0,0 2 0,0 5 274,0 6-1,0-5-546</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-187368.04">4125 144 9830,'1'3'86,"0"0"-1,-1 0 0,1 0 1,0 0-1,0-1 1,2 1-1,-2 0 1,0 0-1,1 0 0,1-1 1,-1 1-1,0-1 1,1 0-1,-1 0 1,0 0-1,0 0 0,5 2 1,3 2 56,-1 0 1,0-1 0,0-1-1,13 6 1,-10-7-10,-1 1 0,1-2 1,0 0-1,-1 0 0,1-1 0,-1 0 0,2 0 1,-2-1-1,18-2 0,-24 2-126,-2 0 0,2-1 0,-1 1 0,0-1 0,0 0 0,0 1 1,0-1-1,-1 0 0,2-1 0,-2 1 0,1-1 0,-1 0 0,1 0 0,-2 0 0,1 0 0,1-1 0,-2 1 0,2-1 0,-2 1 0,0 0 0,1-1 1,-1 0-1,0 0 0,1 0 0,-2 0 0,1 0 0,-1-1 0,0 2 0,1-1 0,0-6 0,-2 7 9,0 1-1,0-1 1,0 0 0,0 0-1,-1 0 1,1 2 0,0-2-1,-1 0 1,1 0-1,-2 1 1,1-1 0,1 0-1,-1 1 1,0-1 0,0 0-1,0 1 1,-1 0-1,0-1 1,1 1 0,-2-2-1,-1 1 42,-2-1 0,2 0 0,-1 0 0,0 1 0,0-1 0,-1 1 0,-7-2 0,-3 1 88,0-1 1,0 1-1,-2 1 0,-21-1 1,31 2-79,1 1 0,-1 1 0,0-1 0,0 1 0,0 1 0,1-1 0,-1 1 0,-1 0 0,-9 4 0,-2 4-32</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-136285.16">2539 240 9830,'21'0'511,"-2"-1"-140,0 1-1,1 1 1,28 5-1,-42-5-289,-1 0-1,0 1 1,0-1 0,1 1-1,-2 0 1,1 1-1,0-2 1,-1 2 0,1-1-1,-1 1 1,1 0-1,-1 1 1,0-1-1,0 1 1,-1-2 0,6 10-1,-1 0 105,1 0 0,-3 0 1,0 0-1,0 1 0,6 23 0,-10-32-127,-1 0 1,-1 1-1,1-2 1,-1 1-1,0 1 1,0-1-1,0 0 1,0 1-1,-1-2 1,1 1-1,-1 1 1,-1-1-1,0 0 1,1 0-1,-1-1 1,0 1-1,-1 0 1,1 0-1,0-1 1,-2 1-1,2-1 1,-7 5-1,5-6 31,-45 39 647,49-40-706,-2 0 0,1 0 0,0 0 1,1 0-1,-1 0 0,0 0 1,1 0-1,-1 1 0,1-1 1,-2 0-1,2 0 0,0 1 1,0-1-1,-1 0 0,1 1 1,0 1-1,1-2-3,-1-1 0,2 0 0,-2 1 0,1 0 1,-1-1-1,1 1 0,0-1 0,-1 1 0,1 0 0,0-1 1,1 1-1,-2-1 0,1 1 0,0-1 0,0 0 0,0 1 1,0-1-1,-1 0 0,1 0 0,1 1 0,-1-1 0,0 0 1,0 0-1,0 0 0,0 0 0,1 0 0,0 0 0,2-1-35,2 0-1,-1 0 1,-1 0-1,2 0 1,-1 0-1,0-1 1,-1 1-1,1-1 0,-1 0 1,1 0-1,0-1 1,-2 0-1,2 1 1,4-6-1,14-9-14</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-135786.98">2971 240 9830,'-3'0'76,"-1"1"-1,1 0 1,-1 0-1,1 0 1,-1 0-1,2 0 1,-1 1-1,-1-1 0,2 1 1,-2 0-1,2 0 1,-1 0-1,0-1 1,1 1-1,0 0 1,-1 1-1,1-1 1,0 1-1,-2 3 1,-32 50 665,33-48-628,0-1 0,-1 1 0,2-1 0,1 1 0,-2 0 0,2-1 0,0 1 0,1 0 0,0-1 1,0 1-1,1 0 0,0-1 0,0 1 0,2 0 0,3 8 0,-4-12-55,0 1 1,0-1 0,2-1-1,-1 1 1,1 0-1,-1 0 1,1 0-1,-1-1 1,2 1-1,-2-2 1,2 1-1,0 0 1,-1 0 0,1-1-1,-1 1 1,2-1-1,-1 0 1,1 0-1,-2-1 1,2 1-1,0-1 1,0-1-1,-2 1 1,2-1 0,0 1-1,5-1 1,-10 0-34,2 0 1,-2 0-1,0 0 1,1 0-1,0 0 1,-1 0 0,1 0-1,-1 0 1,0 0-1,1-1 1,0 1-1,-1-1 1,0 1 0,0 0-1,0 0 1,2-1-1,-2 0 1,0 1-1,0-1 1,0 0 0,1 0-1,-1 0 1,0 0-1,-1 0 1,1 0-1,0 0 1,1-2 0,-2 2-3,0 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0-1 0,0 1 0,-1 0 1,1 0-1,-1 1 0,1-1 0,-1 0 0,1 0 0,-1 0 0,1 0 0,-1 1 0,-1-1 0,1 0 1,1 0-1,-1 0 0,0 1 0,0-1 0,0 0 0,-1 1 0,1-1 0,0 1 0,0-1 0,0 1 1,0-1-1,0 1 0,-1 0 0,-1-1 0,-2 0 33,1 0-1,-1 0 1,0 0 0,1 1-1,-1-1 1,1 1-1,-1 0 1,-7 0 0,-7 4-11</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-135148.4">2568 936 9830,'32'-1'715,"-19"0"-507,0 0 1,1 1-1,-2 1 0,23 3 1,-32-4-172,0 1 1,0 0-1,-1 0 0,1 0 1,0 0-1,0 0 1,-1 0-1,0 0 1,1 0-1,0 1 1,-1-1-1,-1 1 1,2 0-1,-1 0 1,0 0-1,0 0 1,0 0-1,-1 0 0,0 0 1,1 0-1,0 1 1,-1-2-1,0 1 1,-1 1-1,2 3 1,2 7 161,-1 0 0,2-1-1,1 1 1,-1-2 0,1 2 0,1-2 0,10 14 0,-14-25-164,-2 2 0,0 0 0,0-1 0,1 1 0,0 0 0,-1 0-1,-1 0 1,1 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,-1-1 0,0 1 0,0 0-1,2 0 1,-2 0 0,-2 0 0,2 0 0,0 1 0,0-1 0,-1 0 0,1 0 0,-1 0-1,0 0 1,1-1 0,-1 1 0,0-1 0,-4 5 0,-4 4 10</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-134617.96">3000 1055 9830,'0'4'49,"0"-1"1,1 0-1,-1 0 0,1-1 1,1 1-1,-1 0 0,0 0 1,0-1-1,0 1 0,2 0 0,-2 0 1,1-1-1,0 0 0,1 0 1,-1 1-1,0-1 0,1 0 1,-1 0-1,1 0 0,0 0 1,0 0-1,-1-1 0,2 1 0,-1-1 1,1 1-1,-2-1 0,2-1 1,-1 1-1,1 0 0,-1-1 1,0 1-1,1-1 0,1 0 0,-2 1 1,0-1-1,1-1 0,-1 1 1,1 0-1,-1-1 0,1 1 1,-1-1-1,1 0 0,-1 1 1,1-2-1,-1 1 0,-1 0 0,2-1 1,-1 1-1,0-1 0,0 0 1,-1 0-1,1 0 0,-1 0 1,0-1-1,1 1 0,-1 0 0,4-5 1,-4 4-40,0-1-1,1 0 1,-2 0 0,1 1 0,-1 0 0,1-1-1,-1 0 1,-1 0 0,1 0 0,-1 0-1,0 0 1,0 0 0,0 0 0,0 0 0,-1 0-1,0 0 1,-1 1 0,1-1 0,0 0 0,0 0-1,-1 1 1,-1-1 0,-3-5 0,4 6 28,0 1 0,0-1 0,-1 1 0,0 0-1,0 0 1,1 0 0,-1 0 0,0 0 0,0 1 0,-1-1 0,1 1 0,0 0 0,0-1 0,0 1 0,-2 0 0,2 0 0,-1 1 0,1-1 0,-1 1 0,1-1 0,-1 1 0,1 0 0,-2 0 0,2 1-1,-1-1 1,1 1 0,-1-1 0,1 1 0,-1 0 0,1 0 0,-5 2 0,-4 2 116,1 1-1,0 1 1,0 0 0,2-1-1,-2 2 1,2 0 0,0 0-1,-11 13 1,6-6-116</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink12.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-10T09:11:51.707"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#33CCFF"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">517 0 24575,'-39'0'0,"1"2"0,-59 8 0,78-7 0,-2 2 0,2 0 0,1 1 0,1 0 0,-1 1 0,-32 15 0,42-17 0,-10 4 0,3 1 0,-3 1 0,3 0 0,-17 14 0,29-24 0,1 2 0,0-1 0,-1 1 0,1 1 0,1-3 0,-2 2 0,2 0 0,-1 0 0,1 0 0,-1 0 0,1 1 0,1 4 0,0-6 0,0-1 0,0 2 0,0-1 0,0-1 0,0 2 0,1-1 0,-1-1 0,2 2 0,-1-1 0,0-1 0,0 1 0,0 0 0,0-1 0,1 1 0,-1-1 0,1 2 0,-1-2 0,2 0 0,-2 0 0,1 0 0,-1 2 0,4-2 0,0 2 0,1-1 0,-1 0 0,1 2 0,-2-4 0,2 2 0,11 2 0,-15-4 0,1 1 0,-1-1 0,0 1 0,1-1 0,-1 0 0,0 0 0,1 0 0,-1 0 0,1 0 0,-1-1 0,0 1 0,-1 0 0,2-1 0,-1 0 0,1 1 0,-1-1 0,0 0 0,0 0 0,2-1 0,-3 2 0,-1-2 0,0 2 0,0-1 0,2 0 0,-2 0 0,0 1 0,0-1 0,0 1 0,0 0 0,0-2 0,0 1 0,0 0 0,0 1 0,0-1 0,0 0 0,0 1 0,0 0 0,0-1 0,-2-1 0,2 2 0,0-1 0,-1 0 0,1 1 0,0-1 0,-1 1 0,1 0 0,-1-1 0,1 1 0,-1-1 0,1 1 0,-1-2 0,1 2 0,-2 0 0,2-1 0,-1 1 0,-1-1 0,-27-17 0,17 14-227,-1-1-1,0 1 1,-1 0-1,1 0 1,-25-3-1,5 3-6598</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -9746,8 +8618,8 @@
       <inkml:brushProperty name="color" value="#33CCFF"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 30 24575,'50'-12'0,"-7"2"0,41 2 0,125 9 0,-206-1 0,-1 0 0,1 0 0,-1 0 0,1 1 0,-1-1 0,1 1 0,0-1 0,-1 1 0,1 0 0,-1 0 0,0 2 0,1-2 0,-1 0 0,1 1 0,-2 0 0,2-1 0,-1 1 0,-1 0 0,1 1 0,1 0 0,-2-1 0,4 5 0,-4-1 0,0-2 0,0 1 0,-1 0 0,1 0 0,-1 0 0,0 0 0,0 0 0,0 0 0,0 0 0,-1 0 0,0-1 0,0 2 0,1-2 0,-4 8 0,-6 37 0,1-1 0,-5 83 0,10-107-1365,0-6-5461</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="396.91">137 228 24575,'4'0'0,"5"0"0,5 0 0,3 0 0,5 0 0,0 0 0,4 0 0,4 0 0,-2 0 0,-1 0 0,0 0 0,-2 0 0,-2 0 0,0 6 0,0 0 0,-4-1-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 28 24575,'58'-11'0,"-9"1"0,48 3 0,143 8 0,-236-1 0,-2 0 0,2 0 0,-2 0 0,1 1 0,0-1 0,0 1 0,1-1 0,-2 1 0,1 0 0,0 0 0,-1 1 0,1-1 0,0 0 0,0 1 0,-2 0 0,3-1 0,-2 1 0,-1-1 0,1 2 0,2 0 0,-3-1 0,5 4 0,-5 0 0,0-2 0,0 0 0,-1 1 0,1-1 0,-1 1 0,0 0 0,0-1 0,0 1 0,0-1 0,-1 1 0,0-1 0,0 1 0,1-1 0,-5 7 0,-6 34 0,1-1 0,-7 77 0,13-99-1365,-1-5-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="396.91">158 210 24575,'4'0'0,"7"0"0,5 0 0,3 0 0,7 0 0,-1 0 0,5 0 0,4 0 0,-1 0 0,-2 0 0,0 0 0,-2 0 0,-3 0 0,0 6 0,1-1 0,-5 0-8191</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -9775,8 +8647,8 @@
       <inkml:brushProperty name="color" value="#33CCFF"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">37 1 24575,'-1'0'0,"1"0"0,-1 0 0,1 0 0,-1 0 0,1 0 0,0 0 0,-1 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,1 1 0,-1-1 0,1 0 0,0 0 0,-1 1 0,1-1 0,0 0 0,-1 1 0,1-1 0,-1 1 0,1-1 0,0 1 0,0-1 0,0 2 0,-1-2 0,1 1 0,0-1 0,0 1 0,-1-1 0,1 1 0,0-1 0,0 1 0,0-1 0,0 1 0,-1 0 0,1-1 0,0 1 0,0-1 0,0 1 0,0 0 0,1-1 0,-1 1 0,0-1 0,0 1 0,0-1 0,0 2 0,0-1 0,1-1 0,-1 1 0,0-1 0,1 1 0,-1-1 0,0 1 0,16 32 0,-4-19 0,1-1 0,1 0 0,0-2 0,0 0 0,1-2 0,15 8 0,-13-8 0,-1 1 0,0 1 0,0 1 0,25 26 0,-40-38 0,-1 1 0,1-1 0,0 1 0,0 0 0,-1-1 0,1 1 0,0 1 0,0-1 0,0 0 0,-1 0 0,0 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,0 1 0,0-1 0,0 0 0,1 0 0,-1 0 0,0 1 0,0-1 0,0 0 0,0 0 0,0 0 0,0 0 0,0 2 0,0-2 0,-1 0 0,1 0 0,0 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,-1 0 0,0 1 0,1-1 0,0 0 0,-1 0 0,1 0 0,-1 0 0,0 0 0,0-1 0,1 1 0,-1 0 0,0-1 0,0 1 0,1-1 0,-1 1 0,0-1 0,-1 1 0,-6 5 0,-1-1 0,1 0 0,-1-1 0,-9 3 0,18-7 0,-44 14-455,0-3 0,-47 4 0,65-14-6371</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="350.41">78 29 24575,'3'0'0,"5"0"0,5 0 0,3 0 0,3 0 0,1 0 0,1 0 0,1 0 0,-2 0 0,-2 0-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">46 1 24575,'-1'0'0,"1"0"0,-1 0 0,1 0 0,-1 0 0,1 0 0,0 0 0,-2 0 0,2 0 0,-1 0 0,1 0 0,-1 0 0,1 1 0,-1-1 0,1 0 0,0 0 0,-2 1 0,2-1 0,0 0 0,-1 1 0,1-1 0,-1 1 0,1-1 0,0 1 0,0-1 0,0 1 0,-1-1 0,1 1 0,0-1 0,0 1 0,-2-1 0,2 1 0,0-1 0,0 1 0,0-1 0,0 1 0,-1 0 0,1-1 0,0 1 0,0-1 0,0 1 0,0 0 0,1-1 0,-1 1 0,0-1 0,0 0 0,0 0 0,0 2 0,0-1 0,2-1 0,-2 1 0,0-1 0,1 1 0,-1-1 0,0 1 0,20 29 0,-5-17 0,2-1 0,0 0 0,1-2 0,0 0 0,1-2 0,19 8 0,-17-8 0,-1 1 0,1 1 0,-1 1 0,32 24 0,-51-35 0,-1 1 0,1-1 0,0 0 0,1 1 0,-2-1 0,1 1 0,0 1 0,0-1 0,1 0 0,-2 0 0,0 0 0,1 0 0,-1 0 0,1-1 0,-1 1 0,1 0 0,-1 0 0,0 1 0,0-1 0,0 0 0,2 0 0,-2 0 0,0 1 0,0-2 0,0 1 0,0 0 0,0 0 0,0 0 0,0 2 0,0-2 0,-2 0 0,2 0 0,0 0 0,0-1 0,0 1 0,-1 0 0,1 0 0,-1 0 0,0 1 0,1-1 0,0 0 0,-2 0 0,2 0 0,-1-1 0,0 1 0,0-1 0,1 1 0,-2 0 0,1-1 0,0 1 0,1-1 0,-1 1 0,-1-1 0,0 1 0,-8 4 0,-2 0 0,2 0 0,-1-2 0,-12 4 0,23-7 0,-56 12-455,1-2 0,-60 4 0,82-13-6371</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="350.41">98 27 24575,'4'0'0,"6"0"0,7 0 0,3 0 0,4 0 0,1 0 0,2 0 0,0 0 0,-1 0 0,-3 0-8191</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -9832,7 +8704,7 @@
       <inkml:brushProperty name="color" value="#33CCFF"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">159 26 24575,'-50'-13'0,"42"11"0,0-1 0,0 1 0,0 0 0,-1 0 0,1 1 0,-12 1 0,18 0 0,0 0 0,0 1 0,1-1 0,-1 1 0,0-1 0,0 1 0,0 1 0,1-1 0,-1 0 0,0 0 0,1 0 0,-1 0 0,1 0 0,-1 2 0,1-2 0,0 1 0,-1-1 0,1 1 0,0 0 0,0 0 0,0 0 0,0-1 0,1 1 0,-1 1 0,0-1 0,1-1 0,-1 1 0,1 1 0,-1-1 0,1 0 0,0 0 0,0 4 0,0-4 0,-1 1 0,1 0 0,0-1 0,0 1 0,0-1 0,0 0 0,1 2 0,-1-2 0,1 0 0,-1 0 0,1 1 0,0-1 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,1 1 0,-1-2 0,1 1 0,-1-1 0,1 2 0,0-2 0,-1 1 0,1-1 0,0 0 0,3 3 0,5 0 0,1 1 0,0-2 0,-1 0 0,21 4 0,-23-6 0,0 1 0,-1-1 0,0 1 0,1 0 0,-1 2 0,0-2 0,8 6 0,-10-2-80,0-1 0,0 2-1,0 0 1,-1-2 0,1 3-1,-2-1 1,1 0 0,-1 1-1,1-1 1,-2 1 0,1 0 0,-1 0-1,0-1 1,-1 3 0,1-3-1,-1 17 1,-2-10-6746</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">159 23 24575,'-50'-11'0,"42"9"0,0-1 0,0 1 0,0 1 0,-1-1 0,1 1 0,-12 1 0,18 0 0,0 0 0,0 1 0,1-1 0,-1 1 0,0-1 0,0 1 0,0 0 0,1 0 0,-1 0 0,0 0 0,1 0 0,-1 0 0,1 0 0,-1 1 0,1-1 0,0 1 0,-1-1 0,1 1 0,0-1 0,0 1 0,0 0 0,0-1 0,1 0 0,-1 2 0,0-1 0,1-1 0,-1 0 0,1 2 0,-1-1 0,1 0 0,0-1 0,0 5 0,0-5 0,-1 2 0,1 0 0,0-2 0,0 2 0,0-1 0,0-1 0,1 3 0,-1-2 0,1-1 0,-1 1 0,1 1 0,0-1 0,0-1 0,0 1 0,0 1 0,0-2 0,0 1 0,0 0 0,1 1 0,-1-3 0,1 2 0,-1-1 0,1 2 0,0-2 0,-1 0 0,1 0 0,0 0 0,3 3 0,5-1 0,1 1 0,0-1 0,-1 0 0,21 3 0,-23-5 0,0 0 0,-1 0 0,0 1 0,1 0 0,-1 1 0,0-1 0,8 5 0,-10-2-80,0 0 0,0 1-1,0 0 1,-1-2 0,1 3-1,-2 0 1,1-1 0,-1 1-1,1-1 1,-2 1 0,1 0 0,-1 0-1,0-1 1,-1 3 0,1-3-1,-1 15 1,-2-9-6746</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -9860,7 +8732,7 @@
       <inkml:brushProperty name="color" value="#33CCFF"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">55 1 24575,'0'5'0,"0"12"0,-5 3 0,-1 4 0,0 2 0,-3 1 0,0 3 0,1 1 0,3-1 0,1 1 0,2 0 0,1-6-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">55 1 24575,'0'4'0,"0"11"0,-5 3 0,-1 2 0,0 3 0,-3 0 0,0 4 0,1-1 0,3 1 0,1-1 0,2 1 0,1-5-8191</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -9888,7 +8760,7 @@
       <inkml:brushProperty name="color" value="#33CCFF"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">17 2 24575,'-8'65'0,"6"-56"0,0 0 0,0 0 0,1 1 0,1-2 0,-1 2 0,1 0 0,1 16 0,0-24 0,-1 0 0,1 0 0,0 0 0,-1 0 0,1-1 0,0 2 0,0-2 0,0 1 0,0 0 0,0-1 0,0 1 0,0 0 0,1-1 0,-1 0 0,0 0 0,3 3 0,-1-3 0,0 1 0,1 0 0,-1-1 0,1 0 0,-1 0 0,1 1 0,0-2 0,-1 1 0,1-1 0,5 0 0,-5-1 5,0-1 0,0 1 0,1 0 0,-1-2 0,-1 2 0,1-1 0,0-1 0,0 1 0,-1 0 0,1-1 0,-1-1 0,1 1 0,-1 0 0,0 0 0,0-1 0,0-1 0,-1 1 0,1 1 0,-1-2 0,0 1 0,0-1 0,0 1 0,2-7 0,-3 7-49,1 2 1,-1-2-1,0 0 0,0 1 1,0 0-1,-1-1 0,1 1 1,-1-1-1,1 0 0,-1 1 1,0-1-1,0 1 0,0-1 1,0 0-1,-1 1 0,1 0 0,-1-1 1,0 1-1,0-1 0,0 1 1,0 0-1,0-1 0,-1 1 1,1 0-1,-1 0 0,0 0 1,1 1-1,-1-2 0,0 2 1,0-1-1,-1 1 0,1-1 1,-3 0-1,-12-7-6782</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">17 2 24575,'-8'52'0,"6"-45"0,0 1 0,0-1 0,1 1 0,1-2 0,-1 2 0,1 0 0,1 13 0,0-19 0,-1 0 0,1-1 0,0 1 0,-1-1 0,1 0 0,0 2 0,0-3 0,0 2 0,0 0 0,0-2 0,0 2 0,0 0 0,1-2 0,-1 1 0,0 0 0,3 2 0,-1-2 0,0 1 0,1-1 0,-1 0 0,1 0 0,-1 0 0,1 0 0,0-1 0,-1 1 0,1-1 0,5 0 0,-5-1 5,0 0 0,0 0 0,1 0 0,-1-1 0,-1 1 0,1-1 0,0 0 0,0 0 0,-1 1 0,1-2 0,-1 0 0,1 1 0,-1-1 0,0 1 0,0-1 0,0-1 0,-1 0 0,1 2 0,-1-2 0,0 1 0,0-1 0,0 0 0,2-4 0,-3 4-49,1 3 1,-1-3-1,0 1 0,0 1 1,0-1-1,-1 0 0,1 1 1,-1-1-1,1-1 0,-1 2 1,0-1-1,0 0 0,0 0 1,0 0-1,-1 0 0,1 1 0,-1-1 1,0 0-1,0 0 0,0 1 1,0-1-1,0 0 0,-1 1 1,1-1-1,-1 1 0,0-1 1,1 2-1,-1-2 0,0 1 1,0 0-1,-1 0 0,1-1 1,-3 1-1,-12-6-6782</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -10056,7 +8928,7 @@
       <inkml:brushProperty name="color" value="#33CCFF"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 0 24575,'5'14'0,"1"12"0,0 6 0,-2-1-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 0 24575,'5'9'0,"1"7"0,0 5 0,-2-2-8191</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -10084,8 +8956,8 @@
       <inkml:brushProperty name="color" value="#33CCFF"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">47 1 24575,'-4'0'0,"-1"4"0,-4 3 0,0 5 0,2 4 0,2 5 0,1 4 0,2 2 0,1 3 0,1-1 0,0-4-8191</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1004.23">135 59 24575,'9'-1'0,"1"-1"0,-1-1 0,0 1 0,0-1 0,19-9 0,-20 6 0,1 2 0,0 1 0,1 0 0,-1 0 0,15-1 0,-23 4 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 1 0,0-1 0,-1 0 0,1 1 0,-1-1 0,1 1 0,0-1 0,0 1 0,1 2 0,-5 12 0,-27 24 0,18-25 0,12-14 0,0 1 0,-1 1 0,0-1 0,0 0 0,0 0 0,1-1 0,-1 1 0,1 0 0,0 1 0,-1-1 0,1 0 0,-1 0 0,1 1 0,0-1 0,-1 0 0,1 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,0 0 0,0 2 0,0-2 0,0 0 0,0 0 0,1 0 0,-1 0 0,1 0 0,-1 1 0,1-1 0,-1 1 0,0-1 0,0 0 0,1 0 0,0 0 0,0-1 0,-1 1 0,1 0 0,0 0 0,-1 0 0,1-1 0,0 1 0,0 0 0,0-1 0,0 2 0,-1-2 0,1 1 0,2 0 0,8 4 0,-1 1 0,1-1 0,19 5 0,-4-1 0,-22-7 0,0 0 0,0 0 0,0 1 0,0 0 0,0 0 0,-1 0 0,6 7 0,-8-9 0,-1-1 0,1 1 0,-1 0 0,1 0 0,0 0 0,-1 1 0,1-1 0,-1 0 0,1 0 0,-1 0 0,0 0 0,0 0 0,0 0 0,0 0 0,1 0 0,-1 0 0,0 1 0,0-1 0,0 1 0,0-1 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,0 0 0,0 1 0,-1-1 0,1 0 0,-1 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,0 0 0,1-1 0,0 1 0,-1 1 0,0-1 0,0-1 0,0 1 0,0 0 0,-8 6 15,2 0 0,-2 0 0,1-2 0,0 0 0,-1 1 0,-1-2 0,-13 5 0,-1-1-758,-42 4 1,42-9-6084</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">55 1 24575,'-4'0'0,"-2"4"0,-5 2 0,1 5 0,1 3 0,3 5 0,2 4 0,1 2 0,2 2 0,1-1 0,0-3-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1004.23">160 54 24575,'10'-1'0,"2"-1"0,-1-1 0,0 1 0,-1 0 0,23-9 0,-23 5 0,1 3 0,-1 0 0,2 0 0,-1 1 0,17-2 0,-27 4 0,1 0 0,-2 0 0,1 0 0,0 0 0,0 0 0,0 0 0,0 0 0,-1 0 0,2 0 0,-1 0 0,0 1 0,0-1 0,-1 0 0,1 1 0,-1-1 0,2 1 0,-1-1 0,0 1 0,1 1 0,-5 12 0,-33 21 0,22-22 0,14-13 0,0 1 0,-1 1 0,0-1 0,-1-1 0,1 1 0,1-1 0,-1 1 0,1 0 0,0 1 0,-1-1 0,1 0 0,-1 0 0,1 0 0,0 0 0,-2 0 0,2 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,2 0 0,-2 0 0,1 0 0,-1 1 0,1-2 0,-1 2 0,0-1 0,0 0 0,1 0 0,0 0 0,1-1 0,-2 1 0,1 0 0,0 0 0,-1 0 0,1-1 0,0 0 0,1 1 0,-1-1 0,0 2 0,-1-2 0,1 1 0,3 0 0,9 3 0,-1 2 0,1-2 0,22 6 0,-4-2 0,-26-6 0,-1-1 0,1 1 0,0 1 0,0 0 0,-1-1 0,0 1 0,7 6 0,-10-8 0,-1-1 0,1 1 0,-1 0 0,1 0 0,0 0 0,-1 0 0,1 0 0,-1 0 0,2 0 0,-2 0 0,0 0 0,0 0 0,0 0 0,0 0 0,1 0 0,-1 0 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,-1 0 0,1 0 0,0 0 0,0-1 0,0 1 0,0 1 0,-2-1 0,2 0 0,-1 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,0-1 0,1 0 0,0 1 0,-1 1 0,-1-1 0,1-1 0,0 1 0,0 0 0,-10 5 15,3 1 0,-3-1 0,2-2 0,-1 1 0,0 0 0,-2-1 0,-16 4 0,0-1-758,-50 4 1,49-8-6084</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -10113,8 +8985,8 @@
       <inkml:brushProperty name="color" value="#33CCFF"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575,'0'11'0,"0"7"0,0 14 0,0 4 0,0 3 0,0 0 0,0-3 0,0-5-8191</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1021.45">160 32 24575,'-3'56'0,"1"20"0,2-75 0,1 2 0,0-2 0,0 1 0,0 1 0,0-2 0,0 0 0,0 1 0,0-1 0,0 1 0,0 0 0,1-1 0,-1 0 0,0 0 0,1 1 0,-1-1 0,1 0 0,-1 0 0,1-1 0,0 1 0,-1-1 0,1 2 0,0-2 0,-1 1 0,1-1 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,3 0 0,4 0 0,0-1 0,0-1 0,0 1 0,16-5 0,5-9 0,-23 10 0,0 2 0,1-1 0,0 1 0,0 0 0,12-2 0,-18 5 0,-1 0 0,1 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 1 0,0-1 0,-1 1 0,1-1 0,0 1 0,-1 0 0,1-1 0,-1 1 0,1 1 0,-1-1 0,1 0 0,-1 0 0,0 0 0,1 0 0,-1 2 0,0-2 0,0 0 0,0 2 0,0-2 0,0 1 0,0-1 0,-1 2 0,1-2 0,0 1 0,0 2 0,5 23-1365,-3 0-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575,'0'9'0,"0"6"0,0 12 0,0 3 0,0 3 0,0 0 0,0-3 0,0-4-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1021.45">160 27 24575,'-3'47'0,"1"17"0,2-63 0,1 1 0,0-1 0,0 1 0,0 0 0,0-1 0,0 0 0,0 1 0,0-2 0,0 2 0,0 0 0,1-1 0,-1-1 0,0 1 0,1 1 0,-1-1 0,1 0 0,-1 0 0,1-1 0,0 0 0,-1 0 0,1 2 0,0-2 0,-1 1 0,1-1 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,3 0 0,4 0 0,0-1 0,0-1 0,0 2 0,16-6 0,5-6 0,-23 8 0,0 1 0,1 0 0,0 0 0,0 1 0,12-2 0,-18 4 0,-1 0 0,1 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,-1 1 0,1-1 0,0 1 0,-1 0 0,1-1 0,-1 1 0,1 0 0,-1 0 0,1 0 0,-1 0 0,0 0 0,1 0 0,-1 1 0,0-1 0,0 0 0,0 1 0,0-1 0,0 1 0,0-1 0,-1 1 0,1-1 0,0 1 0,0 1 0,5 20-1365,-3-1-5461</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -10143,8 +9015,8 @@
     </inkml:brush>
   </inkml:definitions>
   <inkml:trace contextRef="#ctx0" brushRef="#br0">1 27 24575,'0'5'0,"0"5"0,0 11 0,0 6 0,0 2 0,0 3 0,0-6-8191</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="621.01">153 27 24575,'0'3'0,"-1"1"0,1-1 0,1 0 0,-1 1 0,0-1 0,1 0 0,0 0 0,-1 0 0,1 1 0,0-1 0,0 0 0,0 0 0,1 0 0,-1 0 0,0-1 0,1 1 0,1 2 0,0-2 0,1 0 0,-1-1 0,1 1 0,-1-1 0,1 0 0,0 0 0,0-1 0,-1 1 0,1-1 0,8 1 0,6 3 0,0 1 0,24 11 0,-36-14 0,0 0 0,-1 0 0,0 1 0,0 0 0,1 0 0,-1 0 0,-1 0 0,1 1 0,-1 0 0,0 0 0,5 7 0,-8-11-3,0 1 0,0-1-1,-1 0 1,1 0-1,-1 1 1,0-1 0,0 1-1,1-1 1,-1 0 0,0 1-1,0-1 1,1 1 0,-1-1-1,0 1 1,-1-1 0,1 1-1,0-1 1,0 1 0,0-1-1,-1 1 1,1-1 0,0 0-1,-1 2 1,-1 0 21,0-1 0,1 1 0,-1-1 1,1 1-1,-1-1 0,0 0 0,0 0 0,0 0 1,0 0-1,-3 2 0,-5 2-315,0 0 0,0-1 0,0-1 0,-10 4 0,-5-1-6529</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1036.6">153 1 24575,'4'0'0,"8"0"0,7 0 0,2 0 0,6 0 0,3 0 0,-1 0 0,-2 0 0,-1 0 0,-6 0-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="621.01">183 27 24575,'0'3'0,"-1"1"0,1-1 0,1 0 0,-1 1 0,0-1 0,1 0 0,0 0 0,-1 0 0,1 1 0,1-1 0,-1 0 0,0 0 0,1 0 0,0 0 0,-1-1 0,1 1 0,2 2 0,-1-2 0,2 0 0,-1-1 0,0 1 0,0-1 0,1 0 0,0 0 0,-1-1 0,0 1 0,1-1 0,9 1 0,8 3 0,-1 1 0,29 11 0,-42-14 0,-1 0 0,-1 0 0,0 1 0,0 0 0,1 0 0,-1 0 0,-1 0 0,1 1 0,-2 0 0,1 0 0,6 7 0,-10-11-3,0 1 0,0-1-1,-1 0 1,2 0-1,-2 1 1,0-1 0,0 1-1,1-1 1,-1 0 0,0 1-1,0-1 1,1 1 0,-1-1-1,0 1 1,-1-1 0,1 1-1,0-1 1,0 1 0,0-1-1,-1 1 1,1-1 0,0 0-1,-2 2 1,0 0 21,0-1 0,0 1 0,0-1 1,1 1-1,-2-1 0,1 0 0,0 0 0,-1 0 1,1 0-1,-4 2 0,-6 2-315,0 0 0,0-1 0,0-1 0,-12 4 0,-6-1-6529</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1036.59">183 1 24575,'5'0'0,"9"0"0,9 0 0,2 0 0,7 0 0,4 0 0,-1 0 0,-3 0 0,-1 0 0,-7 0-8191</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -10199,7 +9071,7 @@
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">43 13 24575,'18'-4'0,"-29"-2"0,10 6 0,-1-1 0,1 1 0,-1-1 0,0 1 0,1 0 0,-1 0 0,0 0 0,1 0 0,-1 0 0,0 0 0,1 1 0,-1-1 0,0 0 0,1 1 0,-1-1 0,1 1 0,-1 0 0,1-1 0,-1 1 0,1 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,-2 2 0,2-2 0,1 0 0,-1 0 0,0 0 0,0 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,1 0 0,0 0 0,-1 0 0,1 0 0,0 1 0,0-1 0,0 0 0,0 0 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,1 0 0,-1 0 0,0 0 0,1 0 0,-1 0 0,1 1 0,-1-1 0,1 0 0,0-1 0,-1 1 0,1 0 0,0 0 0,0 0 0,0 0 0,-1 0 0,1-1 0,0 1 0,0 0 0,2 0 0,0 0 0,-1-1 0,1 1 0,0-1 0,-1 1 0,1-1 0,0 0 0,-1 0 0,1 0 0,0-1 0,-1 1 0,1-1 0,-1 1 0,1-1 0,0 0 0,-1 0 0,0 0 0,4-2 0,6-7-105,-17 6 273,-26 4-579,21 0-606,-6 0-5809</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">84 13 24575,'36'-4'0,"-58"-2"0,20 6 0,-2-1 0,2 1 0,-2-1 0,0 1 0,2 0 0,-1 0 0,-1 0 0,2 0 0,-2 0 0,0 0 0,2 1 0,-2-1 0,0 0 0,2 1 0,-2-1 0,2 1 0,-2 0 0,2-1 0,-2 1 0,2 0 0,0 0 0,-2 0 0,2 0 0,0 0 0,0 0 0,-4 2 0,4-2 0,2 0 0,-2 0 0,0 0 0,0 0 0,2 0 0,-2 0 0,2 0 0,-2 0 0,2 0 0,0 0 0,-2 0 0,2 0 0,0 1 0,0-1 0,0 0 0,0 0 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,2 0 0,-2 0 0,0 0 0,2 0 0,-2 0 0,2 1 0,-2-1 0,2 0 0,0-1 0,-2 1 0,2 0 0,0 0 0,0 0 0,0 0 0,-2 0 0,2-1 0,0 1 0,0 0 0,4 0 0,0 0 0,-2-1 0,2 1 0,0-1 0,-2 1 0,2-1 0,0 0 0,-2 0 0,2 0 0,-1-1 0,-1 1 0,2-1 0,-2 1 0,2-1 0,0 0 0,-2 0 0,0 0 0,8-2 0,12-7-105,-34 6 273,-52 4-579,43 0-606,-13 0-5809</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -10226,7 +9098,7 @@
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 5 24575,'2'0'0,"4"0"0,2 0 0,2 0 0,2 0 0,1 0 0,2 0 0,2 0 0,-1 0 0,0 0 0,2 0 0,-1 0 0,-1 0 0,0-2 0,-3-1-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 5 24575,'3'0'0,"5"0"0,3 0 0,3 0 0,3 0 0,1 0 0,3 0 0,3 0 0,-2 0 0,0 0 0,3 0 0,-1 0 0,-2 0 0,1-2 0,-5-1-8191</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -10281,7 +9153,7 @@
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 30 24575,'2'0'0,"3"0"0,1-2 0,1-1 0,3 0 0,0 1 0,2 0 0,1 1 0,0 1 0,0 0 0,3 0 0,-2-3 0,-1 1 0,0-1 0,-3-1 0,-2-1-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 32 24575,'3'0'0,"4"0"0,2-2 0,1-1 0,5-1 0,0 2 0,2 0 0,2 1 0,0 1 0,0 0 0,5 0 0,-4-3 0,-1 1 0,0-1 0,-4-2 0,-3 0-8191</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -10308,7 +9180,7 @@
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575,'2'0'0,"3"0"0,3 0 0,3 2 0,0 1 0,0 2 0,0 0 0,-1 0 0,2-2 0,0-1 0,0 0 0,1-2 0,0 0 0,-2 0-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575,'3'0'0,"5"0"0,4 0 0,5 0 0,0 1 0,0-1 0,0 1 0,-2 0 0,4-1 0,-1 1 0,1-1 0,1 0 0,0 0 0,-4 0-8191</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -10389,7 +9261,7 @@
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 0 24575,'0'5'0,"0"3"0,0 3 0,0 3 0,0 7 0,0 2 0,0-1 0,0-2 0,0-2 0,0-2 0,0-1 0,0-2 0,0 0 0,0-2-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 0 24575,'0'4'0,"0"4"0,0 1 0,0 4 0,0 5 0,0 3 0,0-2 0,0-1 0,0-2 0,0-2 0,0-1 0,0-1 0,0-1 0,0-1-8191</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -10416,7 +9288,7 @@
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 1 24575,'3'2'0,"2"1"0,5 0 0,3-1 0,2 0 0,0-1 0,0-1 0,0 1 0,-1-1 0,0-1 0,-1 1 0,1 0 0,-1 0 0,-2 0-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 1 24575,'4'2'0,"4"2"0,6-1 0,5-1 0,2 1 0,1-2 0,0-1 0,-1 1 0,0-1 0,-1-1 0,-1 1 0,1 0 0,-1 0 0,-3 0-8191</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -10443,7 +9315,7 @@
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 1 24575,'2'0'0,"3"0"0,3 0 0,3 0 0,1 0 0,1 0 0,2 0 0,2 0 0,2 0 0,-1 0 0,-2 0-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 1 24575,'3'0'0,"5"0"0,4 0 0,6 0 0,0 0 0,3 0 0,2 0 0,4 0 0,2 0 0,-1 0 0,-3 0-8191</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -10470,7 +9342,7 @@
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 6 24575,'2'0'0,"8"0"0,8 0 0,4 0 0,2 0 0,0 0 0,-3 0 0,-1 0 0,-4 0 0,-3-2 0,-4-1-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 6 24575,'3'0'0,"11"0"0,12 0 0,5 0 0,4 0 0,-1 0 0,-4 0 0,-2 0 0,-5 0 0,-4-2 0,-6-1-8191</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -10606,16 +9478,16 @@
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1255 39 24575,'0'2'0,"0"4"0,0 1 0,0 4 0,0 0 0,0 4 0,0 2 0,0-1 0,0 0 0,0-1 0,0-3-8191</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="940.63">784 13 24575,'-2'0'0,"-1"3"0,0 2 0,1 3 0,0 4 0,-1 0 0,0 1 0,0 0 0,0 0 0,2-1 0,0 1 0,1 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0-2-8191</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2021.93">262 0 24575,'0'44'0,"-14"119"-1365,14-152-5461</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="53939.3">1007 427 24575,'2'0'0,"3"0"0,3 0 0,3-2 0,-2-1 0,3 0 0,2 1 0,0 0 0,0 1 0,0 1 0,0 0 0,-2 0-8191</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="54519.23">1255 324 24575,'0'4'0,"0"6"0,0 6 0,0 2 0,0 3 0,0 2 0,0 1 0,0-1 0,0 0 0,0-4-8191</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="55928.98">576 388 24575,'2'0'0,"3"0"0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="56838.03">706 362 24575,'27'-5'0,"-24"4"0,0 0 0,0 0 0,0 0 0,1 0 0,-1 1 0,0-1 0,0 1 0,1 0 0,4 1 0,-5-1 0,0 0 0,-1 0 0,1 1 0,-1-1 0,1 1 0,0 0 0,-1 0 0,0 0 0,1 0 0,-1 0 0,0 1 0,1-1 0,-1 0 0,0 1 0,0 0 0,0 0 0,0-1 0,-1 1 0,1 0 0,0 0 0,-1 1 0,1-1 0,-1 0 0,2 4 0,-3-4 0,0 1 0,0 0 0,0 0 0,0-1 0,0 1 0,-1 0 0,1 0 0,-1-1 0,1 1 0,-1 0 0,0-1 0,0 1 0,0-1 0,-1 1 0,1-1 0,-1 0 0,1 0 0,-1 1 0,0-1 0,0 0 0,0 0 0,0-1 0,-2 3 0,-28 18 0,26-18 0,0 0 0,0 0 0,0 0 0,1 1 0,-7 6 0,15-10 0,1 0 0,-1 0 0,1-1 0,-1 1 0,1-1 0,-1 0 0,1 1 0,3-2 0,99-1-1365,-96 2-5461</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="57825.06">563 388 24575,'2'-2'0,"3"-1"0,3 0 0,2 1 0,2 1 0,-1 0-8191</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="58607.96">1 440 24575,'2'0'0,"3"0"0,1-2 0,1-1 0,2 0 0,2 1 0,3 0 0,-1-1 0,0 0 0,0 0 0,2 0 0,1 2 0,-1 0 0,1 1 0,-4-1-8191</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="59720.92">223 350 24575,'0'-1'0,"1"0"0,-1 0 0,0 1 0,1-1 0,-1 0 0,1 1 0,-1-1 0,1 1 0,0-1 0,-1 1 0,1-1 0,-1 1 0,1-1 0,0 1 0,0-1 0,-1 1 0,1 0 0,0 0 0,-1-1 0,1 1 0,0 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,1 0 0,27-2 0,-24 2 0,4-1 0,1 1 0,0 1 0,-1-1 0,1 2 0,17 3 0,-25-4 0,-1-1 0,1 1 0,-1-1 0,1 1 0,-1 0 0,0-1 0,1 1 0,-1 0 0,0 0 0,0 0 0,1 0 0,-1 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 1 0,-1-1 0,1 0 0,0 1 0,0-1 0,-1 0 0,1 1 0,-1-1 0,0 1 0,1-1 0,-1 1 0,0-1 0,0 1 0,0-1 0,0 1 0,0-1 0,0 1 0,0-1 0,0 1 0,-1-1 0,1 1 0,-1-1 0,1 1 0,-1-1 0,0 1 0,1-1 0,-1 0 0,0 1 0,-2 1 0,-2 5 0,0-1 0,0 0 0,-1 0 0,0-1 0,0 0 0,-1 0 0,0 0 0,0-1 0,-1 0 0,-12 7 0,31-10 0,0 0 0,0 1 0,-1 0 0,1 0 0,-1 1 0,15 8 0,-23-11 0,0 0 0,0 0 0,1 0 0,-1 1 0,0-1 0,0 1 0,-1-1 0,1 1 0,0 0 0,0 0 0,-1-1 0,1 1 0,-1 0 0,0 0 0,0 1 0,1-1 0,-1 0 0,-1 0 0,1 1 0,0-1 0,0 3 0,-1-3 0,-1 0 0,1 0 0,-1 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,-1-1 0,1 1 0,0 0 0,-1-1 0,1 1 0,-1-1 0,0 0 0,0 1 0,1-1 0,-1 0 0,0 0 0,0 0 0,0 0 0,0-1 0,-4 2 0,-13 4-170,-1-1-1,0 0 0,0-2 1,0 0-1,0-2 0,-1 0 1,-28-2-1,34 0-6655</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1489 36 24575,'0'2'0,"0"4"0,0 0 0,0 5 0,0-1 0,0 4 0,0 2 0,0-1 0,0 0 0,0-1 0,0-3-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="940.63">930 12 24575,'-2'0'0,"-2"3"0,1 2 0,0 2 0,1 4 0,-2 0 0,1 2 0,-1-1 0,1 0 0,1-1 0,1 1 0,1 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,0-2-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2021.93">311 0 24575,'0'41'0,"-17"111"-1365,17-142-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="53939.3">1195 398 24575,'2'0'0,"4"0"0,3 0 0,4-1 0,-2-2 0,3 0 0,3 1 0,0 0 0,-1 1 0,1 1 0,-1 0 0,-1 0-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="54519.23">1489 302 24575,'0'4'0,"0"5"0,0 6 0,0 2 0,0 3 0,0 1 0,0 2 0,0-2 0,0 0 0,0-3-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="55928.98">683 362 24575,'3'0'0,"3"0"0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="56838.03">837 338 24575,'32'-5'0,"-28"4"0,0 0 0,-1 0 0,1 0 0,0 0 0,0 1 0,0-1 0,-1 1 0,2 0 0,4 1 0,-5-1 0,0 0 0,-2 0 0,1 1 0,0-1 0,0 1 0,1 0 0,-2 0 0,1 0 0,0 0 0,0 0 0,-1 1 0,2-1 0,-2 0 0,0 1 0,1-1 0,-1 1 0,0-1 0,0 1 0,0 0 0,0 0 0,0 1 0,0-2 0,-1 1 0,3 4 0,-4-4 0,0 1 0,0-1 0,0 1 0,0-1 0,0 1 0,-2 0 0,2-1 0,-1 0 0,1 1 0,-1 0 0,0-1 0,0 1 0,0-2 0,-2 2 0,2-1 0,-1 0 0,0 0 0,0 1 0,0-1 0,-1-1 0,1 1 0,0-1 0,-3 3 0,-33 16 0,31-16 0,0 0 0,-1 0 0,1-1 0,1 2 0,-8 5 0,18-9 0,0 0 0,0 0 0,1-1 0,-2 1 0,2-1 0,-1 0 0,0 1 0,5-2 0,116-1-1365,-113 2-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="57825.06">668 362 24575,'2'-2'0,"4"-1"0,4 1 0,1 0 0,4 1 0,-2 0-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="58607.96">1 411 24575,'2'0'0,"4"0"0,1-2 0,2-1 0,1 0 0,3 1 0,4 0 0,-2 0 0,1-1 0,-1 0 0,3 0 0,1 2 0,-1 0 0,1 1 0,-5-1-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="59720.92">264 327 24575,'0'-1'0,"2"0"0,-2 0 0,0 1 0,1-1 0,-1 0 0,1 1 0,-1-1 0,1 1 0,0-1 0,-1 1 0,2-1 0,-2 1 0,1-1 0,0 1 0,0-1 0,-1 1 0,1 0 0,0 0 0,-1-1 0,2 1 0,-1 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,1 0 0,0 0 0,32-2 0,-28 2 0,5-1 0,1 1 0,0 1 0,-2-1 0,2 2 0,20 3 0,-29-4 0,-2-1 0,1 1 0,-1-1 0,2 1 0,-2 0 0,0-1 0,1 1 0,0 0 0,-1-1 0,0 1 0,1 0 0,0 0 0,-1 0 0,0 0 0,0 0 0,0 0 0,1 1 0,-2-1 0,1 0 0,0 1 0,0-1 0,-1-1 0,1 2 0,-1-1 0,0 1 0,1-1 0,-1 1 0,0-1 0,0 1 0,0-1 0,0 1 0,0-2 0,0 2 0,0-1 0,0 1 0,-1-1 0,1 1 0,-1-1 0,1 1 0,-1-1 0,0 1 0,1-2 0,-1 1 0,-1 1 0,-1 1 0,-3 5 0,0-2 0,0 1 0,-1-1 0,0 0 0,0-1 0,-2 1 0,1 0 0,0-2 0,-2 1 0,-13 6 0,36-9 0,0 0 0,0 1 0,-1-1 0,1 1 0,-2 1 0,19 7 0,-28-10 0,1 0 0,-1 0 0,2 0 0,-2 1 0,1-1 0,-1 0 0,-1 0 0,1 1 0,1 0 0,-1 0 0,-1-1 0,2 1 0,-2 0 0,0 0 0,0 0 0,2 0 0,-2 0 0,-1 0 0,1 1 0,0-1 0,0 2 0,-1-2 0,-1 0 0,1 0 0,-1 0 0,0 0 0,0-1 0,0 1 0,-1 0 0,1 0 0,0 0 0,-1-1 0,0 1 0,1 0 0,-1-1 0,1 0 0,-2 0 0,1 0 0,0 1 0,0-1 0,0 0 0,0 0 0,-1 0 0,1 0 0,-1-1 0,-4 2 0,-15 3-170,-2 0-1,0 0 0,1-3 1,-1 1-1,0-2 0,-1 0 1,-33-2-1,40 0-6655</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -10671,8 +9543,8 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 127 24575,'51'64'0,"-41"-50"0,0-1 0,1 1 0,0-2 0,16 14 0,-26-25 0,0 0 0,0-1 0,0 1 0,0 0 0,1-1 0,-1 1 0,0-1 0,0 1 0,0-1 0,0 0 0,1 1 0,-1-1 0,0 0 0,0 0 0,1 0 0,-1 0 0,0 0 0,0 0 0,1 0 0,-1-1 0,0 1 0,0 0 0,2-1 0,0-1 0,0 1 0,0-1 0,0 0 0,0 0 0,0 0 0,0 0 0,-1-1 0,4-3 0,5-8 0,0 0 0,14-27 0,-17 29 0,-6 8-170,1 0-1,0 0 0,1 0 1,-1 0-1,1 0 0,-1 1 1,9-6-1,-3 4-6655</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1208.41">210 206 24575,'2'0'0,"3"0"0,5 0 0,1-2 0,3-6 0,2-3 0,-1-4 0,1-4 0,-1-4 0,1-2 0,-1 2 0,-2 1 0,0 3 0,-1 2 0,0 4 0,-1 5-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 127 24575,'61'65'0,"-50"-51"0,1-1 0,1 1 0,0-2 0,19 14 0,-30-25 0,-1 0 0,0-1 0,0 1 0,0 0 0,2-1 0,-2 1 0,0-1 0,0 1 0,0-1 0,1 0 0,0 1 0,-1-1 0,0 0 0,1 0 0,0 0 0,-1 0 0,0 0 0,1 0 0,0 0 0,-1-1 0,0 1 0,0 0 0,3-1 0,0-1 0,-1 1 0,1-1 0,-1 0 0,1 0 0,-1 0 0,1 0 0,-2-1 0,5-3 0,6-8 0,1 0 0,15-27 0,-19 29 0,-8 8-170,2 0-1,-1 0 0,2 0 1,-2 0-1,2 0 0,-1 1 1,10-7-1,-3 5-6655</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1208.41">249 207 24575,'3'0'0,"3"0"0,5 0 0,2-2 0,4-6 0,2-3 0,-1-4 0,1-4 0,-1-5 0,1-1 0,-2 2 0,-1 1 0,-1 3 0,0 2 0,-1 4 0,-1 5-8191</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -10700,7 +9572,7 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 163 24575,'0'6'0,"2"0"0,-1 0 0,1-1 0,0 1 0,0 0 0,0-1 0,1 0 0,0 1 0,0-1 0,5 6 0,-6-8 0,0 0 0,0-1 0,0 1 0,0 0 0,0-1 0,0 0 0,1 1 0,0-1 0,-1 0 0,1 0 0,0 0 0,0-1 0,0 1 0,0-1 0,0 1 0,0-1 0,0 0 0,1 0 0,3 0 0,-1-2 0,0-1 0,0 0 0,0 0 0,0 0 0,0-1 0,-1 1 0,1-2 0,-1 1 0,0 0 0,0-1 0,0 0 0,6-6 0,5-6 0,-1 0 0,14-20 0,-14 14-341,0-1 0,-1-1-1,18-43 1,-23 45-6485</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 164 24575,'0'6'0,"3"0"0,-2 0 0,1-1 0,1 1 0,-1 0 0,1-1 0,1 0 0,-1 1 0,1-1 0,6 6 0,-7-8 0,-1 0 0,1-1 0,-1 1 0,1 0 0,-1-1 0,1 0 0,0 1 0,1-1 0,-1 0 0,0 0 0,1 0 0,0-1 0,0 1 0,-1-1 0,1 1 0,0-1 0,0 0 0,1 0 0,3 0 0,0-2 0,-1-1 0,1 0 0,0 0 0,-1 0 0,1-1 0,-2 1 0,1-2 0,0 1 0,-1 0 0,0-1 0,0 0 0,8-6 0,6-6 0,-1 0 0,17-20 0,-17 14-341,0-2 0,-2 0-1,23-43 1,-28 45-6485</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -10728,7 +9600,7 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 236 24575,'22'26'0,"-20"-22"0,2 1 0,-1-1 0,0-1 0,1 1 0,0 0 0,8 5 0,-10-8 0,0 0 0,1 0 0,-1 0 0,0 0 0,1-1 0,-1 1 0,1-1 0,-1 1 0,1-1 0,-1 0 0,1 0 0,0 0 0,-1-1 0,1 1 0,-1 0 0,0-1 0,1 0 0,3-1 0,6-4 0,0 1 0,0-2 0,-1 0 0,0 0 0,0-1 0,-1 0 0,0-1 0,-1 0 0,11-13 0,72-98 0,-84 108 0,30-50-1365,-32 47-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 217 24575,'27'24'0,"-25"-20"0,3 1 0,-1-2 0,-1 0 0,2 1 0,0-1 0,9 6 0,-11-8 0,-1-1 0,2 1 0,-2 0 0,1 0 0,0-1 0,0 1 0,1-1 0,-2 1 0,2-1 0,-2 0 0,2 0 0,-1 0 0,0-1 0,0 1 0,0 0 0,-1-1 0,2 0 0,3-1 0,8-3 0,-1 0 0,1-1 0,-2-1 0,0 1 0,1-1 0,-2-1 0,0 0 0,-1 0 0,13-13 0,88-89 0,-103 99 0,38-46-1365,-40 43-5461</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -10756,7 +9628,7 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 297 24575,'29'30'0,"-18"-20"0,5 8 0,-11-11 0,0-1 0,0 0 0,0-1 0,1 0 0,7 6 0,-11-10 0,-1 0 0,0 0 0,1 0 0,-1-1 0,1 1 0,-1-1 0,1 1 0,-1-1 0,1 1 0,0-1 0,-1 0 0,1 0 0,-1 0 0,1 0 0,0 0 0,-1 0 0,1 0 0,-1 0 0,1-1 0,-1 1 0,1-1 0,-1 1 0,1-1 0,-1 0 0,1 1 0,-1-1 0,1 0 0,-1 0 0,0 0 0,2-2 0,14-14 0,-1-2 0,-1 0 0,-1-1 0,-1 0 0,-1-1 0,13-28 0,8-12 0,58-94-1365,-84 145-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 279 24575,'35'29'0,"-22"-20"0,6 8 0,-13-11 0,0 0 0,0 0 0,0-2 0,1 1 0,9 5 0,-14-9 0,-1 0 0,1 0 0,0 0 0,-1-1 0,2 1 0,-2-1 0,1 1 0,-1-1 0,2 1 0,-1-1 0,-1 0 0,2 0 0,-2 0 0,1 0 0,1 0 0,-2 0 0,1 0 0,0 0 0,0-1 0,-1 1 0,2-1 0,-2 1 0,1-1 0,-1 0 0,2 1 0,-2-1 0,1 0 0,0 0 0,-1 1 0,2-3 0,18-13 0,-2-2 0,-1 0 0,-1-1 0,-2 0 0,0 0 0,15-27 0,9-12 0,70-88-1365,-100 137-5461</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -10784,7 +9656,7 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 348 24575,'7'16'0,"2"-1"0,0 0 0,1 0 0,1-1 0,0 0 0,19 19 0,-28-32 0,-1 0 0,0-1 0,0 1 0,1 0 0,-1-1 0,1 1 0,-1 0 0,0-1 0,1 0 0,-1 1 0,1-1 0,-1 0 0,1 0 0,-1 0 0,1 0 0,0 0 0,-1 0 0,1 0 0,-1-1 0,0 1 0,1 0 0,-1-1 0,1 1 0,-1-1 0,1 0 0,-1 0 0,0 1 0,0-1 0,1 0 0,0-1 0,39-37 0,-33 29 0,75-88-682,123-192-1,-186 260-6143</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 331 24575,'8'15'0,"3"-1"0,-1 0 0,1 0 0,2 0 0,0-1 0,22 18 0,-33-30 0,-1 0 0,0-1 0,0 1 0,2 0 0,-2-1 0,1 1 0,-1 0 0,1-1 0,0 0 0,-1 1 0,1-1 0,-1 0 0,2 0 0,-2 0 0,1 0 0,1 0 0,-2 0 0,1 0 0,-1-1 0,0 1 0,2 0 0,-2-1 0,1 1 0,-1-1 0,2 0 0,-2 0 0,0 1 0,0-1 0,1 0 0,1 0 0,44-37 0,-38 29 0,87-84-682,143-183-1,-216 248-6143</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -10812,7 +9684,7 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 302 24575,'0'6'0,"1"-1"0,1 1 0,-1-1 0,1 0 0,0 1 0,1-1 0,-1 0 0,1 0 0,0-1 0,0 1 0,0 0 0,8 7 0,50 48 0,-59-57 0,1 0 0,0 0 0,0-1 0,1 1 0,-1-1 0,1 1 0,-1-1 0,1 0 0,0-1 0,0 1 0,-1 0 0,8 1 0,-9-3 0,0 0 0,0-1 0,1 1 0,-1 0 0,0-1 0,0 1 0,1-1 0,-1 0 0,0 1 0,0-1 0,0 0 0,0 0 0,0-1 0,0 1 0,0 0 0,0-1 0,-1 1 0,1-1 0,0 0 0,-1 1 0,1-1 0,1-3 0,38-54 0,-3-1 0,48-104 0,-34 63 0,-36 69-1365,-4 8-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 287 24575,'0'5'0,"1"0"0,2 1 0,-2-2 0,1 1 0,0 1 0,2-1 0,-2-1 0,2 1 0,-1-1 0,1 1 0,-1-1 0,10 8 0,59 45 0,-69-55 0,0 1 0,1 0 0,-1-1 0,2 1 0,-2-1 0,2 1 0,-1-1 0,0-1 0,1 0 0,0 1 0,-2 0 0,10 1 0,-10-3 0,-1 0 0,0-1 0,2 1 0,-2 0 0,0-1 0,1 1 0,0-1 0,0 0 0,-1 1 0,0-1 0,1 0 0,-1 0 0,0 0 0,1 0 0,-1 0 0,1-1 0,-2 1 0,1-1 0,0 0 0,0 1 0,0-1 0,1-3 0,46-51 0,-5 0 0,58-100 0,-41 60 0,-42 66-1365,-5 7-5461</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -10840,7 +9712,7 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 138 24575,'12'20'0,"1"-1"0,1-1 0,1 0 0,0-1 0,2 0 0,0-1 0,0-1 0,25 15 0,-41-29 0,0 0 0,1 0 0,0 0 0,-1 0 0,1 0 0,-1-1 0,1 1 0,0 0 0,0-1 0,-1 0 0,1 1 0,0-1 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,0-1 0,-1 1 0,1 0 0,0-1 0,0 1 0,-1-1 0,1 0 0,-1 1 0,1-1 0,0 0 0,-1 0 0,1 0 0,-1 0 0,0-1 0,1 1 0,-1 0 0,0 0 0,0-1 0,2-2 0,5-7 0,0-1 0,-1 0 0,11-24 0,-8 16 0,86-163-1365,-84 160-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 138 24575,'14'20'0,"2"-1"0,1-1 0,1 0 0,0-1 0,2 0 0,1-1 0,-1-1 0,31 15 0,-50-29 0,0 0 0,1 0 0,1 0 0,-2 0 0,1 0 0,0-1 0,0 1 0,0 0 0,1-1 0,-2 0 0,1 1 0,1-1 0,-1 0 0,-1 0 0,2 0 0,-1 0 0,1 0 0,-1-1 0,-1 1 0,2 0 0,-1-1 0,1 1 0,-2-1 0,1 0 0,-1 1 0,2-1 0,-1 0 0,-1 0 0,2 0 0,-2 0 0,0-1 0,2 1 0,-2 0 0,0 0 0,0-1 0,3-2 0,5-7 0,1-1 0,-2 0 0,14-24 0,-10 16 0,103-163-1365,-100 160-5461</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -10896,7 +9768,7 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 199 24575,'5'1'0,"1"1"0,0 0 0,-1 1 0,0-1 0,1 1 0,-1 0 0,0 1 0,0-1 0,-1 1 0,6 5 0,1 0 0,134 115 0,-143-123 0,0 0 0,0 0 0,0 0 0,0 0 0,0-1 0,-1 1 0,1-1 0,1 1 0,-1-1 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0-1 0,0 1 0,0-1 0,0 1 0,0-1 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,-1-1 0,1 1 0,-1 0 0,1-1 0,1-2 0,9-8 0,0 0 0,19-26 0,-24 27 0,66-88 0,48-58 0,-105 141-1365,-4 6-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 187 24575,'6'1'0,"0"1"0,1 0 0,-1 0 0,0 0 0,0 1 0,0 0 0,0 1 0,0-2 0,-2 2 0,7 5 0,2-1 0,152 108 0,-163-115 0,0 0 0,0 0 0,1 0 0,-1 0 0,0-1 0,-1 1 0,2-1 0,0 1 0,-1-1 0,1 0 0,-1 0 0,0 0 0,0 0 0,1 0 0,-1 0 0,0 0 0,0-1 0,1 1 0,-1-1 0,0 1 0,1-1 0,-1 0 0,0 0 0,-1 0 0,2 0 0,-1 1 0,0-1 0,-1-1 0,1 1 0,0 0 0,0-1 0,1-2 0,11-7 0,0 0 0,21-25 0,-27 26 0,75-83 0,54-55 0,-119 133-1365,-4 6-5461</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -10924,7 +9796,7 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 170 24575,'2'1'0,"0"-1"0,0 1 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,-1 0 0,1 0 0,-1 0 0,1 1 0,-1-1 0,0 1 0,1-1 0,-1 1 0,0 0 0,1 1 0,20 35 0,-19-33 0,9 20 0,-8-16 0,0 0 0,1-1 0,0 1 0,0-1 0,12 14 0,-15-21 0,-1 1 0,1-1 0,0 1 0,0-1 0,0 0 0,0 1 0,1-1 0,-1 0 0,0 0 0,0-1 0,1 1 0,-1 0 0,0-1 0,1 1 0,-1-1 0,0 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,0-1 0,1 1 0,-1-1 0,1 1 0,-1-1 0,0 0 0,0 0 0,4-2 0,38-21 0,-2-2 0,65-51 0,-3 1 0,74-45-1365,-164 111-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 170 24575,'2'1'0,"0"-1"0,1 1 0,-1 0 0,0 0 0,-1 0 0,2 0 0,-1 0 0,-1 0 0,1 0 0,-1 0 0,1 1 0,0-1 0,-1 1 0,1-1 0,-1 1 0,0 0 0,1 1 0,23 35 0,-22-33 0,11 20 0,-10-16 0,1 0 0,0-1 0,1 1 0,-1-1 0,14 14 0,-16-21 0,-2 1 0,1-1 0,0 1 0,0-1 0,1 0 0,-1 1 0,1-1 0,-1 0 0,1 0 0,-1-1 0,1 1 0,-1 0 0,1-1 0,0 1 0,-1-1 0,0 0 0,2 0 0,-2 0 0,1 0 0,0 0 0,-1-1 0,1 1 0,-1-1 0,2 1 0,-2-1 0,0 0 0,0 0 0,5-2 0,42-21 0,-2-2 0,73-51 0,-4 1 0,82-45-1365,-182 111-5461</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -10952,7 +9824,7 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 44 24575,'5'2'0,"-1"1"0,1-1 0,-1 1 0,0 0 0,0 0 0,0 0 0,0 1 0,0-1 0,-1 1 0,1 0 0,-1 0 0,0 1 0,3 4 0,-1-1 0,24 34 0,-20-28 0,0 0 0,1-1 0,11 12 0,-19-24 0,-1 0 0,1 0 0,-1 0 0,1-1 0,0 1 0,-1 0 0,1-1 0,0 1 0,-1-1 0,1 0 0,0 1 0,0-1 0,-1 0 0,1 0 0,0 0 0,0 0 0,0-1 0,-1 1 0,1 0 0,0-1 0,0 1 0,-1-1 0,1 1 0,0-1 0,-1 0 0,3-1 0,43-30 0,-43 30 0,41-36-455,-2-1 0,40-48 0,-70 73-6371</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 44 24575,'6'2'0,"-1"1"0,1-1 0,-2 1 0,1 0 0,0 0 0,-1 0 0,1 1 0,0-1 0,-2 1 0,2 0 0,-1 0 0,-1 1 0,4 4 0,-1-1 0,29 34 0,-25-28 0,1 0 0,1-1 0,12 12 0,-21-24 0,-2 0 0,1 0 0,0 0 0,0-1 0,0 1 0,-1 0 0,2-1 0,-1 1 0,-1-1 0,2 0 0,-1 1 0,0-1 0,0 0 0,0 0 0,0 0 0,1 0 0,-1-1 0,-1 1 0,2 0 0,-1-1 0,0 1 0,0-1 0,0 1 0,0-1 0,-1 0 0,4-1 0,51-30 0,-52 30 0,50-36-455,-4-1 0,48-48 0,-82 73-6371</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -10980,7 +9852,7 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 135 24575,'1'5'0,"0"0"0,0-1 0,0 1 0,0-1 0,1 1 0,0-1 0,0 1 0,0-1 0,0 0 0,1 0 0,5 7 0,38 41 0,-40-46 0,-3-2 0,0-1 0,1 1 0,-1-1 0,1 0 0,0 0 0,0-1 0,0 1 0,0-1 0,0 0 0,1 0 0,-1 0 0,1 0 0,0-1 0,9 2 0,-10-3 0,0 0 0,0-1 0,0 1 0,0-1 0,0 0 0,0 0 0,0-1 0,0 1 0,0-1 0,0 1 0,-1-1 0,1-1 0,-1 1 0,1 0 0,-1-1 0,0 0 0,0 1 0,3-5 0,88-97 0,28-28 0,-95 114-1365,-17 14-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 135 24575,'1'5'0,"0"0"0,0-1 0,1 1 0,-1-1 0,1 1 0,0-1 0,1 1 0,-1-1 0,0 0 0,2 0 0,5 7 0,45 41 0,-47-46 0,-4-2 0,1-1 0,0 1 0,0-1 0,0 0 0,1 0 0,0-1 0,-1 1 0,1-1 0,0 0 0,0 0 0,0 0 0,1 0 0,0-1 0,10 2 0,-11-3 0,-1 0 0,1-1 0,0 1 0,-1-1 0,1 0 0,0 0 0,-1-1 0,1 1 0,-1-1 0,1 1 0,-1-1 0,0-1 0,0 1 0,0 0 0,0-1 0,-1 0 0,1 1 0,3-5 0,102-97 0,33-28 0,-111 114-1365,-19 14-5461</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -11008,7 +9880,7 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 326 24575,'1'0'0,"0"0"0,0 0 0,0 1 0,0-1 0,0 0 0,0 1 0,0-1 0,0 1 0,-1-1 0,1 1 0,0-1 0,0 1 0,0-1 0,0 1 0,-1 0 0,1 0 0,0-1 0,-1 1 0,1 0 0,-1 0 0,1 0 0,-1 0 0,1 1 0,11 31 0,-11-29 0,0-1 0,0 1 0,1 0 0,-1-1 0,1 1 0,-1-1 0,1 0 0,3 4 0,-4-5 0,1-1 0,-1 0 0,0 0 0,1 0 0,0 0 0,-1 0 0,1 0 0,0-1 0,-1 1 0,1-1 0,0 1 0,0-1 0,-1 1 0,1-1 0,0 0 0,0 0 0,0 0 0,0 0 0,-1 0 0,4-1 0,-1 0 0,0 0 0,0 0 0,0-1 0,-1 0 0,1 0 0,-1 0 0,1 0 0,-1-1 0,3-2 0,8-7 0,-2-1 0,0 0 0,13-20 0,-20 27 0,57-84-682,64-126-1,-117 201-6143</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 308 24575,'1'0'0,"0"0"0,1 0 0,-1 1 0,0-1 0,0 0 0,0 1 0,1-1 0,-1 1 0,-1-1 0,1 1 0,0-1 0,0 1 0,1-1 0,-1 1 0,-1 0 0,1 0 0,0-1 0,-1 1 0,1 0 0,-1 0 0,2 0 0,-2 0 0,1 0 0,13 31 0,-13-29 0,1 0 0,-1 1 0,1 0 0,-1-1 0,2 0 0,-2 0 0,1 0 0,4 4 0,-5-5 0,2-1 0,-2-1 0,0 1 0,2 0 0,-1 0 0,-1 0 0,2 0 0,-1-1 0,-1 1 0,2-1 0,-1 1 0,0-1 0,0 1 0,0-1 0,0 0 0,1 0 0,-1 0 0,1 0 0,-2 0 0,5-1 0,-1 0 0,-1 0 0,1 0 0,0-1 0,-1 0 0,0 1 0,0-1 0,1 0 0,-2-1 0,4-2 0,10-6 0,-2-1 0,-1-1 0,16-18 0,-24 25 0,68-79-682,77-119-1,-140 190-6143</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -11036,7 +9908,7 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 380 24575,'2'0'0,"1"1"0,-1 0 0,1 0 0,-1 0 0,0 0 0,0 0 0,1 0 0,-1 1 0,0-1 0,0 1 0,0-1 0,0 1 0,-1 0 0,1-1 0,0 1 0,-1 0 0,3 4 0,24 40 0,-24-39 0,9 20 0,-9-20 0,0 1 0,0 0 0,0-1 0,1 1 0,0-1 0,0-1 0,8 9 0,-12-14 0,0-1 0,-1 0 0,1 1 0,0-1 0,0 0 0,0 0 0,-1 1 0,1-1 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0-1 0,0 1 0,0 0 0,0 0 0,-1-1 0,1 1 0,0 0 0,0-1 0,-1 1 0,1-1 0,0 1 0,-1-1 0,1 1 0,0-1 0,24-23 0,-18 16 0,500-472-1365,-470 442-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 364 24575,'2'0'0,"2"1"0,-2 0 0,1 0 0,-1-1 0,0 1 0,1 0 0,0 0 0,-1 1 0,0-1 0,1 1 0,-1-1 0,0 1 0,-1 0 0,1-1 0,1 1 0,-2 0 0,3 3 0,27 39 0,-27-37 0,11 19 0,-11-19 0,1 0 0,-1 1 0,1-1 0,0 0 0,1 0 0,-1-1 0,10 8 0,-14-13 0,0-1 0,-1 0 0,1 1 0,0-1 0,0 0 0,0 0 0,-1 1 0,1-1 0,0 0 0,0 0 0,1 0 0,-1 0 0,0 0 0,-1 0 0,1 0 0,0-1 0,0 1 0,0 0 0,0 0 0,-1-1 0,1 1 0,1 0 0,-1-1 0,-1 1 0,1-1 0,0 1 0,-1-1 0,1 1 0,0-1 0,27-22 0,-21 16 0,554-453-1365,-520 424-5461</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -11064,7 +9936,7 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 319 24575,'0'9'0,"1"1"0,1-1 0,0 1 0,0-1 0,1 1 0,0-1 0,1 0 0,-1 0 0,7 8 0,-8-12 0,1 1 0,0-1 0,1-1 0,-1 1 0,1 0 0,0-1 0,0 0 0,0 0 0,1 0 0,-1 0 0,1-1 0,0 0 0,0 0 0,0 0 0,0 0 0,7 1 0,-8-3 0,0-1 0,0 0 0,0 0 0,0 0 0,0 0 0,0-1 0,-1 1 0,1-1 0,0 0 0,0-1 0,0 1 0,-1 0 0,1-1 0,-1 0 0,1 0 0,5-5 0,54-47 0,-47 39 0,79-73-455,-5-3 0,83-110 0,-158 181-6371</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 303 24575,'0'9'0,"1"0"0,1 0 0,1 1 0,-1-2 0,1 2 0,1-2 0,0 1 0,-1-1 0,9 8 0,-10-11 0,1 1 0,1-1 0,0-2 0,-1 2 0,2 0 0,-1-1 0,1 0 0,-1-1 0,2 1 0,-1 0 0,0-1 0,1 0 0,-1 0 0,1-1 0,0 1 0,7 1 0,-8-3 0,-1-1 0,1 0 0,-1 0 0,1 0 0,-1 0 0,1-1 0,-2 1 0,1-1 0,1 0 0,-1-1 0,1 1 0,-2 0 0,2-1 0,-2 1 0,2-1 0,5-5 0,60-44 0,-52 36 0,89-68-455,-6-4 0,93-104 0,-177 172-6371</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -11092,7 +9964,7 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 348 24575,'2'0'0,"1"1"0,-1-1 0,1 1 0,0 0 0,-1 0 0,0 0 0,1 0 0,-1 0 0,1 1 0,-1-1 0,0 1 0,0-1 0,0 1 0,3 4 0,30 34 0,-18-18 0,-15-20 0,1 1 0,-1 0 0,0-1 0,1 0 0,-1 1 0,1-1 0,0 0 0,0 0 0,0-1 0,0 1 0,0-1 0,0 1 0,0-1 0,0 0 0,1 0 0,-1 0 0,0-1 0,1 1 0,-1-1 0,1 0 0,-1 0 0,1 0 0,-1 0 0,0 0 0,1-1 0,-1 0 0,0 0 0,1 0 0,-1 0 0,0 0 0,0 0 0,0-1 0,0 0 0,3-2 0,286-174 0,-260 157 0,28-18-341,-1-4 0,-3-1-1,52-53 1,-85 71-6485</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 330 24575,'2'0'0,"1"1"0,0-1 0,0 1 0,0 0 0,-1 0 0,1 0 0,0 0 0,-1 0 0,1 1 0,0-2 0,-1 2 0,0-1 0,0 1 0,4 4 0,32 32 0,-20-17 0,-15-19 0,0 0 0,-1 1 0,0-1 0,2 0 0,-2 1 0,1-1 0,0 0 0,1 0 0,-1-1 0,0 0 0,0 0 0,1 1 0,-1-1 0,0 0 0,2 0 0,-2 0 0,0-1 0,2 1 0,-2-1 0,1 0 0,0 0 0,0 0 0,-1 0 0,0 0 0,2-1 0,-2 0 0,0 0 0,2 0 0,-2 0 0,0 0 0,1 0 0,-1 0 0,0-1 0,4-2 0,312-165 0,-284 149 0,31-17-341,-2-4 0,-2 0-1,56-51 1,-93 67-6485</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -11112,15 +9984,16 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:13:42.645"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:20:49.507"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.1" units="cm"/>
-      <inkml:brushProperty name="height" value="0.1" units="cm"/>
-      <inkml:brushProperty name="color" value="#008C3A"/>
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 127 9830,'1'9'258,"0"0"-1,1 0 1,0 0-1,0-1 1,1 1-1,0-1 1,0 1 0,6 9-1,40 60 895,-48-76-1126,1 0 0,-1 0 0,0 0 0,1-1 0,-1 1 0,1 0 0,-1-1 0,1 1 0,0-1 0,-1 1 0,1-1 0,0 0 0,0 0 0,0 0 0,0 0-1,0 0 1,1 0 0,-1 0 0,0-1 0,0 1 0,0-1 0,1 0 0,-1 0 0,0 1 0,0-1 0,1-1 0,-1 1 0,0 0 0,0-1 0,1 1 0,-1-1 0,0 1 0,0-1 0,0 0 0,0 0 0,0 0 0,0 0 0,0-1 0,0 1-1,0 0 1,0-1 0,-1 1 0,1-1 0,1-2 0,9-9-139,-1 0 0,0-1 0,-1 0 0,13-26 0,-17 30 85,28-56-149,-25 44 146,2 1 0,1 1 1,26-37-1,-28 46 67</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 22 24575,'1'-1'0,"-1"0"0,1 0 0,-1 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,1 0 0,1 0 0,-1 0 0,-1 1 0,1-1 0,0 0 0,0 1 0,0-1 0,0 1 0,0 0 0,0 0 0,0-1 0,0 1 0,1-1 0,-1 1 0,0 0 0,0 0 0,0-1 0,0 1 0,2 0 0,41-3 0,-39 3 0,9-1 0,1 1 0,-1 0 0,0 1 0,0 1 0,0 0 0,-1 0 0,1 1 0,0 0 0,23 10 0,-31-10 0,1 0 0,-2 0 0,1 0 0,0 1 0,0 0 0,-2 1 0,1-2 0,0 2 0,-1 0 0,0-1 0,1 1 0,-1 1 0,-1-2 0,1 2 0,-1 0 0,-1-1 0,0 1 0,0-1 0,1 2 0,-2-1 0,2 10 0,-2-6 0,0-1 0,-1 2 0,0-2 0,-1 1 0,0 1 0,0-2 0,-1 1 0,-2 0 0,1-1 0,0 0 0,-1 1 0,-1-1 0,0-1 0,-1 2 0,1-2 0,-2 1 0,1-2 0,-2 2 0,1-2 0,-1 0 0,-1 0 0,0 0 0,1-1 0,-2 0 0,-11 5 0,18-9 0,0 0 0,-2 0 0,2 1 0,0-2 0,1 2 0,-2-1 0,1 1 0,1 0 0,0 0 0,-1-1 0,0 1 0,1 1 0,1-1 0,-1 0 0,0 0 0,1 0 0,0 1 0,-2 4 0,3-5 0,0 0 0,1-1 0,-1 1 0,2-1 0,-1 0 0,0 1 0,0 0 0,0-1 0,0 1 0,0-2 0,1 1 0,-1 0 0,2 1 0,-1-1 0,0 0 0,0 0 0,0-1 0,0 0 0,1 1 0,-1 0 0,0-1 0,1 1 0,-1-1 0,2 0 0,-2 0 0,5 1 0,4 2 24,1 0 0,0 0 0,0-1 0,24 3 0,-32-6-89,-1 1 1,0-1-1,0 1 1,1-1-1,-1 0 1,0-1-1,0 1 0,1 0 1,0-1-1,-1 1 1,-1-1-1,2 0 1,-1 0-1,0 0 1,1 0-1,-1 0 0,-1-1 1,1 0-1,-1 1 1,2-1-1,-2 0 1,4-3-1,6-13-6761</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1139.62">674 22 24575,'-1'-1'0,"-1"1"0,1 0 0,-1 0 0,1 0 0,-1 0 0,0 1 0,0-1 0,1 0 0,0 1 0,-1-1 0,1 0 0,0 0 0,-1 1 0,0 0 0,1-1 0,-1 1 0,1 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,-1 0 0,1 1 0,1-1 0,-1-1 0,0 2 0,1-1 0,-1 0 0,1 1 0,0-1 0,-1 1 0,1-1 0,0 1 0,0-1 0,0 1 0,0-2 0,0 1 0,0 1 0,0-1 0,1 1 0,-1-1 0,0 1 0,1-1 0,-1 0 0,2 3 0,2 5 0,0 1 0,0 0 0,2-1 0,11 18 0,-6-12 0,-1 1 0,-1-1 0,-2 2 0,1-1 0,-3 1 0,2-1 0,-3 1 0,-1 0 0,3 27 0,-6-40 3,0-1 0,-1 1 0,0-2 1,0 2-1,0-1 0,-1 1 0,1-2 0,-1 1 0,1 0 0,-1 0 0,0 0 0,0-1 0,-1 1 0,1 0 0,-1 0 0,1-1 1,-2 1-1,1-2 0,1 1 0,-1 0 0,0 0 0,-6 2 0,-9 4-127,1-1 0,-2-1-1,-22 8 1,12-6-815,13-3-5887</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -11140,15 +10013,15 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:13:58.192"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:21:04.122"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.1" units="cm"/>
-      <inkml:brushProperty name="height" value="0.1" units="cm"/>
-      <inkml:brushProperty name="color" value="#008C3A"/>
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 261 9830,'6'4'209,"0"1"0,0-1 0,0 1-1,-1 0 1,0 0 0,0 1 0,0 0 0,0 0 0,3 6-1,-4-5-91,1 0 0,0-1-1,0 0 1,1 1-1,0-2 1,0 1 0,10 7-1,-12-11-62,0 0-1,0-1 1,0 1-1,0-1 1,0 0-1,0 0 1,1 0-1,-1 0 1,0-1-1,1 1 1,-1-1-1,0 0 1,1-1-1,-1 1 1,0-1-1,0 0 1,1 0-1,-1 0 1,0-1-1,0 1 1,0-1-1,0 0 1,-1 0-1,1 0 0,0-1 1,6-5-1,6-6-122,0-1 0,-1-1 0,0 0 0,13-21 0,-11 15-122,155-200-625,-157 203 797</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">162 1 24575,'-2'3'0,"1"1"0,-2-2 0,1 1 0,-1 0 0,1 0 0,-1 0 0,-1 0 0,2-1 0,-2 0 0,0 1 0,-5 2 0,-8 8 0,12-8 0,-10 8 0,-1 0 0,4 2 0,-2 0 0,-14 22 0,26-31 0,-2 1 0,1-1 0,2 1 0,-1 0 0,0-2 0,2 2 0,-1 0 0,1 0 0,0 0 0,1-1 0,-1 1 0,2 0 0,0-2 0,-1 2 0,7 8 0,1 5 0,1-1 0,16 21 0,-23-35 0,1-1 0,-2 1 0,2-2 0,0 1 0,-1 0 0,1 0 0,1 0 0,-1-1 0,1 0 0,0 1 0,0-1 0,0 0 0,0-2 0,2 2 0,6 2 0,-9-5 0,0 0 0,1 0 0,-1 0 0,0-1 0,1 0 0,-2 0 0,1 0 0,0 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0-1 0,0 0 0,0 0 0,-2 0 0,2-1 0,-2 1 0,2 0 0,-1 0 0,3-6 0,8-4 0,-3-1 0,1 0 0,9-15 0,-5 4 0,0 1 0,-4-2 0,15-34 0,-25 53 0,-1-1 0,2 1 0,-2-1 0,0 0 0,-1 1 0,2-1 0,-4 0 0,2 1 0,-1-1 0,0 1 0,0-1 0,-2 0 0,1 1 0,-1-1 0,-1 1 0,2 0 0,-2 0 0,-10-11 0,10 14-65,1 0 0,-2 1 0,1-1 0,-1 0 0,0 1 0,0-1 0,0 1 0,0 0 0,-1 1 0,1-1 0,0 1 0,-1 0 0,1 0 0,-1 0 0,1 0 0,-2 1 0,2-1 0,-1 1 0,0 0 0,-7 1 0,-11 3-6761</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -11176,376 +10049,11 @@
       <inkml:brushProperty name="color" value="#33CCFF"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 82 24575,'3'1'0,"1"1"0,-1 1 0,-1-1 0,2 0 0,-2 1 0,1 0 0,0-1 0,-1 1 0,1 0 0,3 7 0,4 2 0,-3-4 0,2 0 0,-2-1 0,2 0 0,-1-1 0,1-1 0,0 1 0,11 3 0,-16-7 0,0 0 0,0 0 0,1-1 0,-1 0 0,1 0 0,-1-1 0,1 1 0,-1-1 0,1 0 0,-1-1 0,1 1 0,-1-1 0,1 0 0,-1-1 0,0 1 0,0-1 0,8-5 0,-10 7 0,0-1 0,-1 0 0,1 0 0,-1 0 0,0-1 0,0 1 0,1 0 0,-1-1 0,0 1 0,0-1 0,0 1 0,1-1 0,-2 1 0,1-1 0,0 0 0,0 0 0,0 0 0,-1 1 0,1-1 0,-1 0 0,0 0 0,0 0 0,1 0 0,-1 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,-1 0 0,0 0 0,0 1 0,0-1 0,1 0 0,-1 0 0,-1 1 0,1-1 0,-2-1 0,-5-8 0,-1 0 0,-1 1 0,0 0 0,-17-13 0,20 17 0,2 2-136,0 0-1,-1 0 1,1 1-1,0 0 1,-1 1-1,0 0 1,1 0-1,-1 0 0,-9-1 1,-2 1-6690</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 82 24575,'4'1'0,"0"1"0,0 1 0,-2-1 0,3 0 0,-3 1 0,2 0 0,0-1 0,-2 1 0,2 0 0,3 7 0,5 2 0,-4-4 0,3 0 0,-3-1 0,3 0 0,-2-1 0,2-1 0,0 1 0,13 3 0,-20-7 0,1 0 0,0 0 0,1-1 0,-1 0 0,1 0 0,-2-1 0,2 1 0,-1-1 0,1 0 0,-1-1 0,1 1 0,-1-1 0,1 0 0,-2-1 0,1 1 0,0-1 0,9-5 0,-11 7 0,-1-1 0,-1 0 0,2 0 0,-2 0 0,0-1 0,0 1 0,2 0 0,-2-1 0,0 1 0,0-1 0,0 1 0,2-1 0,-3 1 0,1-1 0,0 0 0,0 0 0,0 0 0,-1 1 0,2-1 0,-2 0 0,0 0 0,0 0 0,1 0 0,-1 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,-2 0 0,2 0 0,-1 0 0,0 0 0,0 1 0,0-1 0,1 0 0,-2 0 0,0 1 0,1-1 0,-3-1 0,-5-8 0,-2 0 0,-1 1 0,0 0 0,-20-13 0,24 17 0,2 2-136,0 0-1,-1 0 1,1 1-1,0 0 1,-1 1-1,-1 0 1,2 0-1,-1 0 0,-11-1 1,-2 1-6690</inkml:trace>
 </inkml:ink>
 </file>
 
 <file path=xl/ink/ink60.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:14:02.327"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.1" units="cm"/>
-      <inkml:brushProperty name="height" value="0.1" units="cm"/>
-      <inkml:brushProperty name="color" value="#008C3A"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 145 9830,'3'1'113,"-1"0"0,1 0-1,-1 1 1,0-1 0,0 1 0,1-1-1,-1 1 1,0 0 0,-1 0 0,1 0-1,0 0 1,0 0 0,-1 1 0,3 3 0,1 2 87,24 32 469,28 34 375,-52-68-947,1 0 0,-1 0 0,1-1 0,0 0-1,1 0 1,-1-1 0,1 0 0,0 0 0,8 3 0,-11-6-23,0 0 0,0 0 0,0-1 0,0 0 0,0 1 0,0-2 1,0 1-1,0 0 0,0-1 0,0 1 0,0-1 0,0 0 0,-1-1 1,1 1-1,0-1 0,6-3 0,6-4-203,-1-1 0,20-16-1,-25 18 63,300-248-1543,-279 227 1593</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink61.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:14:03.370"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.1" units="cm"/>
-      <inkml:brushProperty name="height" value="0.1" units="cm"/>
-      <inkml:brushProperty name="color" value="#008C3A"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 256 9830,'19'0'1365,"26"0"274,22-4-513,17-8 344,19-9-2149,14-9 88,2-6 174,-5-1 32,-7-1-32,-15 5 230,-19 9 411,-19 9 1,-18 10-1,-19 13 278,-12 5-502</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink62.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:14:04.265"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.1" units="cm"/>
-      <inkml:brushProperty name="height" value="0.1" units="cm"/>
-      <inkml:brushProperty name="color" value="#008C3A"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 400 9830,'4'0'273,"8"-3"338,6-6-632,7 0 538,7-3-568,12-6-52,16-8-21,18-7 0,8-4 21,9-4-21,-1-5 27,1-3-27,-8 8 78,-15 6 13,-13 10 565,-16 9-532</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink63.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:14:15.317"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.1" units="cm"/>
-      <inkml:brushProperty name="height" value="0.1" units="cm"/>
-      <inkml:brushProperty name="color" value="#008C3A"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 79 9830,'0'8'138,"0"-1"-1,0 0 1,0 1 0,1-1-1,0 1 1,0-1 0,1 0-1,0 0 1,1 0 0,-1 0-1,1 0 1,1 0 0,-1-1 0,1 1-1,0-1 1,1 0 0,-1 0-1,1 0 1,0-1 0,1 0-1,-1 0 1,1 0 0,0-1-1,0 0 1,1 0 0,-1 0-1,1-1 1,0 0 0,-1 0-1,2-1 1,11 3 0,-3 0 76,1-2 1,-1 0-1,1-1 1,30 0-1,-39-2-48,0 0 0,0-1 0,0 0-1,0-1 1,-1 0 0,1 0 0,-1 0-1,1-1 1,-1 0 0,0-1 0,0 0 0,9-6-1,34-33-741,65-71-1,-47 44 498,-52 54 107</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink64.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:14:16.244"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.1" units="cm"/>
-      <inkml:brushProperty name="height" value="0.1" units="cm"/>
-      <inkml:brushProperty name="color" value="#008C3A"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 678 9830,'3'0'273,"9"-7"499,17-21-883,22-24-12,23-20-13,14-17 24,7-8 14,-6 6 48,-11 14 11,-15 13 0,-14 18 22,-12 13-8,-13 12 25</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink65.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:14:24.969"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.1" units="cm"/>
-      <inkml:brushProperty name="height" value="0.1" units="cm"/>
-      <inkml:brushProperty name="color" value="#008C3A"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 321 9830,'0'4'192,"1"1"1,0-1-1,0 0 0,0 0 0,1 1 1,-1-1-1,1 0 0,0 0 1,0 0-1,6 6 0,31 40 606,-24-33-455,-8-8-346,-1-2 136,-1 1 0,2-1 0,-1 0 0,1-1 0,0 1 0,10 6 0,-14-12-112,-1 0 1,1 0 0,0 0-1,0 0 1,0 0 0,0 0-1,0-1 1,0 1 0,0-1 0,0 0-1,0 0 1,0 0 0,0 0-1,0 0 1,0-1 0,0 0-1,-1 1 1,1-1 0,0 0 0,0 0-1,0-1 1,-1 1 0,1 0-1,2-3 1,23-16-256,0-1 1,-2-1-1,0-1 1,27-33-1,-20 21-9,234-255-748,-243 258 977</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink66.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:14:27.320"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.1" units="cm"/>
-      <inkml:brushProperty name="height" value="0.1" units="cm"/>
-      <inkml:brushProperty name="color" value="#008C3A"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 220 9830,'0'-4'0,"7"-4"0,14-9 0,10-4 0,14-7 0,11-2 0,6 1 0,-3 2 0,-8 4 0,-10 8 273,-7 5 0,-7 5 0,-7 3-273</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink67.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:14:33.273"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.1" units="cm"/>
-      <inkml:brushProperty name="height" value="0.1" units="cm"/>
-      <inkml:brushProperty name="color" value="#008C3A"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 492 9830,'134'66'2700,"-130"-64"-2621,0 0 1,0-1 0,0 0 0,0 1 0,1-2-1,-1 1 1,0 0 0,0-1 0,1 0-1,-1 0 1,0 0 0,1-1 0,-1 1 0,0-1-1,1 0 1,-1 0 0,0 0 0,4-3 0,8-3-135,-1-1-1,-1-1 1,20-14 0,-18 12-164,358-259-1627,-134 95 1363,-192 142 637,-13 11-112</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink68.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:14:34.303"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.1" units="cm"/>
-      <inkml:brushProperty name="height" value="0.1" units="cm"/>
-      <inkml:brushProperty name="color" value="#008C3A"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 329 9830,'7'-4'0,"17"-11"0,16-15 0,14-17 0,10-3 0,2-1 0,-8 4 0,-10 11 0,-9 7 0,-11 10 0</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink69.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:16:48.780"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.1" units="cm"/>
-      <inkml:brushProperty name="height" value="0.1" units="cm"/>
-      <inkml:brushProperty name="color" value="#008C3A"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 468 9830,'4'0'273,"4"0"0,1 4 0,7 4 338,4 5-225,2 0-113,1-2 0,7-10 712,14-13 236,20-18-1770,18-20 61,10-18 1,-5-5 272,-8-2-60,-15 5 105,-18 11 94,-14 12-32,-11 14 108</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink7.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-10T09:08:40.035"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.035" units="cm"/>
-      <inkml:brushProperty name="height" value="0.035" units="cm"/>
-      <inkml:brushProperty name="color" value="#33CCFF"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 0 24575,'3'0'0,"4"0"0,0 5 0,0 5 0,1 6 0,2 1 0,2 5 0,2 5 0,-1 1 0,0-4 0,-3-1 0,-2 0 0,0-4 0,-1-1 0,0-4 0,0-3-8191</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink70.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:20:49.507"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.035" units="cm"/>
-      <inkml:brushProperty name="height" value="0.035" units="cm"/>
-      <inkml:brushProperty name="color" value="#E71224"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 23 24575,'1'-1'0,"-1"0"0,1 0 0,-1 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,-1 1 0,1-1 0,0 0 0,0 1 0,0-1 0,0 1 0,0-1 0,0 1 0,0-1 0,0 1 0,0-1 0,0 1 0,0 0 0,0 0 0,0-1 0,0 1 0,2 0 0,37-3 0,-35 3 0,8-1 0,0 1 0,0 0 0,0 1 0,0 1 0,0 0 0,-1 0 0,1 2 0,-1-1 0,22 11 0,-28-11 0,0 0 0,-1 0 0,0 1 0,1 0 0,-1 0 0,-1 1 0,1-1 0,-1 1 0,0 0 0,0 0 0,0 0 0,0 1 0,-1-1 0,0 1 0,0 0 0,-1 0 0,0 0 0,0 0 0,0 1 0,-1-1 0,2 11 0,-2-6 0,0-1 0,-1 1 0,0-1 0,-1 1 0,0 0 0,0-1 0,-1 1 0,-1-1 0,0 0 0,0 0 0,-1 0 0,0 0 0,-1-1 0,0 1 0,0-1 0,-1 0 0,0-1 0,-1 1 0,0-1 0,0-1 0,-1 1 0,0-1 0,0 0 0,-1-1 0,-10 6 0,16-10 0,0 0 0,-1 0 0,1 1 0,0-1 0,1 1 0,-1-1 0,0 1 0,1 0 0,0 0 0,-1 0 0,1 0 0,0 1 0,1-1 0,-1 0 0,0 1 0,1-1 0,0 1 0,-1 5 0,2-6 0,0 0 0,1-1 0,-1 1 0,1 0 0,0-1 0,0 1 0,0 0 0,0-1 0,0 1 0,0-1 0,1 0 0,-1 0 0,1 1 0,0-1 0,0 0 0,0 0 0,0 0 0,0-1 0,0 1 0,0 0 0,0-1 0,1 1 0,-1-1 0,1 0 0,-1 0 0,5 1 0,3 3 24,1-1 0,0 0 0,0-1 0,22 4 0,-30-7-89,0 1 1,0-1-1,0 1 1,0-1-1,0 0 1,0-1-1,0 1 0,0 0 1,1-1-1,-1 1 1,-1-1-1,1 0 1,0 0-1,0-1 1,0 1-1,0 0 0,-1-1 1,1 0-1,-1 1 1,1-1-1,-1 0 1,4-4-1,5-13-6761</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1139.63">619 23 24575,'-1'-1'0,"-1"1"0,1 0 0,-1 0 0,1 0 0,-1 0 0,1 1 0,-1-1 0,1 0 0,0 1 0,-1-1 0,1 1 0,0-1 0,-1 1 0,1 0 0,0-1 0,-1 1 0,1 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 1 0,1-1 0,-1 0 0,0 1 0,1-1 0,-1 0 0,1 1 0,0-1 0,-1 1 0,1-1 0,0 1 0,0-1 0,0 1 0,0-1 0,0 0 0,0 1 0,0-1 0,1 1 0,-1-1 0,0 1 0,1-1 0,-1 0 0,2 3 0,1 6 0,1 1 0,0-1 0,1 0 0,11 19 0,-6-13 0,-1 1 0,-1-1 0,-1 2 0,0-1 0,-2 1 0,1 0 0,-2 0 0,-1 0 0,2 29 0,-5-43 3,0-1 0,-1 1 0,0-1 1,0 1-1,0-1 0,0 1 0,0-1 0,-1 0 0,1 0 0,-1 0 0,0 0 0,0 0 0,0 0 0,0 0 0,-1 0 0,1-1 1,-1 1-1,0-1 0,1 0 0,-1 0 0,0 0 0,-5 2 0,-8 5-127,0-2 0,-1 0-1,-21 7 1,11-5-815,13-4-5887</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink71.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:21:04.122"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.035" units="cm"/>
-      <inkml:brushProperty name="height" value="0.035" units="cm"/>
-      <inkml:brushProperty name="color" value="#E71224"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">129 1 24575,'-2'3'0,"1"1"0,-1-1 0,0 0 0,0 0 0,0 0 0,0 0 0,-1 0 0,1-1 0,-1 1 0,0 0 0,-4 2 0,-7 9 0,10-9 0,-8 9 0,0 0 0,2 1 0,-1 1 0,-11 24 0,20-34 0,-1 1 0,1 0 0,1 0 0,-1 0 0,1-1 0,1 1 0,-1 1 0,1-1 0,0 0 0,1 0 0,-1 0 0,1 0 0,1-1 0,-1 1 0,5 9 0,1 5 0,1-1 0,13 23 0,-19-38 0,1-1 0,-1 1 0,1-1 0,0 0 0,0 0 0,0 0 0,1 0 0,-1 0 0,1-1 0,0 1 0,0-1 0,0 0 0,0-1 0,1 1 0,6 2 0,-8-5 0,0 0 0,1 0 0,-1 0 0,0-1 0,1 0 0,-1 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0-1 0,0 1 0,0-1 0,0 0 0,0 0 0,-1 0 0,1-1 0,-1 1 0,1 0 0,-1-1 0,3-5 0,6-5 0,-2 0 0,0-1 0,8-16 0,-4 5 0,-1 0 0,-2-1 0,11-36 0,-19 55 0,-1 0 0,1 0 0,-1 0 0,0 0 0,-1 0 0,1 0 0,-2 0 0,1 0 0,-1 0 0,0 0 0,0 0 0,-1 0 0,0 0 0,0 0 0,-1 1 0,1-1 0,-1 1 0,-8-12 0,8 15-65,0 0 0,-1 0 0,1 0 0,-1 0 0,0 1 0,0-1 0,0 1 0,0 0 0,0 0 0,0 0 0,0 1 0,-1 0 0,1 0 0,-1 0 0,1 0 0,-1 1 0,1-1 0,-1 1 0,0 0 0,-5 1 0,-9 3-6761</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink72.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -11569,12 +10077,12 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">50 185 24575,'7'-1'0,"1"-2"0,-1 1 0,0-1 0,0 0 0,0 0 0,8-6 0,0 0 0,10-3 0,75-40 0,-90 46 0,1-1 0,-1 0 0,0-1 0,-1 0 0,0-1 0,12-14 0,-15 15 0,-3 4 0,-4 6 0,-12 30 0,-13 73 0,-18 160 0,40-221 0,4-32 0,0 0 0,-1 0 0,-1 0 0,0 0 0,0 0 0,-1-1 0,-1 1 0,-9 21 0,11-31 0,-1 1 0,1-1 0,0 0 0,-1 1 0,1-1 0,-1 0 0,0-1 0,1 1 0,-1 0 0,0-1 0,0 0 0,0 0 0,0 1 0,0-2 0,0 1 0,-1 0 0,1-1 0,0 1 0,0-1 0,-1 0 0,-4-1 0,1 1 0,1 0 0,-1-1 0,1 0 0,-1-1 0,1 1 0,0-1 0,0 0 0,0-1 0,-12-6 0,18 9 0,0 0 0,-1 0 0,1 0 0,0 0 0,-1 0 0,1-1 0,0 1 0,-1 0 0,1 0 0,0-1 0,-1 1 0,1 0 0,0 0 0,0-1 0,-1 1 0,1 0 0,0-1 0,0 1 0,-1 0 0,1-1 0,0 1 0,0-1 0,0 1 0,0 0 0,0-1 0,0 1 0,0 0 0,0-1 0,0 1 0,0-1 0,0 1 0,0 0 0,0-1 0,0 1 0,0-1 0,0 1 0,0-1 0,16-8 0,28 0 0,-41 8 0,208-25 0,-166 15 0,9 0 0,-50 14 0,-13 2 0,-17 3 0,-96 2-3,74-7-451,0 1 0,-93 21 0,123-19-6372</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="794.38">0 185 24575,'4'0'0,"6"0"0,5 0 0,5-4 0,-2-6 0,6-1 0,-3-3 0,-3-3 0,2-3 0,3-3 0,1-1 0,-2-1 0,-2 4 0,-4 5-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">58 178 24575,'8'-1'0,"2"-2"0,-2 1 0,0-1 0,0 0 0,0 0 0,10-5 0,-1-1 0,13-2 0,86-39 0,-104 44 0,1-1 0,-2 0 0,1 0 0,-1-1 0,-1-1 0,15-13 0,-18 15 0,-4 3 0,-4 6 0,-14 28 0,-16 71 0,-20 154 0,46-213 0,5-30 0,0-1 0,-1 1 0,-1-1 0,0 1 0,-1-1 0,0 0 0,-2 0 0,-10 21 0,13-30 0,-2 1 0,2-1 0,-1 0 0,0 1 0,1-1 0,-2 0 0,1-1 0,0 0 0,0 1 0,-1-1 0,1 0 0,-1 0 0,1 1 0,-1-2 0,1 1 0,-2 0 0,2-1 0,-1 1 0,1-1 0,-2 0 0,-4-1 0,0 1 0,2 0 0,-1-1 0,1 0 0,-1-1 0,1 1 0,0-1 0,0 0 0,0 0 0,-14-7 0,21 9 0,0 0 0,-1 0 0,1 0 0,0 0 0,-1 0 0,1-1 0,0 1 0,-1 0 0,1 0 0,0-1 0,-2 1 0,2 0 0,0 0 0,0-1 0,-1 1 0,1 0 0,0-1 0,0 1 0,-1 0 0,1-1 0,0 1 0,0-1 0,0 1 0,0 0 0,0-1 0,0 1 0,0 0 0,0-1 0,0 1 0,0-1 0,0 1 0,0 0 0,0-1 0,0 1 0,0-1 0,0 1 0,0-1 0,19-7 0,32-1 0,-47 8 0,242-24 0,-194 15 0,11-1 0,-58 14 0,-16 2 0,-19 2 0,-112 3-3,86-7-451,0 1 0,-109 20 0,144-19-6372</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="794.38">0 178 24575,'5'0'0,"6"0"0,7 0 0,5-4 0,-2-6 0,7 0 0,-3-4 0,-4-2 0,2-3 0,4-3 0,1-1 0,-3-1 0,-1 3 0,-6 6-8191</inkml:trace>
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink73.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink61.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -11602,7 +10110,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink74.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink62.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -11628,11 +10136,11 @@
   </inkml:definitions>
   <inkml:trace contextRef="#ctx0" brushRef="#br0">1 108 9830,'0'-4'0,"4"7"611,1 11-65,1 13 0,-2 9 0,3 3-160,5-1 0,0-2-113,-2-12 0,2-14 114,-1-9-387</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="678.79">250 108 9830,'0'3'78,"0"1"1,0-1-1,0 0 0,0 0 0,1 0 0,-1 0 1,1 1-1,0-1 0,0 0 0,0 0 0,0 0 1,0-1-1,1 1 0,0 0 0,-1 0 0,1-1 1,3 4-1,-2-4-6,0 0-1,1 1 1,0-1 0,-1-1 0,1 1-1,0 0 1,0-1 0,0 0-1,0 0 1,0 0 0,0-1 0,0 1-1,5-1 1,42 0 463,34 2 211,-81-2-681,0 1 0,-1-1 0,1 1 1,0 0-1,0 0 0,0 0 0,-1 1 0,1-1 0,-1 1 1,1 0-1,-1 0 0,0 0 0,0 1 0,1-1 0,-2 1 1,5 4-1,-6-6-30,-1 1-1,1-1 1,-1 0 0,1 0 0,-1 1 0,0-1-1,0 0 1,0 1 0,0-1 0,0 0 0,0 1 0,0-1-1,0 0 1,0 1 0,-1-1 0,1 0 0,0 1-1,-1-1 1,1 0 0,-1 0 0,0 1 0,1-1-1,-1 0 1,0 0 0,0 0 0,0 0 0,0 0 0,1 0-1,-2 0 1,1 0 0,0-1 0,0 1 0,0 0-1,0 0 1,-2 0 0,-50 29 696,45-26-578,-1 1-54,0 0 1,0-1-1,-1 0 0,1-1 0,-1 0 0,0-1 0,-13 2 0,3-4-54</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1092.39">250 108 9830,'4'-4'0,"6"-6"0,6-1 0,3 1 273,4 3 0,1 2 0,6-2 338,2-4-225,4-1 160,0 3-273,-7-3 0,-7 2-273</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1092.38">250 108 9830,'4'-4'0,"6"-6"0,6-1 0,3 1 273,4 3 0,1 2 0,6-2 338,2-4-225,4-1 160,0 3-273,-7-3 0,-7 2-273</inkml:trace>
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink75.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink63.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -11661,7 +10169,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink76.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink64.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -11690,7 +10198,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink77.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink65.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -11719,7 +10227,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink78.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink66.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -11743,11 +10251,11 @@
       <inkml:brushProperty name="color" value="#008C3A"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 459 9830,'19'0'349,"0"0"1,-1-1-1,1-1 1,0-1-1,-1 0 0,0-1 1,21-8-1,-8-1 219,2 2 0,0 2-1,47-8 1,-22 6 571,81-26 0,-56 13-320,-17 5 86,-42 10-485,1 2-1,0 1 1,1 1 0,29-2-1,41-6 744,-68 8-402,55-3 0,-31 9-384,-32 0-137,1 0-1,-1-1 1,0-1-1,0-2 1,0 1-1,0-2 1,0-1-1,19-7 1,-20 6-240,0 0 0,0 2 0,1 0 0,-1 1 0,1 1 0,0 0 0,30 3 0,-21-1 0,0-1 0,45-7 0,-55 5 0,0-2 0,1 0 0,-1-1 0,-1-1 0,0-1 0,29-16 0,-23 11 0,1 1 0,42-14 0,-43 17 0,0 0 0,0-2 0,27-16 0,-39 18 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 459 9830,'22'0'349,"0"0"1,-2-1-1,2-1 1,0-1-1,-1 0 0,-1-1 1,25-8-1,-10-1 219,3 2 0,0 2-1,54-8 1,-25 6 571,92-26 0,-64 13-320,-19 5 86,-48 10-485,0 2-1,1 1 1,1 1 0,33-2-1,47-6 744,-78 8-402,63-3 0,-35 9-384,-37 0-137,1 0-1,-1-1 1,0-1-1,0-2 1,0 1-1,0-2 1,0-1-1,21-7 1,-22 6-240,0 0 0,0 2 0,1 0 0,-1 1 0,1 1 0,-1 0 0,36 3 0,-25-1 0,0-1 0,52-7 0,-63 5 0,0-2 0,1 0 0,-1-1 0,-2-1 0,1-1 0,33-16 0,-27 11 0,2 1 0,48-14 0,-50 17 0,1 0 0,0-2 0,30-16 0,-44 18 0</inkml:trace>
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink79.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink67.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -11771,8 +10279,394 @@
       <inkml:brushProperty name="color" value="#008C3A"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 15 9830,'70'-8'1403,"-33"1"-876,-32 7-457,-1 0 0,1 1 0,-1-1-1,0 1 1,1 0 0,-1 0-1,0 0 1,0 1 0,1 0 0,-1 0-1,0 0 1,0 0 0,-1 0 0,1 1-1,0-1 1,-1 1 0,0 0 0,0 0-1,1 1 1,-2-1 0,1 0-1,0 1 1,-1 0 0,0 0 0,3 5-1,-2-4 6,0 0 0,-1 0-1,0 0 1,0 0-1,0 1 1,0-1 0,-1 1-1,0-1 1,0 1 0,-1 0-1,1-1 1,-1 1-1,0 0 1,-1-1 0,1 1-1,-1-1 1,0 1-1,-1 0 1,-3 8 0,4-12-26,-1 0 1,1 0-1,0 0 0,0 1 1,0-1-1,0 0 1,0 1-1,1-1 1,-1 0-1,1 1 1,-1-1-1,1 1 0,0-1 1,0 1-1,0-1 1,0 1-1,1-1 1,-1 0-1,1 1 1,-1-1-1,1 1 1,0-1-1,2 4 0,-1-3 9,0-1-1,1 0 0,-1 0 0,1 0 0,-1 0 0,1 0 0,0-1 0,0 1 0,0-1 0,0 0 0,0 0 0,0 0 0,0 0 0,0-1 0,0 1 0,0-1 0,1 1 0,4-1 1,-2 0-17,-1-1 1,1 1 0,0-1 0,0 0 0,0-1-1,-1 1 1,1-1 0,0 0 0,-1 0 0,0-1-1,1 0 1,7-5 0,10-9-74</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="594.44">400 40 9830,'2'1'113,"1"0"0,0 1-1,0 0 1,0-1 0,-1 1 0,1 0-1,-1 0 1,0 0 0,1 1 0,-1-1-1,0 1 1,0-1 0,-1 1 0,4 5 0,1 0 87,5 8 49,2-1-1,0 0 1,0-1 0,1-1 0,20 15 0,-30-25-214,0 0 0,0-1 1,0 0-1,0 0 0,0 0 0,0 0 1,1-1-1,-1 0 0,1 0 0,-1 0 0,1 0 1,-1-1-1,1 0 0,-1 1 0,1-2 0,-1 1 1,1 0-1,-1-1 0,1 0 0,-1 0 1,1-1-1,-1 1 0,0-1 0,0 0 0,0 0 1,0 0-1,0 0 0,7-6 0,16-20-164,-22 21 126,0 1-1,0 0 0,1 1 0,0 0 0,8-6 0,-13 10 33,0 0 0,1 1 0,-1-1-1,1 0 1,-1 1 0,1-1 0,0 1 0,-1-1 0,1 1 0,-1 0 0,1 0 0,0 0 0,-1 0-1,1 0 1,0 0 0,-1 0 0,1 0 0,0 1 0,-1-1 0,1 0 0,-1 1 0,1 0 0,-1-1-1,1 1 1,-1 0 0,1 0 0,-1 0 0,0 0 0,2 1 0,12 13 197,-2 1-1,0 0 1,0 1 0,-2 1 0,0 0 0,-1 0-1,8 20 1,2 3 14,-1-6-206</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 14 9830,'81'-7'1403,"-38"0"-876,-37 7-457,-1 0 0,0 1 0,0-1-1,0 1 1,0 0 0,0 0-1,0 0 1,-1 1 0,2-1 0,-1 1-1,-1 0 1,1 0 0,-1 0 0,0 1-1,1-2 1,-2 2 0,1 0 0,-1 0-1,2 1 1,-3-2 0,2 1-1,-1 1 1,-1 0 0,1-1 0,3 6-1,-3-5 6,1 1 0,-2 0-1,0-1 1,1 1-1,-1 0 1,0 0 0,-1 1-1,0-2 1,1 2 0,-2-1-1,1 0 1,-1 1-1,0-1 1,-1 0 0,1 0-1,-2 0 1,1 1-1,-1-1 1,-4 8 0,5-11-26,-1 0 1,1 0-1,-1 0 0,1 0 1,0 0-1,0 0 1,0 1-1,1-1 1,-1 0-1,1 0 1,-2 0-1,2 1 0,0-1 1,0 1-1,0-1 1,0 0-1,2 0 1,-2 0-1,1 1 1,-1-1-1,1 0 1,0 0-1,3 4 0,-2-3 9,0-1-1,2-1 0,-2 1 0,1 0 0,0 0 0,0 0 0,1-1 0,-1 1 0,1-1 0,-1-1 0,1 1 0,-1 0 0,1 0 0,-1-1 0,1 1 0,-1-1 0,2 1 0,4-1 1,-2 0-17,-1-1 1,1 1 0,0-1 0,0 0 0,0-1-1,-2 2 1,2-2 0,0 0 0,-1 0 0,0-1-1,1 0 1,8-4 0,12-9-74</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="594.43">464 37 9830,'2'1'113,"2"0"0,-1 1-1,1 0 1,-1-1 0,0 1 0,0-1-1,-1 1 1,1 0 0,0 1 0,-1-1-1,1 1 1,-1-2 0,-1 2 0,5 5 0,1-1 87,6 8 49,2-1-1,0 0 1,0-1 0,1-1 0,24 14 0,-36-23-214,1-1 0,0 0 1,-1 0-1,1 0 0,-1 0 0,1 0 1,1-1-1,-1 0 0,0-1 0,0 1 0,1 0 1,-2-1-1,2 0 0,-1 1 0,1-2 0,-2 1 1,2 0-1,-1-1 0,1 0 0,-2 1 1,2-2-1,-1 1 0,-1-1 0,1 0 0,0 0 1,-1 0-1,1 0 0,8-5 0,18-19-164,-25 20 126,0 0-1,-1 0 0,2 2 0,0-1 0,9-5 0,-14 9 33,-1 0 0,1 1 0,-1-1-1,2 0 1,-2 1 0,1-1 0,0 1 0,0-1 0,0 1 0,-1 0 0,1 0 0,1 0 0,-2 0-1,1 0 1,0 0 0,0 0 0,0 0 0,0 1 0,-1-1 0,2 0 0,-2 1 0,1 0 0,-1-1-1,2 1 1,-2 0 0,1 0 0,-1 0 0,0 0 0,3 1 0,13 12 197,-2 0-1,1 1 1,-1 1 0,-3 1 0,1-1 0,-1 1-1,9 18 1,2 4 14,-1-7-206</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink68.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:27:12.631"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.1" units="cm"/>
+      <inkml:brushProperty name="height" value="0.1" units="cm"/>
+      <inkml:brushProperty name="color" value="#008C3A"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">2639 95 9830,'2'8'165,"0"0"1,-1 0-1,2 0 0,-1-1 1,1 1-1,1 0 0,-1-1 1,2 1-1,0-2 1,0 1-1,-1 0 0,2 0 1,0-1-1,1 0 0,-1-1 1,15 12-1,13 5 516,0 0 1,54 25 0,-77-42-468,-9-4-192,18 9 230,0 1-1,0 1 1,-1-1 0,28 24-1,-46-34-222,0 0-1,0 0 1,1-1-1,-1 1 1,-1 0 0,1 0-1,0 0 1,-1 0-1,1 0 1,-1 1-1,1-1 1,-1 0-1,2 0 1,-2 0-1,0 0 1,0 1 0,1-1-1,-1 0 1,0 0-1,0 0 1,0 1-1,0-1 1,-1 0-1,1 0 1,0 0-1,0 1 1,-3 1-1,2-2 16,0 0-1,-1 1 1,0-1-1,0 1 1,0-1-1,-1 0 0,2 0 1,-1 1-1,0-1 1,-1 0-1,1 0 1,-1-1-1,-4 2 0,-9 2 187,1-2-1,-2 0 0,-26 1 1,22-2-27,1 0 1,-1-2 0,-1 0-1,2-2 1,-1 1 0,1-2-1,0 0 1,0-2 0,0 1-1,-34-15 1,51 18-247,-1-1 0,0 1 0,0-1 0,1 1 0,-1-1 0,0 0 0,2 0 0,-1 0 0,0 0 0,0-1 0,0 1 0,1-1 0,0 1 0,1-1 0,-2 0 0,2 0 0,0 0 0,0 1 0,-1-1 0,2 0 0,-1 0 0,1 0-1,0-1 1,0 1 0,1 0 0,-1 0 0,2 0 0,-1 1 0,0-1 0,0 0 0,0 0 0,2 0 0,-2 0 0,1 1 0,1-1 0,-1 1 0,1-1 0,0 2 0,0-1 0,1 0 0,-1 0 0,1 0 0,4-3 0,12-7-135,0 1-1,39-17 1,-33 18 151,46-29 1,-64 35-18,-3 1 0,1-1-1,0 0 1,-1 0 0,1 1-1,-2-2 1,0 1 0,1-1-1,-2 0 1,2 0 0,3-11 0,-8 15 48,1-1 0,0 1 0,-1-1 0,0 1 0,0-1 0,2 1 1,-2-1-1,-2 1 0,2-1 0,0 1 0,-1 0 0,1 0 0,-1 0 1,0-1-1,1 1 0,-1 0 0,-2-1 0,2 1 0,0 0 0,0 0 1,-1 0-1,0 0 0,0 0 0,0 0 0,0 0 0,0 1 1,0-1-1,-1 0 0,1 1 0,0 0 0,-2 0 0,2 0 0,-6-1 1,-1-1 52,1 0 0,0 1 1,-1 0-1,0 0 0,0 0 1,0 1-1,0 1 0,0-1 1,0 1-1,-9 1 0,-8 3-32</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1107.44">1 120 9830,'48'0'755,"0"2"0,-1 2 1,1 2-1,75 16 0,-121-21-703,2-1 0,-1 1 0,1 0 0,-2 1 0,1-1-1,0 0 1,0 1 0,0 0 0,-1-1 0,2 1 0,-2 0 0,0-1 0,1 1 0,-1 1 0,-1-1-1,1 0 1,1 1 0,-2-1 0,0 1 0,2-1 0,-2 1 0,0 0 0,0 0 0,-1-1 0,1 1 0,-1 0-1,1 4 1,-1 7 216,-1-1-1,0-1 0,-1 1 1,-1 0-1,-4 12 0,-2 11 62,-20 165 1248,20-222-1827,-4 1 193</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1466.28">177 362 9830,'10'0'546,"13"5"65,8 0-338,4 1 0,0-2 0,-6 3 0,-1 1 0,-7-3-273</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="30284.07">646 946 9830,'28'1'423,"0"-2"-1,-1 0 0,2-2 1,-1-1-1,-1 0 0,41-12 1,247-57 2703,-90 23-596,-145 32-1857,-45 11-222,-1-1 0,1-1 0,63-26 0,-60 19-296,1 3 1,-1 1-1,2 1 1,46-6-1,83-25 452,-67 18-327,-75 19-121,0-1 0,39-14-1,-29 7-19,-19 7-12,1-2 1,31-14-1,-35 13-112</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink69.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:27:40.654"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.1" units="cm"/>
+      <inkml:brushProperty name="height" value="0.1" units="cm"/>
+      <inkml:brushProperty name="color" value="#008C3A"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 9830,'20'0'338,"-1"0"1,1 2-1,0 0 0,-1 1 1,1 0-1,19 6 1,-27-5-194,1 1 1,-2-1 0,1 1 0,-2 1 0,2 0-1,-2 0 1,-1 1 0,2 0 0,-2 0 0,11 12-1,-14-14-48,-1 1-1,1 0 0,-1-1 0,-1 1 1,0 0-1,1 1 0,-2-1 0,0 1 1,0 0-1,-1-1 0,0 1 0,1 0 1,-2 0-1,1 10 0,-3-12 8,1 2 0,-1-1 0,-1 0 0,0 0 0,0 0 0,0 0-1,-2 0 1,2 0 0,-1-1 0,-1 0 0,-1 1 0,1-1 0,0 0 0,-1 0-1,0-1 1,-8 7 0,2-3 81,-2 1 1,-1-1-1,1-1 0,-24 9 0,23-10-26,2 1 0,-1 0 1,0-1-1,-17 14 0,30-20-136,-1 1 0,0-1-1,1 0 1,-1 1 0,1-1 0,0 1 0,-2-1-1,2 1 1,-1-1 0,1 1 0,0-1 0,-1 1 0,1 0-1,0-1 1,-1 1 0,1-1 0,0 1 0,0 0-1,0-1 1,0 1 0,-1 0 0,1-1 0,0 1 0,0 0-1,0-1 1,0 1 0,1-1 0,-1 1 0,0 0-1,0-1 1,0 0 0,0 1 0,1-1 0,-1 1 0,1 0-1,0 0 31,2 1-1,-2-1 1,1 0-1,1 0 1,-1 0-1,-1 0 1,1 0-1,1-1 0,-1 1 1,0-1-1,4 2 1,70 4 647,-71-6-667,19 0 166,6 1 79,1 0 0,-1-2 0,0 0 0,0-2-1,32-6 1,-41 3-232</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="703.29">665 120 9830,'4'-3'63,"0"1"0,0 0 1,0 0-1,1-1 0,0 1 0,-1 1 0,1-1 0,0 1 1,-1-1-1,1 1 0,-1 1 0,1-1 0,1 0 0,-2 1 1,1 0-1,1 0 0,4 1 0,-7-1-20,0 0-1,-1 0 1,2 1-1,-2-1 0,2 1 1,-2-1-1,1 1 1,0 0-1,-1 0 1,2 0-1,-2 0 1,0 1-1,0-1 1,1 0-1,-1 1 0,0 0 1,1-1-1,-1 1 1,-1-1-1,2 1 1,-2 0-1,1 0 1,-1 0-1,0 0 1,0 1-1,1-1 0,-1 0 1,0 1-1,1 2 1,2 28 304,-4-28-225,0 1-1,1 0 0,0-1 1,0 0-1,0 1 0,1 0 0,0 0 1,0-1-1,0 0 0,2 1 1,-1-1-1,1-1 0,-1 1 0,1 0 1,7 6-1,13 9 604,52 31-1,-59-41-558,1 1-1,-2 1 1,0-1 0,-1 1-1,0 2 1,-1-1-1,15 20 1,-28-32-136,0-1 0,-1 1 0,1 0 1,1 1-1,-2-1 0,1 0 0,-1 0 0,0 0 1,1 1-1,-1-1 0,0 0 0,0 1 0,0-1 1,0 0-1,0 0 0,0 1 0,0-1 0,0 0 1,0 0-1,0 0 0,-1 0 0,1 0 0,-1 0 1,1 1-1,-2-1 0,2 0 0,-1 0 0,-1 2 1,0-1 23,-2 0 1,2-1 0,-2 1-1,2-1 1,-1 0-1,-1 0 1,2 0 0,-2 0-1,1 0 1,-1 0 0,1-1-1,-4 1 1,-6 1 83,0-1-1,0-1 1,0 0 0,0 0-1,-24-4 1,34 3-140,-1 0 0,0 0 1,0 0-1,1-1 0,-1 2 0,2-2 0,-2 1 1,1-1-1,-1 0 0,2 0 0,-1 0 1,0-1-1,1 1 0,0 0 0,-2-1 0,3 1 1,-1 0-1,-1-1 0,1 0 0,-1-6 1,-4-9-28</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink7.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-10T09:08:40.035"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#33CCFF"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 0 24575,'5'0'0,"5"0"0,1 5 0,-1 5 0,2 6 0,3 1 0,3 5 0,3 5 0,-1 1 0,0-4 0,-5-1 0,-3 0 0,0-4 0,-2-1 0,1-4 0,-1-3-8191</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink70.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:28:07.431"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.1" units="cm"/>
+      <inkml:brushProperty name="height" value="0.1" units="cm"/>
+      <inkml:brushProperty name="color" value="#008C3A"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">57 8 9830,'98'-1'1957,"108"3"-364,-202-2-1557,0 0 0,-1 1 0,1-1 0,0 1 0,0-1 0,-1 0 0,0 2 0,1-1 1,-1 0-1,1 1 0,4 1 0,-7-1-5,0-1 1,0 0-1,0 0 1,2 0-1,-2 0 1,0 1-1,-1-1 1,1-1-1,0 2 1,0-1-1,-1 1 1,1-1-1,1 1 1,-2-1-1,0 1 1,1 0-1,-1 1 1,0 2 61,0 1 0,-1 0 0,-1-1 0,1 1 0,-1 0 1,0 0-1,-1-2 0,1 2 0,0-1 0,-7 8 0,6-10-25,2 0 0,0 0-1,-1-1 1,1 1 0,0 0 0,-1 0-1,2 0 1,-1 1 0,1-1-1,-1-1 1,1 1 0,0 1-1,0-1 1,1 0 0,-1 0 0,1-1-1,-1 2 1,4 4 0,0-1 141,1 1 1,1 1 0,-1-3 0,2 2 0,7 6 0,-3-2-185,-5-6 83,-1-1 1,0 1-1,0-1 0,-2 1 0,2 0 1,-2 0-1,1 0 0,2 8 0,-5-11-73,-1-1 0,0 0 0,-1 0 0,1 0 0,0 0-1,-2 0 1,2 0 0,-1 0 0,1 0 0,-1 0 0,0 0-1,0 0 1,0 0 0,0 0 0,-1-1 0,0 1 0,1-1-1,0 0 1,-1 1 0,0-1 0,0 1 0,0-1 0,0 1-1,0-1 1,0 0 0,0 0 0,0 0 0,-1 0-1,1 0 1,0-1 0,-4 2 0,-7 1 96,0 0 0,0 0-1,-1-1 1,2 0 0,-2 0 0,1-1 0,-21-1 0,8-1-86</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-980.65">2907 31 9830,'-1'35'1010,"0"-17"-676,-1 1-1,6 28 0,-3-42-263,0-1 1,-1 0 0,1 0 0,2 0 0,-2 0 0,1 0 0,-1-1-1,1 1 1,1 0 0,0-1 0,-1 1 0,2 0 0,-2-2 0,2 1-1,-1 0 1,0 0 0,5 3 0,10 2 166,-1 1 0,1-2 0,0 0 0,0 0 0,22 4 0,-35-10-169,-2 1 1,2-1 0,-2 1 0,1 0 0,-1 0 0,1-1-1,-1 1 1,1 0 0,-2 1 0,1 0 0,-1-1 0,2 1 0,-2 0-1,0-1 1,1 1 0,1 4 0,25 56 668,-18-36-392,-3-10-300</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1092.56">3164 221 9830,'0'-3'0,"0"-7"0,0-5 0,-6-7 0,0-5 0,-5-2 0,-1 1 0,3 0 0,-3 5 0,0 3 0,4 5 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6359.34">2850 980 9830,'11'0'210,"2"1"0,-2 1 0,1-1-1,-1 2 1,0 0 0,1 0 0,-2 0 0,2 0 0,-2 2-1,0 0 1,14 8 0,-21-12-158,1 1-1,-2 0 1,2 0 0,-2 0-1,0 0 1,2 0-1,-2 0 1,0 0 0,0 0-1,0 1 1,0-1 0,0 1-1,-1 0 1,0 0-1,1-1 1,0 1 0,-2 0-1,1 0 1,0 0-1,-1 0 1,1 0 0,-1-1-1,0 1 1,0 0 0,0 0-1,0 1 1,-1-1-1,1-1 1,-1 1 0,0 0-1,0 0 1,0 0 0,-1 0-1,0-1 1,1 0-1,-1 1 1,1 0 0,-2-1-1,1 1 1,-4 2 0,-12 11 392,0-1 1,-34 22 0,39-28-303,-1 0 1,0 1-1,2 0 0,-1 0 1,1 2-1,1-1 0,0 2 0,-8 13 1,11-1 219,8-25-346,0 1-1,0 0 1,1-1 0,-1 1 0,0 0 0,0 0 0,0-1 0,1 1 0,-1 0 0,0-1 0,1 1 0,-1-1-1,1 0 1,-1 1 0,0-1 0,1 1 0,-1-1 0,1 1 0,1-1 0,-2 1 0,1-1 0,-1 0-1,1 1 1,0-1 0,-1 0 0,1 1 0,0-1 0,-1 0 0,1 0 0,1 0 0,-1 1 0,0-1 0,17 1 29</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6975.64">3334 1122 9830,'0'9'210,"0"-1"0,1 2 0,0-2 0,0 1-1,2-2 1,-1 2 0,0-1 0,8 14 0,-7-18-144,-1-1 0,1 1 0,0 0 0,0-2 0,1 1 0,-1 0 0,0 0 1,1 0-1,0 0 0,0-1 0,0 0 0,1 0 0,-2 0 0,2 0 0,-1 0 0,1 0 0,1-1 1,-2 0-1,1 0 0,5 1 0,-1-1 51,2 0 0,-1 0 0,0 0 0,0-1 0,1 0 0,-1 0 0,0-1 0,19-3 0,-25 3-110,0 0 0,-1-1 0,2 1 0,-2-1 0,1 0 0,-1 0 0,0 0 0,1 0 0,-1 1 0,0-2 0,0 1 0,-1-1 0,2 0 0,-2 0 0,0 0 0,1 1 0,-1-1 0,-1 0-1,1-1 1,-1 1 0,2 0 0,-2 0 0,0 0 0,0-6 0,1 3-36,0 1 0,-1-1-1,-1-1 1,1 2 0,-1-1 0,0 0-1,-1 1 1,0-1 0,-1 0-1,1 0 1,0 1 0,-1-1 0,0 0-1,-1 1 1,0-1 0,-1 1-1,-2-5 1,-1 3 23,0 1 0,0 0-1,0 1 1,-1-1 0,0 2 0,0-2-1,0 2 1,0-1 0,-1 2 0,0 0-1,-16-6 1,2 2 201,0 2 0,-1 0-1,-37-4 1,49 8-96,1 0 1,-1 1 0,2 0-1,-1 0 1,-1 1-1,2 0 1,-2 0-1,1 2 1,1-1 0,-13 5-1,18-5-51,2 0 0,-2 0 0,2 0 0,0 1-1,-1 0 1,1 0 0,-1 0 0,1 0 0,1 0 0,-2 0-1,2 1 1,0-1 0,-1 1 0,1 0 0,0-1 0,-1 5-1,-5 13-11</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7845.84">2878 1407 9830,'5'0'273,"6"0"0,6 0 0,6 0 0,4 0 0,0 0 0,3 0 1,-5 0-274</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9850.78">0 909 9830,'5'0'273,"6"8"338,6 11-1,1 9-64,2 6-159,1 4 223,-1 0-337,-1-7 0,-2-4 0,-4-4 0,-6-5-273</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10785.9">513 957 9830,'0'-2'19,"0"1"0,-2 0 0,2 0 1,-1 0-1,0 0 0,1 0 0,-1 0 0,0 0 0,1 0 0,-1 0 0,0 1 1,0-1-1,-1 0 0,1 0 0,0 1 0,0 0 0,0-1 0,0 1 0,0-1 0,-1 1 1,1-1-1,0 1 0,0 0 0,-1 0 0,1-1 0,-1 1 0,-1 0 0,-44-5 746,41 5-700,-4 0 58,0 0-1,0 0 0,-2 1 0,2 0 0,0 1 0,-13 3 1,21-5-97,0 0 1,1 0 0,-1 1 0,1-1-1,-1 1 1,0-1 0,1 1 0,-1 0-1,1-1 1,0 1 0,-2 0 0,2 0-1,0 0 1,0 0 0,0 0 0,0 0-1,0 0 1,-1 0 0,1 1-1,0-1 1,1 0 0,-1 1 0,0-2-1,1 1 1,-1 1 0,1-1 0,0 1-1,-1-1 1,1 1 0,0-1 0,0 1-1,0-1 1,0 1 0,0-1 0,0 1-1,0-1 1,0 0 0,1 0 0,-1 1-1,1-1 1,-1 0 0,1 1 0,-1-1-1,1 0 1,0 1 0,0-1 0,2 2-1,-1-1 1,0 0 1,1 0-1,-1 0 0,0 0 0,0 0 0,1-1 0,0 1 0,-1 0 0,2-1 0,-2 0 1,2 1-1,-1-1 0,-1-1 0,2 1 0,-1-1 0,0 1 0,1 0 0,-2-1 0,2 0 1,-1 0-1,0 0 0,1 0 0,-1 0 0,1-1 0,-1 1 0,-1-1 0,2 1 0,-1-1 0,1 1 1,-2-1-1,1-1 0,1 1 0,-2 0 0,2-1 0,-2 0 0,0 1 0,0-1 0,2 0 1,-2 0-1,0 0 0,0 0 0,0 0 0,0 0 0,-1-1 0,4-4 0,-1-1-128,-1 2 136,-1 1 1,0 1-1,1-2 1,0 1-1,0 0 0,1 2 1,4-7-1,-7 9-9,0 0-1,0 1 0,0-1 1,1 0-1,-1 1 0,1-1 1,-1 1-1,0-1 0,0 1 1,2-1-1,-2 1 1,0 0-1,0 0 0,1 0 1,0 0-1,-1 0 0,1 0 1,-1 0-1,0 0 0,0 0 1,2 0-1,-2 1 0,0-1 1,0 1-1,1-1 0,-1 1 1,1-1-1,-1 1 0,0 0 1,0-1-1,0 1 0,0 0 1,0 0-1,1 0 0,-1 0 1,0 0-1,0 0 0,1 2 1,17 16 281,-2 0 1,-1 2 0,0-1-1,-3 1 1,19 39-1,-19-39-178,31 72 418,-40-85-493,-2-1 1,0 1-1,1-1 1,-2 0-1,0 1 1,-1 0-1,1 0 1,-2 0-1,1-1 1,-3 14-1,0-18-23,2-1 0,0 1-1,-1-1 1,1-1-1,-2 1 1,1 0-1,0 0 1,-1 0 0,1 0-1,0-1 1,0 1-1,-1 0 1,1-1 0,-1 0-1,0 0 1,0 0-1,1 0 1,-2-1-1,2 1 1,-2 0 0,1-1-1,1 1 1,-2-1-1,1 0 1,1 0 0,-2 0-1,1 0 1,-1 0-1,-4-2 1,-6 1 100,0 0 0,-1-1 0,1-1 0,-27-9 0,-20-18 494,42 20-579</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink71.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:35:14.671"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.1" units="cm"/>
+      <inkml:brushProperty name="height" value="0.1" units="cm"/>
+      <inkml:brushProperty name="color" value="#008C3A"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 1 9830,'24'8'995,"2"0"-1,40 9 0,4 1-58,145 41 1858,1-6 1,274 36-1,-412-76-1760,-1 3 0,104 33 0,-63-16-243,-80-23-757,2-2-1,0-1 1,69 3-1,122-7 18,-140-4-47,-87 1-4,-1 0 0,-1 1 0,2-1 0,-1-1 0,1 1 0,-2 0 0,2-1 0,-1 1 0,1-1 0,-2 0 0,1 0 0,0 0 0,0 0 0,-1 1 0,2-2 0,-2 1 0,2-1 0,-2 1 0,0-1 0,1 0 0,-1 0 0,0 0 0,1 0 0,1-3 0,8-16 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink72.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:35:15.925"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.1" units="cm"/>
+      <inkml:brushProperty name="height" value="0.1" units="cm"/>
+      <inkml:brushProperty name="color" value="#008C3A"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 0 9830,'19'8'984,"-6"-2"-442,46 21 981,2-2-1,97 25 0,141 25 853,-198-52-1503,676 174 6172,-576-150-7044,-180-43 0,-1 0 0,2 0 0,-1-2 0,1 0 0,41-3 0,-39 1 0,1 0 0,0 1 0,36 6 0,-42-2 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink73.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:35:17.858"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.1" units="cm"/>
+      <inkml:brushProperty name="height" value="0.1" units="cm"/>
+      <inkml:brushProperty name="color" value="#008C3A"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 1 9830,'20'2'327,"-2"1"0,0 0-1,1 1 1,-1 1 0,-1 0-1,1 2 1,-1-1 0,30 16 0,42 14 705,223 53 2474,-29-10-998,85 22 1397,-338-96-3667,0 0 0,0-2 0,0 0 0,39-2 0,-42-2-52,-1 2 0,-1 0 0,2 2 0,-2-1 0,0 2 0,35 10 0,-29-7-186,0 0 0,0-1 0,2-3 0,-1 0 0,0-1 0,55-2 0,-43-1 0,0 2 0,75 10 0,13 13 0,-107-19 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink74.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:38:30.966"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.1" units="cm"/>
+      <inkml:brushProperty name="height" value="0.1" units="cm"/>
+      <inkml:brushProperty name="color" value="#008C3A"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">2521 961 9830,'-5'-6'214,"0"-1"-1,-2 1 1,1 0-1,-1 1 1,-13-10-1,16 13-129,-3-2 22,0 0-1,-1 0 0,1 1 0,-2-1 0,1 2 1,0-1-1,0 2 0,0-1 0,-1 0 1,1 1-1,-2 0 0,2 1 0,0-1 0,-1 1 1,-14 2-1,11-1 24,0 0 0,2 1-1,-2-1 1,2 1 0,-2 1 0,2 0 0,-1 1 0,1 0 0,-1 0 0,2 1-1,-15 8 1,19-9-55,1 1 0,-1-2 0,1 2 0,0 0 0,0 1 0,2-1-1,-2-1 1,2 2 0,0 0 0,0-1 0,-1 1 0,2-1 0,0 1 0,0 0-1,0 0 1,1-1 0,0 1 0,0 0 0,1 0 0,0 0 0,1 4 0,-1-4-5,1-1 1,-1 0 0,0 0 0,1 1-1,0-1 1,1 0 0,-1-1 0,2 1-1,-1 0 1,1 0 0,-1-1 0,2 1 0,-2-2-1,2 1 1,-1 0 0,1 0 0,0-1-1,1 1 1,-2-1 0,2-1 0,0 1-1,8 2 1,38 3 422,-49-8-458,0 1 0,-1-1 0,0-1 0,1 1 0,-1 0 0,0 0 0,1-1 0,0 1 0,-1-1 0,1 0 0,-1 0 0,0 0 0,0 0 0,0 0 0,0 0 0,1 0 0,-1 0 0,2-3 0,-4 3-7,0 0 1,2 0-1,-2 1 1,0-1-1,0 1 0,0-1 1,0 0-1,0 0 1,0 0-1,0 0 1,0 0-1,0 0 1,0 0-1,0 1 0,0-1 1,-2 0-1,2 0 1,0 0-1,-1 0 1,1 0-1,-1 1 0,1-1 1,-1 0-1,1 0 1,-1 1-1,1-1 1,-1 0-1,0 1 1,1-1-1,-2 1 0,1-1 1,0 1-1,1-1 1,-1 1-1,0-1 1,0 1-1,-1 0 0,1-1 1,0 1-1,-1 0 1,-45-16 496,47 16-516,-33-7 273,-30-5 136,61 12-383,-1-1-1,1 1 0,0-1 1,-1 0-1,1 0 0,1 0 1,-1 0-1,-1 0 0,2 0 1,-1 0-1,0-1 1,0 1-1,0 0 0,1-1 1,0 1-1,0 0 0,-1-1 1,0 0-1,0-2 0,4-6 195,6 4-183</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-1692.91">262 889 9830,'-1'37'1024,"0"-29"-821,0-1 0,1 1 1,0 1-1,0-2 0,1 1 0,3 12 1,-2-16-145,0-1 0,-1 0 0,1 1 0,1-1 0,-1 0 0,0-1 0,2 1 0,-2 0 0,2 0 0,-2-1 0,1 1 0,1-1 0,-1 0 0,1 1 1,0-1-1,0-1 0,-1 0 0,9 3 0,62 12 605,-63-15-531,-1 0 0,1 1 1,-2-1-1,1 2 0,1 0 0,-2 0 0,13 6 0,-22-9-112,1 1 0,-1-1-1,0 0 1,1 1 0,-1-1-1,0 0 1,0 1 0,2-1 0,-2 1-1,0-1 1,0 0 0,0 1 0,0-1-1,0 1 1,0-1 0,1 0-1,-1 0 1,0 0 0,0 1 0,0-1-1,0 1 1,-1-1 0,1 1-1,0-1 1,0 0 0,0 1 0,0-1-1,0 1 1,0-1 0,-2 0-1,2 1 1,0-1 0,0 1 0,-1-1-1,1 0 1,0 1 0,0-1 0,-1 0-1,1 0 1,-1 1 0,1-1-1,0 0 1,-1 0 0,1 1 0,0-1-1,-1 0 1,1 0 0,-2 0-1,2 0 1,0 1 0,-1-1 0,1 0-1,-2 0 1,-28 11 517,28-11-513,-407 86 3694,400-85-3629,6 0-58,2 0-1,-1-1 1,0 0-1,1 1 1,-2-1-1,1 0 1,1 0-1,-2 0 1,1 0-1,1 0 1,-1 0-1,0-1 1,0 1-1,0 0 1,-2-2-1,2-2 34</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-1280.64">262 961 9830,'6'0'273,"5"-4"113,7-2-113,4 1 0,5 1 0,2 1 1,0 2-1,1 0 0,0 0 0,0-3 113,-4-1-386</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4428.78">2116 1 9830,'26'0'533,"-1"1"-1,1 1 1,-1 1-1,38 8 1,-53-9-450,0 1 0,-1 0-1,0 0 1,0 1 0,1 0 0,-1 0 0,-1 1-1,1 0 1,-2 0 0,2 1 0,-1-1 0,-1 1-1,0 1 1,5 6 0,-11-12-44,1 1 1,-2-1-1,1 0 1,0 1-1,-1 0 1,1-1-1,-1 1 1,0-1-1,1 1 1,-1 0-1,0-1 1,0 1-1,0-1 1,0 0-1,0 1 1,-1 0-1,1-1 1,0 1-1,-1-1 1,1 1-1,-1-1 1,0 1-1,1-1 0,-2 1 1,1-1-1,0 1 1,-2 1-1,-47 38 818,9-8-297,35-26-433,-1 1-1,3 0 1,-2 0-1,1 0 1,1 1 0,0-1-1,1 1 1,-3 13-1,6-19-61,-1 0 0,1 0 1,1 1-1,-1-1 0,0-1 0,1 1 0,0 0 0,0 1 0,1-1 0,-1 0 0,0 0 0,0 0 0,1-2 1,1 2-1,-2 0 0,1 0 0,1-1 0,-1 0 0,0 1 0,2-1 0,-2 0 0,1 0 0,0 0 0,0-1 1,1 1-1,-2-1 0,7 3 0,11 4 125,0-1 0,1-2 0,-2 0 0,2 0 0,0-2 0,37 4 0,-23-5-144</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4919.21">2666 145 9830,'-1'-1'10,"-1"0"0,0-1 1,1 1-1,-1 0 0,1 1 0,0-2 0,0 1 0,-1 0 0,1-1 1,0 1-1,1-1 0,-1 1 0,0-1 0,0 0 0,1 1 0,0-1 0,-2 0 1,2 1-1,0-1 0,-1 0 0,1 1 0,0 0 0,0-1 0,1 0 1,-1 0-1,0 1 0,0-1 0,2 0 0,-2 1 0,1-1 0,0 0 1,-1 1-1,1-1 0,0 1 0,0-1 0,1 1 0,-1 0 0,0 0 1,0 0-1,1 0 0,-1-1 0,1 1 0,0 0 0,-1 0 0,3-1 1,4-2 63,0 0 1,0 0-1,1 1 1,-1 0 0,2 0-1,-1 1 1,0 0-1,12-2 1,12 0 243,-2 2 1,1 0 0,1 2-1,-2 1 1,35 5-1,-63-6-281,-1 0 0,0 0 0,-1 1 0,2-1 0,-1 1 0,-1-1 0,2 1 0,-1 0 0,-1 0 0,1-1 0,0 1 0,0 0 0,-1 0 0,1 1-1,0-1 1,-1 0 0,1 0 0,-1 1 0,0-2 0,0 2 0,1-1 0,-1 1 0,0-1 0,-1 1 0,1-1 0,0 1 0,-1 0 0,1 0 0,-1-1 0,2 1 0,-2 0 0,0 0 0,0-1 0,0 1-1,0-1 1,0 1 0,-2 3 0,-1 7 206,-1-2-1,0 2 0,-1-2 1,-12 21-1,-3 7 232,17-30-371,-1 1 0,2 0-1,-1 0 1,2 0 0,0 1-1,0-2 1,1 2-1,1-2 1,1 16 0,0-20-23,0 1 1,-1-1-1,1 0 1,1 0-1,-1 0 1,0 0-1,2 0 1,-2-1-1,2 1 0,-1 0 1,1-1-1,-1 0 1,2 0-1,-2 0 1,2 0-1,-2-1 1,2 1-1,0-1 1,-1 1-1,2-1 1,7 2-1,23 5 473,-1 0-1,52 4 1,-35-5-462</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3199.18">176 193 9830,'12'-1'297,"1"0"0,-2-1 0,2 1 0,12-6 0,44-5 403,-62 11-591,0 1 0,1 0 1,-1 0-1,0 1 1,0-1-1,0 1 1,13 3-1,-18-3-70,-1 0 1,1 0-1,1 0 1,-2 0-1,1 0 1,-1 0-1,2 1 1,-2-1-1,0 0 1,1 1-1,-1-1 0,1 0 1,-1 1-1,0-1 1,0 1-1,0 0 1,-1-1-1,1 1 1,1 0-1,-2 0 1,1 0-1,-1 0 0,0-1 1,0 1-1,1 0 1,-1 0-1,0-1 1,-1 1-1,1 3 1,-3 6 118,2-1 0,-2 0 1,0 1-1,0-1 0,-2 0 1,1 0-1,-2 0 0,0 0 1,0-2-1,-12 16 0,-8 2 364,1 0-1,-32 23 0,56-49-492,1 1 0,-2-1-1,1 1 1,1-1 0,-1 1 0,1-1-1,-1 1 1,0 0 0,1-1 0,-1 1 0,1 0-1,0-1 1,-2 1 0,2 0 0,0 0-1,-1-1 1,1 1 0,0 0 0,0 0 0,-1 0-1,1-1 1,0 1 0,0 0 0,0 0 0,0-1-1,0 0 1,0 1 0,1 0 0,-1 0-1,0 0 1,1 1 0,1-1 19,0 0-1,-1 1 1,1-1 0,0 0-1,0 0 1,-1-1 0,1 1-1,1 0 1,-2 0 0,1-1 0,1 1-1,-1-1 1,4 1 0,82 2 713,-79-3-680,29-1-36</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3641.73">610 409 9830,'2'-17'0,"1"1"0,0 0 0,2-1 0,1 1 0,12-26 0,5-14 0,-16 35-8,-3 8 27,-1 0 0,2 0 0,0 1 0,2-1 0,-2 2 0,4-2 0,10-15 0,-18 27 10,-1 1 0,2-1 0,-1 1 0,-1 0 0,1-1 0,-1 1-1,1 0 1,0 0 0,-1 0 0,1 0 0,1 0 0,-1 0 0,-1 0 0,1 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,-1 0-1,2 0 1,-1 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,-1 0 0,1 1 0,-1-1 0,1 0 0,1 1 0,-2-1 0,1 1-1,-1-1 1,1 1 0,-1-1 0,1 1 0,-1-1 0,1 1 0,-1-1 0,1 2 0,24 28 443,-23-25-376,19 27 538,-2 2 0,-2 1 0,19 60 0,13 27 355,-34-98-667,-1-9-257</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6861.25">1044 457 9830,'15'2'303,"0"1"-1,0-1 1,0 1 0,-1 2-1,1-1 1,-1 2 0,0 0-1,19 9 1,17 7 189,263 111 3148,-6-11-251,-53-34-874,-229-80-2450</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink75.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:40:51.221"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.1" units="cm"/>
+      <inkml:brushProperty name="height" value="0.1" units="cm"/>
+      <inkml:brushProperty name="color" value="#008C3A"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">73 0 9830,'-1'0'47,"-1"1"-1,0-1 1,0 0-1,0 1 0,1 0 1,-1-1-1,0 1 1,1 0-1,-1 0 1,0 0-1,1 0 1,-1 0-1,1 0 1,0 0-1,-1 0 1,1 1-1,0-1 1,0 1-1,-1-1 0,1 1 1,1-1-1,-1 1 1,0-1-1,0 1 1,0 0-1,1 0 1,-1-1-1,1 1 1,-1 3-1,0-1 17,0 0 0,1 0 0,-1 0 1,1 0-1,0 0 0,0-1 0,0 1 0,1 0 0,0 0 0,-1 0 0,1 0 0,0-1 0,2 5 0,1-2 63,1 0-1,0 0 0,0-1 1,0 1-1,1-1 0,-1 0 0,1-1 1,0 1-1,1-1 0,-1-1 1,11 6-1,79 28 1111,-93-36-1199,3 1 30,69 20 544,-68-21-537,-1 0 0,1 0 1,-1 0-1,1-1 1,0 0-1,-1 0 0,1 0 1,-1-1-1,10-2 1,-15 2-79,1 1 1,0-1 0,0 0 0,0 0-1,0 0 1,-1 0 0,1 0-1,-1 0 1,1-1 0,-1 1 0,1 0-1,-1-1 1,1 1 0,-1-1 0,0 0-1,0 1 1,0-1 0,0 0-1,0 0 1,0 0 0,-1 0 0,1 1-1,-1-1 1,1 0 0,-1 0 0,0 0-1,1 0 1,-1 0 0,0 0 0,-1 0-1,1 0 1,0 0 0,0 0-1,-1 0 1,1 0 0,-1 0 0,-1-4-1,-1-1-58,1 0 0,-2 0 0,1 0 0,-1 0 0,0 0 0,0 1 0,-1 0-1,-7-8 1,2 5 130,0 1-1,0 0 0,-1 1 1,0 0-1,-1 1 0,1 1 1,-1-1-1,0 2 0,-1-1 1,1 2-1,-21-4 0,11 4 118,-1 0 0,1 2 0,-1 0 0,0 2 0,-39 5 0,36-2-155</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink76.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:40:51.995"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.1" units="cm"/>
+      <inkml:brushProperty name="height" value="0.1" units="cm"/>
+      <inkml:brushProperty name="color" value="#008C3A"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 255 9830,'4'-5'0,"1"-4"0,9-7 0,6-3 0,8-12 0,4-5 0,0-1 0,-5-2 0,-7 1 0,-3 16 0,0 20 611,-3 22 208,1 18-209,1 5-223,3 5 223,-2 2-64,-4-3-273,-4-9-273</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink77.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:40:58.396"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.1" units="cm"/>
+      <inkml:brushProperty name="height" value="0.1" units="cm"/>
+      <inkml:brushProperty name="color" value="#008C3A"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">26 1 9830,'-4'0'273,"-2"8"273,1 16 273,1 12-272,0 9-1,3 5 0,0-2-273,0-5 0,1-10-273</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="948.2">276 100 9830,'-10'0'222,"0"0"1,0 0-1,0 1 0,0 1 0,0-1 0,1 2 1,-1-1-1,-11 6 0,17-6-166,1 0-1,-1 0 1,1 1-1,-1-1 1,1 1-1,0 0 1,0 0-1,1 0 1,-1 0-1,1 1 1,-1-1-1,1 1 1,0 0-1,0-1 1,0 1-1,1 0 1,0 0-1,-1 0 1,1 0-1,1 0 1,-1 0-1,0 6 1,1-4 31,-1 1 0,1-1 1,0 1-1,0 0 0,1-1 0,0 1 1,0-1-1,1 0 0,2 9 0,-3-13-56,0 0 0,0 0 0,0 0 0,0-1 0,0 1 0,0 0 0,0-1 0,0 1 0,1-1 0,-1 0 0,1 1 0,-1-1 0,1 0 0,-1 0 0,1 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,0-1 0,0 1 0,0 0 0,0-1 0,0 0 0,-1 0 0,1 1 0,0-1 0,0 0 0,0 0 0,0-1 0,0 1 0,0 0 0,0-1 0,3 0 0,-5 1-21,0 0 1,-1 0 0,1-1-1,0 1 1,0 0 0,0 0-1,0 0 1,-1 0 0,1 0-1,0-1 1,0 1 0,0 0-1,0 0 1,0 0 0,0 0 0,-1-1-1,1 1 1,0 0 0,0 0-1,0 0 1,0-1 0,0 1-1,0 0 1,0 0 0,0 0-1,0-1 1,0 1 0,0 0-1,0 0 1,0 0 0,0-1-1,0 1 1,0 0 0,0 0-1,0 0 1,0-1 0,1 1-1,-1 0 1,0 0 0,0 0-1,0-1 1,0 1 0,0 0-1,0 0 1,1 0 0,-1 0-1,0 0 1,0-1 0,0 1-1,0 0 1,1 0 0,-1 0-1,0 0 1,0 0 0,0 0-1,1 0 1,-1 0 0,0 0 0,0 0-1,0 0 1,1 0 0,-1 0-1,0 0 1,0 0 0,0 0-1,1 0 1,-1 0 0,0 0-1,-14-7 255,-2 3-220</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink78.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:40:56.917"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.1" units="cm"/>
+      <inkml:brushProperty name="height" value="0.1" units="cm"/>
+      <inkml:brushProperty name="color" value="#008C3A"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 9830,'0'8'546,"0"16"273,0 12-272,0 5-274,0 3 273,0-2-273,0 6 546,0-2-546,0-4 0,0-10-273</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="652.37">126 175 9830,'19'-9'52,"11"-7"408,2 2 1,36-12-1,27-13 769,-95 39-1192,1 0-1,0 0 1,0 0 0,0 0 0,0 1 0,0-1-1,0 0 1,0 0 0,0 1 0,0-1 0,0 0 0,0 1-1,-1-1 1,1 1 0,0-1 0,0 1 0,-1-1-1,1 1 1,0 0 0,-1-1 0,1 1 0,0 0 0,-1 0-1,1-1 1,-1 1 0,1 0 0,-1 0 0,1 0-1,-1 0 1,0 0 0,0-1 0,1 1 0,-1 1 0,7 35 654,-7-33-586,3 244 2405,-4-176-2017,0-35-447</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="902.67">275 450 9830,'5'0'273,"5"0"0,5 0 0,4 0 0,0 0-273</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink79.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:43:22.162"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.1" units="cm"/>
+      <inkml:brushProperty name="height" value="0.1" units="cm"/>
+      <inkml:brushProperty name="color" value="#008C3A"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 9830,'5'8'611,"2"7"-338,4 8 337,2 10-64,-2 9 274,1 3-434,0-3-113,-2-4 0,-4-8-273</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="620.62">93 143 9830,'0'-2'0,"0"0"0,2 0 0,-2 2 0,1-2 0,-1 0 0,1 1 0,0-1 0,1 0 0,-2 1 0,1-1 0,0 1 0,0-1 0,2 1 0,-2 0 0,0-1 0,0 2 0,2-1 0,2-2 0,40-18 0,-22 11 0,5-4 67,75-34 758,-93 45-746,0-1 1,0 1-1,0 1 0,0 0 0,0 0 0,1 0 0,-1 1 1,1 0-1,11 0 0,-17 2-22,-2-1 0,1 1-1,0 0 1,0 0 0,0 0 0,0 1 0,0-1-1,-2 0 1,2 0 0,0 1 0,-1 0 0,0 0-1,1 0 1,-2 1 0,2-1 0,-2 1 0,1-2 0,-1 2-1,1 0 1,-2-1 0,1 1 0,1 0 0,-2 0-1,0-1 1,0 2 0,1-1 0,-1 0 0,0 4-1,3 2 141,-3 1 0,2 0 0,-2-1 0,0 2-1,-1-2 1,-1 1 0,-3 18 0,-12 18 494,-2-2 0,-42 67-1,52-97-552,7-13-98,1 1-1,-2-1 1,1 1-1,0-1 1,1 1 0,-1 0-1,1-1 1,0 1-1,-2 0 1,2-1 0,0 0-1,0 1 1,0 0 0,0-1-1,0 1 1,2 0-1,-2-1 1,0 1 0,1 0-1,-1-1 1,1 1-1,0-1 1,-1 0 0,2 0-1,-1 1 1,0-1-1,0 1 1,0-1 0,1 0-1,-1 1 1,1-1 0,0 0-1,-1 0 1,0 0-1,2 0 1,-2 0 0,1 0-1,0-1 1,0 0-1,0 1 1,0-1 0,0 1-1,-1-1 1,2 1-1,-1-1 1,4 0 0,14 3 194,0-2 1,0 0-1,1-1 1,20-1 0,-17 0-20,15-1 96,1-1 0,40-6-1,-43 2-264</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -11800,7 +10694,7 @@
       <inkml:brushProperty name="color" value="#33CCFF"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 6 24575,'74'-2'0,"-42"-1"0,-1 2 0,1 2 0,52 10 0,-81-11 0,-1 0 0,1 1 0,-2-1 0,2 1 0,-1-1 0,0 1 0,0 0 0,1 0 0,-1 0 0,0 1 0,0-1 0,0 0 0,-1 2 0,1-1 0,0-1 0,0 1 0,0 0 0,-1 0 0,1 0 0,-1 0 0,1 1 0,-1-1 0,0 1 0,0-1 0,0 1 0,0-1 0,0 1 0,-1 0 0,1 0 0,0-1 0,-1 1 0,0-1 0,1 2 0,-1-1 0,0-1 0,0 1 0,-1 4 0,-2 7 0,0-1 0,-1 1 0,0-1 0,-1 1 0,-12 24 0,12-28 0,3-6 0,1 1 0,-2-1 0,2 0 0,-1 1 0,1 0 0,0-1 0,0 0 0,0 2 0,1-2 0,-1 1 0,1 0 0,0 0 0,0-1 0,0 2 0,0-2 0,1 0 0,0 2 0,0-2 0,-1 1 0,5 7 0,-2-6 0,-1 0 0,2-1 0,-1 0 0,1 1 0,0-1 0,1-1 0,-2 1 0,2-1 0,0 0 0,-1-1 0,1 2 0,0-2 0,0 0 0,8 2 0,31 13-1365,-24-13-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 6 24575,'82'-2'0,"-46"-1"0,-1 2 0,0 2 0,59 9 0,-91-10 0,0 0 0,0 1 0,-2-1 0,2 1 0,0-1 0,-1 1 0,0 0 0,1 0 0,0 0 0,-1 1 0,0-2 0,0 1 0,-1 2 0,2-1 0,-1-1 0,0 1 0,0 0 0,-1-1 0,2 1 0,-2 0 0,1 1 0,-1-1 0,0 1 0,0-2 0,0 2 0,1-1 0,-1 1 0,-1 0 0,1-1 0,0 0 0,-1 1 0,0-1 0,1 2 0,-1-2 0,0 0 0,0 1 0,-1 3 0,-2 7 0,-1-1 0,0 1 0,-1-1 0,0 1 0,-14 23 0,13-27 0,4-6 0,1 2 0,-2-1 0,1 0 0,0 0 0,1 1 0,0-2 0,0 1 0,0 2 0,1-3 0,-1 2 0,1 0 0,0-1 0,0 0 0,0 2 0,0-3 0,1 1 0,0 2 0,0-3 0,-1 2 0,6 6 0,-3-6 0,-1 1 0,3-1 0,-2-1 0,1 2 0,1-2 0,0 0 0,-1 1 0,1-1 0,1-1 0,-2 0 0,2 2 0,-1-3 0,1 1 0,9 2 0,34 11-1365,-27-11-5461</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -11820,7 +10714,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:27:12.631"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:43:21.090"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.1" units="cm"/>
@@ -11828,10 +10722,8 @@
       <inkml:brushProperty name="color" value="#008C3A"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">2247 98 9830,'1'8'165,"1"0"1,-1 0-1,1 0 0,0 0 1,1 0-1,0 0 0,0-1 1,1 1-1,0-1 1,0 0-1,0 0 0,1 0 1,0-1-1,1 0 0,-1 0 1,13 11-1,11 6 516,0-1 1,46 26 0,-66-42-468,-7-5-192,15 9 230,0 1-1,0 1 1,-1 0 0,24 24-1,-39-35-222,0 0-1,0 0 1,0-1-1,0 1 1,-1 0 0,1 0-1,0 0 1,-1 0-1,1 0 1,-1 1-1,1-1 1,-1 0-1,1 0 1,-1 0-1,0 0 1,0 1 0,1-1-1,-1 0 1,0 0-1,0 0 1,0 1-1,0-1 1,-1 0-1,1 0 1,0 0-1,0 1 1,-2 1-1,1-2 16,0 1-1,-1 0 1,1-1-1,-1 1 1,0-1-1,0 0 0,1 0 1,-1 1-1,0-1 1,0 0-1,0 0 1,0-1-1,-4 2 0,-8 2 187,1-2-1,-1 0 0,-23 1 1,19-2-27,1 0 1,-1-2 0,0 0-1,1-2 1,-1 1 0,1-2-1,0 0 1,0-2 0,0 1-1,-29-16 1,43 19-247,0-1 0,-1 1 0,1-1 0,0 1 0,0-1 0,0 0 0,1 0 0,-1-1 0,1 1 0,-1-1 0,1 1 0,0-1 0,0 1 0,1-1 0,-1 0 0,1 0 0,0 0 0,0 0 0,0 0 0,1 0 0,-1 0 0,1 0-1,0-1 1,0 1 0,1 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,0 0 0,0 0 0,1 0 0,-1 0 0,1 1 0,0-1 0,0 1 0,1-1 0,-1 1 0,1 0 0,0 0 0,0 0 0,0 0 0,4-3 0,10-7-135,0 0-1,33-16 1,-28 17 151,40-29 1,-56 36-18,-1 1 0,0-1-1,0 0 1,-1 0 0,1 0-1,-1-1 1,-1 1 0,1-1-1,-1 0 1,1 0 0,3-12 0,-7 16 48,1-1 0,0 1 0,-1-1 0,0 1 0,0-1 0,1 1 1,-1-1-1,-1 1 0,1-1 0,0 1 0,-1-1 0,1 1 0,-1 0 1,0-1-1,1 1 0,-1 0 0,-1-1 0,1 1 0,0 0 0,0 0 1,-1 0-1,1 0 0,-1 0 0,0 0 0,1 0 0,-1 1 1,0-1-1,0 0 0,0 1 0,0 0 0,-1 0 0,1-1 0,-5 0 1,0-1 52,0 0 0,0 1 1,-1 0-1,1 0 0,-1 0 1,0 1-1,1 1 0,-1-1 1,0 1-1,-7 1 0,-7 3-32</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1107.44">1 123 9830,'41'0'755,"0"2"0,-1 2 1,1 2-1,63 17 0,-102-22-703,1-1 0,0 1 0,0 0 0,-1 1 0,1-1-1,-1 0 1,1 1 0,-1 0 0,0-1 0,1 1 0,-1 0 0,0 0 0,0 0 0,0 1 0,-1-1-1,1 0 1,0 1 0,-1-1 0,0 1 0,1-1 0,-1 1 0,0 0 0,0 0 0,-1-1 0,1 1 0,-1 0-1,1 5 1,-1 6 216,-1-1-1,0 0 0,-1 0 1,0 0-1,-4 13 0,-2 11 62,-17 169 1248,18-227-1827,-4 0 193</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1466.28">151 372 9830,'8'0'546,"12"5"65,6 0-338,4 1 0,0-2 0,-5 3 0,-2 1 0,-5-2-273</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="30284.07">550 971 9830,'24'1'423,"0"-2"-1,-1 0 0,1-2 1,0-1-1,-1 0 0,35-13 1,210-58 2703,-76 24-596,-124 33-1857,-38 10-222,-1 0 0,0-1 0,55-27 0,-52 20-296,1 2 1,0 2-1,1 1 1,39-7-1,71-25 452,-57 18-327,-64 20-121,0-1 0,33-14-1,-25 6-19,-15 8-12,0-2 1,26-15-1,-29 14-112</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 0 9830,'4'0'273,"2"4"0,-1 6 0,4 6 113,-1 12 434,4 6-434,-1 1-113,2 4 337,-1-2-337,1-1 114,-1 0 159,-2-5-546</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="374.52">225 25 9830,'0'4'273,"9"19"948,6 18-357,2 14-45,-3 7-273,-4-3-273,-3-7 0,-3-9 0,-2-11-273</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -11851,7 +10743,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:27:40.654"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:43:29.363"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.1" units="cm"/>
@@ -11859,8 +10751,9 @@
       <inkml:brushProperty name="color" value="#008C3A"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 9830,'17'0'338,"0"0"1,0 2-1,0 0 0,0 1 1,0 0-1,17 7 1,-24-6-194,1 1 1,-1 0 0,0 0 0,-1 1 0,1 0-1,-1 1 1,-1 0 0,1 0 0,-1 1 0,9 11-1,-12-13-48,0 0-1,0 0 0,-1 0 0,0 0 1,-1 0-1,1 1 0,-1 0 0,0 0 1,-1 0-1,0 0 0,0 0 0,0 0 1,-1 1-1,1 9 0,-3-11 8,1 1 0,-1-1 0,-1 1 0,1-1 0,-1 0 0,0 0-1,-1 1 1,1-1 0,-1-1 0,0 1 0,-1 0 0,0-1 0,1 0 0,-2 1-1,1-2 1,-7 7 0,1-2 81,-1 0 1,-1-1-1,1 0 0,-21 9 0,20-11-26,1 1 0,0 0 1,0 0-1,-15 14 0,26-21-136,-1 1 0,0-1-1,1 0 1,-1 1 0,1-1 0,0 1 0,-1-1-1,1 1 1,-1-1 0,1 1 0,0-1 0,-1 1 0,1 0-1,0-1 1,-1 1 0,1-1 0,0 1 0,0 0-1,0-1 1,0 1 0,-1 0 0,1-1 0,0 1 0,0 0-1,0-1 1,0 1 0,1-1 0,-1 1 0,0 0-1,0-1 1,0 1 0,0 0 0,1-1 0,-1 1 0,1 0-1,0 0 31,1 1-1,-1-1 1,1 0-1,0 0 1,0 0-1,-1 0 1,1 0-1,0-1 0,0 1 1,0-1-1,3 2 1,61 4 647,-62-6-667,17 0 166,5 2 79,0-1 0,0-2 0,0-1 0,0-1-1,28-6 1,-36 3-232</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="703.29">575 126 9830,'3'-3'63,"1"0"0,-1 1 1,1 0-1,0-1 0,0 1 0,0 1 0,0-1 0,0 1 1,0-1-1,0 1 0,0 1 0,0-1 0,1 0 0,-1 1 1,0 0-1,1 0 0,4 1 0,-7-1-20,1 0-1,-1 0 1,1 1-1,-1-1 0,1 1 1,-1-1-1,1 1 1,-1 0-1,0 0 1,1 0-1,-1 0 1,0 1-1,0-1 1,0 0-1,0 1 0,0 0 1,0-1-1,0 1 1,-1 0-1,1 0 1,-1 0-1,1 0 1,-1 0-1,0 0 1,0 1-1,0-1 0,0 0 1,0 1-1,1 3 1,1 28 304,-3-28-225,0 0-1,1 0 0,0-1 1,0 1-1,0 0 0,0 0 0,1 0 1,0 0-1,0-1 0,1 1 1,0-1-1,0 0 0,0 0 0,0 0 1,7 7-1,10 8 604,46 34-1,-51-44-558,0 2-1,-1 0 1,0 0 0,-1 1-1,0 1 1,-1 0-1,13 20 1,-24-33-136,0 0 0,-1 0 0,1 0 1,0 1-1,-1-1 0,1 0 0,-1 0 0,0 0 1,1 1-1,-1-1 0,0 0 0,0 1 0,0-1 1,0 0-1,0 0 0,0 1 0,0-1 0,0 0 1,0 1-1,0-1 0,-1 0 0,1 0 0,-1 0 1,1 1-1,-1-1 0,1 0 0,-1 0 0,-1 2 1,0-1 23,-1 0 1,1-1 0,-1 1-1,1-1 1,-1 1-1,0-1 1,1 0 0,-1 0-1,0 0 1,0 0 0,0-1-1,-3 1 1,-5 1 83,0-1-1,-1-1 1,1 0 0,0 0-1,-21-4 1,29 3-140,0 0 0,-1 0 1,1 0-1,0-1 0,0 1 0,1-1 0,-1 1 1,0-1-1,0 0 0,1 0 0,-1 0 1,1-1-1,0 1 0,0 0 0,-1-1 0,2 0 1,-1 1-1,0-1 0,0 0 0,-1-6 1,-3-10-28</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 128 9830,'1'-2'24,"-1"0"0,1 0 0,0 0 0,1-1 0,-1 1 0,0 0 0,0 0 0,0 1-1,2-1 1,-2 0 0,1 0 0,-1 1 0,1-1 0,1 0 0,-1 1 0,0-1 0,1 1 0,-1 0 0,0 1 0,1-2 0,-1 2 0,0-1 0,2 0-1,-2 0 1,0 1 0,2-1 0,-2 1 0,5-1 0,7-1 201,-1 0 0,2 0-1,28 1 1,-41 1-178,2 0 0,-1-1 0,0 2 0,0-1 0,-1 0-1,2 0 1,-2 1 0,1 0 0,0-1 0,0 1 0,0 0 0,0 0 0,-1 0 0,1 1 0,-1-1 0,1 0 0,0 1-1,-1 0 1,0-2 0,-1 2 0,2 0 0,-1 0 0,0 0 0,-1 0 0,1 0 0,0 1 0,-1-1 0,0-1 0,0 2-1,1-1 1,-1 0 0,0 1 0,-1-1 0,1 1 0,-1-1 0,0 0 0,1 1 0,-1-1 0,-1 5 0,-1 10 193,-2-1 0,0 0 0,-1 1 1,-1-2-1,-9 17 0,-4 17 80,18-46-278,-1-1 1,2 1-1,-1-1 0,1 0 0,-1 1 0,1 0 1,0 0-1,0-1 0,0 0 0,0 1 0,0 0 0,1-1 1,-1 1-1,1 0 0,1-1 0,-1 0 0,0 0 1,0 1-1,0-1 0,0 1 0,2-1 0,-2 0 1,1 0-1,0 0 0,1 0 0,-1 0 0,0 0 1,1 0-1,-1-1 0,0 1 0,1-1 0,0 1 1,-1-1-1,2-1 0,-2 1 0,1 0 0,0 0 1,0 0-1,1 0 0,-2-1 0,7 1 0,8 0 137,1-1 0,-2 0 1,1-1-1,0 0 0,-1-1 0,24-5 0,-13 1-134</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="483.65">547 105 9830,'2'-3'0,"-1"1"0,1 0 0,1 0 0,-1 0 0,0 1 0,0-1 0,1 0 0,-1 1 0,2-1 0,-2 0 0,0 1 0,2 0 0,-2 0 0,1 0 0,4-1 0,-3 1 0,42-16 216,1 1 0,1 3 1,98-16-1,-140 28-132,-1 1 0,1 0 0,-1 0 0,1 1 1,0-1-1,0 1 0,-2 0 0,2 0 0,0 1 0,-2-1 1,2 0-1,-1 1 0,0 0 0,0 1 0,0-1 0,-1 1 1,1 0-1,-1-1 0,0 1 0,0 1 0,0-1 0,-1 1 1,1-1-1,-1 1 0,1 0 0,-2 0 0,5 8 0,6 11 309,-1 0 0,-1 1 0,12 45 0,-15-42-326,16 34 498,-21-56-308,-4-7-222,-7-11-137,-2 1 86</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="736.29">863 269 9830,'9'0'546,"10"0"-273,9 0 273,6 0-273,7 0 274,1 0-274,-2 0 0,-2 0 0,-8 0-273</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -11880,7 +10773,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:28:07.431"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:43:27.648"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.1" units="cm"/>
@@ -11888,14 +10781,8 @@
       <inkml:brushProperty name="color" value="#008C3A"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">50 8 9830,'86'-1'1957,"94"3"-364,-176-2-1557,-1 0 0,0 1 0,0-1 0,1 1 0,-1 0 0,0-1 0,0 2 0,0-1 1,0 0-1,0 1 0,4 1 0,-6-1-5,0-1 1,0 0-1,0 0 1,1 0-1,-1 0 1,0 1-1,-1-1 1,1 0-1,0 1 1,0-1-1,-1 1 1,1-1-1,0 1 1,-1-1-1,0 1 1,1 0-1,-1 1 1,0 3 61,0 0 0,-1 0 0,0 0 0,0 0 0,-1 0 1,0 0-1,0-1 0,0 1 0,0-1 0,-6 9 0,6-11-25,1 0 0,0 0-1,-1 0 1,1 0 0,0 0 0,0 0-1,1 0 1,-1 1 0,1-1-1,-1 0 1,1 0 0,0 1-1,0-1 1,1 0 0,-1 0 0,1 0-1,-1 1 1,3 4 0,1 0 141,0 0 1,1 1 0,0-2 0,1 1 0,6 7 0,-2-2-185,-5-7 83,-1-1 1,1 1-1,-1 0 0,-1 0 0,1 0 1,-1 1-1,0-1 0,2 9 0,-4-12-73,-1-1 0,0 0 0,-1 0 0,1 0 0,0 0-1,-1 1 1,1-1 0,-1 0 0,1 0 0,-1 0 0,0 0-1,0 0 1,0 0 0,0 0 0,0-1 0,-1 1 0,1 0-1,0-1 1,-1 1 0,1-1 0,-1 1 0,0-1 0,0 1-1,1-1 1,-1 0 0,0 0 0,0 0 0,0 0-1,0 0 1,0-1 0,-3 2 0,-6 2 96,-1-1 0,1 0-1,-1-1 1,1 0 0,-1 0 0,0-1 0,-17-1 0,6-1-86</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-980.65">2546 33 9830,'-1'36'1010,"0"-17"-676,0 1-1,4 30 0,-2-45-263,0-1 1,-1 0 0,1 1 0,1-1 0,-1 0 0,1 0 0,-1 0-1,1 0 1,0 0 0,1-1 0,-1 1 0,1 0 0,-1-1 0,1 0-1,0 0 1,0 0 0,4 3 0,8 3 166,0 0 0,1-1 0,0-1 0,0 0 0,19 5 0,-31-11-169,-1 1 1,1-1 0,-1 1 0,0 0 0,0 0 0,0 0-1,0 0 1,0 0 0,-1 1 0,1 0 0,-1-1 0,1 1 0,-1 0-1,0 0 1,0 0 0,2 4 0,21 59 668,-15-37-392,-3-11-300</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1092.56">2771 233 9830,'0'-4'0,"0"-6"0,0-6 0,-5-7 0,0-6 0,-5-1 0,0 0 0,2 1 0,-3 5 0,1 3 0,3 5 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6359.34">2496 1032 9830,'10'0'210,"1"1"0,-1 1 0,0-1-1,0 2 1,0 0 0,0 0 0,-1 0 0,1 1 0,-1 1-1,0 0 1,12 9 0,-18-13-158,0 1-1,-1 0 1,1 0 0,-1 0-1,0 0 1,1 0-1,-1 0 1,0 1 0,0-1-1,-1 1 1,1-1 0,0 1-1,-1 0 1,0 0-1,0 0 1,1 0 0,-2 0-1,1 0 1,0 0-1,-1 0 1,1 0 0,-1 0-1,0 0 1,0 0 0,0 0-1,0 1 1,-1-1-1,1 0 1,-1 0 0,0 0-1,0 0 1,0 0 0,0 0-1,-1-1 1,1 1-1,-1 0 1,1 0 0,-1-1-1,0 1 1,-3 2 0,-11 12 392,0-1 1,-29 23 0,33-30-303,0 1 1,0 0-1,1 1 0,0 0 1,0 1-1,2 0 0,-1 1 0,-7 15 1,10-2 219,7-26-346,0 1-1,0 0 1,1-1 0,-1 1 0,0 0 0,0 0 0,0-1 0,1 1 0,-1 0 0,0-1 0,1 1 0,-1-1-1,1 1 1,-1 0 0,0-1 0,1 1 0,-1-1 0,1 1 0,0-1 0,-1 1 0,1-1 0,-1 0-1,1 1 1,0-1 0,-1 0 0,1 1 0,0-1 0,-1 0 0,1 0 0,0 0 0,0 1 0,0-1 0,15 1 29</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6975.64">2920 1181 9830,'0'9'210,"0"0"0,1 1 0,0-1 0,0 0-1,1-1 1,0 1 0,0 0 0,7 14 0,-7-19-144,0-1 0,1 1 0,-1 0 0,1-1 0,0 0 0,0 0 0,0 0 1,0 0-1,1 0 0,-1 0 0,1-1 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,1-1 1,-1 0-1,0 0 0,5 1 0,-1-1 51,1 1 0,0-1 0,0 0 0,0-1 0,0 0 0,0 0 0,0-1 0,16-4 0,-21 4-110,-1 0 0,0-1 0,1 1 0,-1-1 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,-1-1 0,1 1 0,-1-1 0,1 0 0,-1 0 0,0 0 0,0 0 0,0 0 0,-1 0-1,1-1 1,-1 1 0,1 0 0,-1-1 0,0 1 0,0-6 0,1 3-36,-1 0 0,0 0-1,-1-1 1,1 1 0,-1 0 0,0 0-1,-1 0 1,0 0 0,0 0-1,0 0 1,0 0 0,-1 0 0,0 0-1,0 0 1,-1 0 0,0 1-1,-3-6 1,0 4 23,0 1 0,0-1-1,0 2 1,-1-1 0,0 1 0,0-1-1,0 2 1,0-1 0,-1 1 0,0 1-1,-14-6 1,2 2 201,0 1 0,-1 1-1,-33-5 1,44 9-96,0 0 1,0 1 0,1 0-1,-1 0 1,0 1-1,1 1 1,-1-1-1,0 2 1,1-1 0,-11 5-1,16-5-51,1 0 0,-1 1 0,1-1 0,0 1-1,0 0 1,0 0 0,0 0 0,0 0 0,1 1 0,-1-1-1,1 1 1,0-1 0,0 1 0,0 0 0,0 0 0,0 4-1,-5 14-11</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7845.84">2521 1481 9830,'4'0'273,"6"0"0,5 0 0,5 0 0,3 0 0,1 0 0,2 0 1,-4 0-274</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9850.78">0 957 9830,'4'0'273,"6"8"338,5 12-1,1 10-64,1 5-159,2 5 223,-2 0-337,0-7 0,-2-5 0,-4-3 0,-5-6-273</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10785.9">449 1007 9830,'0'-2'19,"0"1"0,-1 0 0,1 0 1,-1 0-1,0 0 0,1 0 0,-1 0 0,0 0 0,1 0 0,-1 0 0,0 1 1,0-1-1,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 1 0,0-1 0,0 1 1,0-1-1,0 1 0,0 0 0,-1 0 0,1-1 0,0 1 0,-2 0 0,-38-5 746,36 5-700,-4 0 58,0 0-1,0 0 0,-1 1 0,1 0 0,0 1 0,-11 3 1,18-4-97,1-1 1,0 0 0,-1 1 0,1-1-1,-1 1 1,1-1 0,0 1 0,-1 0-1,1-1 1,0 1 0,-1 0 0,1 0-1,0 0 1,0 0 0,0 0 0,0 0-1,0 0 1,0 0 0,0 1-1,0-1 1,1 0 0,-1 1 0,0-1-1,1 0 1,-1 1 0,1-1 0,0 1-1,-1-1 1,1 1 0,0-1 0,0 1-1,0-1 1,0 1 0,0-1 0,0 1-1,0-1 1,0 1 0,1-1 0,-1 1-1,1-1 1,-1 0 0,1 1 0,-1-1-1,1 0 1,0 1 0,0-1 0,1 2-1,0-1 1,0 1 1,0-1-1,0 0 0,0 0 0,0 0 0,0-1 0,1 1 0,-1 0 0,1-1 0,-1 0 1,1 1-1,0-1 0,-1 0 0,1 0 0,0-1 0,0 1 0,0 0 0,-1-1 0,1 0 1,0 0-1,0 0 0,0 0 0,0 0 0,0-1 0,0 1 0,-1-1 0,1 1 0,0-1 0,0 0 1,-1 0-1,1-1 0,0 1 0,-1 0 0,1-1 0,-1 0 0,0 1 0,0-1 0,1 0 1,-1 0-1,0 0 0,-1-1 0,1 1 0,0 0 0,-1-1 0,3-4 0,0-2-128,-2 3 136,0 1 1,0 0-1,0-1 1,1 1-1,0 0 0,0 1 1,4-6-1,-6 9-9,0 0-1,0 1 0,0-1 1,0 0-1,0 1 0,1-1 1,-1 1-1,0-1 0,0 1 1,1-1-1,-1 1 1,0 0-1,0 0 0,1 0 1,-1 0-1,0 0 0,1 0 1,-1 0-1,0 0 0,0 0 1,1 0-1,-1 1 0,0-1 1,0 1-1,1-1 0,-1 1 1,0-1-1,0 1 0,0 0 1,0-1-1,0 1 0,0 0 1,0 0-1,0 0 0,0 0 1,0 0-1,0 0 0,1 2 1,14 17 281,-1 0 1,-1 2 0,0 0-1,-2 0 1,16 41-1,-17-41-178,28 76 418,-36-90-493,-1 0 1,0 0-1,0-1 1,-1 1-1,0 0 1,-1 1-1,1-1 1,-2 0-1,1 0 1,-3 14-1,1-19-23,1-1 0,0 1-1,-1-1 1,1 0-1,-1 0 1,0 0-1,0 0 1,0 0 0,0 0-1,0-1 1,0 1-1,0 0 1,0-1 0,-1 0-1,1 0 1,-1 1-1,1-1 1,-1-1-1,1 1 1,-1 0 0,0-1-1,1 1 1,-1-1-1,0 0 1,1 0 0,-1 0-1,0 0 1,0 0-1,-4-2 1,-6 1 100,1-1 0,-1 0 0,1-1 0,-24-9 0,-18-20 494,38 21-579</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 280 9830,'0'0'5,"0"0"0,0-1-1,0 1 1,0 0 0,0 0-1,0 0 1,0 0 0,0-1 0,0 1-1,0 0 1,0 0 0,0 0 0,0 0-1,1-1 1,-1 1 0,0 0-1,0 0 1,0 0 0,0 0 0,0 0-1,0 0 1,0-1 0,1 1 0,-1 0-1,0 0 1,0 0 0,0 0-1,0 0 1,0 0 0,1 0 0,-1 0-1,0 0 1,0 0 0,0 0-1,0 0 1,1 0 0,-1 0 0,0 0-1,0 0 1,0 0 0,0 0 0,1 0-1,-1 0 1,0 0 0,0 0-1,0 0 1,1 0 0,12 6 524,13 13 527,-25-18-1015,17 12 376,-8-6-241,0 1 0,0 0 0,14 15 0,-22-21-124,-1 0 0,1 0 0,-1 0-1,1 0 1,-1 1 0,1-1 0,-1 0 0,0 1-1,0-1 1,-1 0 0,1 1 0,0-1 0,-1 1-1,1 0 1,-1-1 0,0 1 0,0-1 0,0 1-1,0-1 1,0 1 0,-1 0 0,1-1 0,-2 5-1,-32 58 892,27-55-826,1 1 1,0 0 0,1 0 0,0 0 0,0 1 0,1 0-1,1 0 1,-3 15 0,6-26-95,-1 0 0,1 0 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,0 0 0,0 0 0,0 1 0,0-1 0,1 0 0,-1 0-1,1 0 1,-1 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,1 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,0-1 0,0 1 0,0 0 0,0 0 0,0-1 0,0 1 0,0-1 0,0 1 0,0-1-1,0 0 1,0 1 0,1-1 0,-1 0 0,0 0 0,0 0 0,0 0 0,1 0 0,-1 0 0,0 0 0,0 0 0,0 0 0,0 0 0,1-1 0,-1 1 0,0-1 0,0 1 0,2-2 0,8-1-64,-1-1 0,0-1 1,1 0-1,10-8 0,15-10-20</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="639.82">400 355 9830,'9'0'200,"0"1"1,-1 1-1,1 0 1,-1 0-1,0 0 0,1 1 1,-1 0-1,0 1 1,12 7-1,-15-8-115,0 0-1,0 0 1,0 1 0,0 0 0,0 0 0,-1 0-1,1 1 1,-1-1 0,-1 1 0,1 0-1,0 0 1,-1 1 0,0-1 0,2 7-1,-4-11-55,-1 0 0,0 1 0,1-1 0,-1 0 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,0 0 0,0 1 0,-1-1 0,1 0 0,0 0 0,-1 0 0,1 0 0,-1 1 0,1-1 0,-1 0 0,1 0 0,-1 0 0,0 0 0,1 0 0,-1 0 0,0-1 0,-2 2 0,0 1 41,0-2 0,0 1 0,0 0 0,0-1 0,-1 0 0,1 1-1,-1-1 1,1-1 0,-6 2 0,-3-1 129,-1 0 0,1 0 1,0-2-1,-20-2 0,28 3-188,0-1-1,0 0 1,0 0 0,0 0 0,1-1-1,-1 1 1,0-1 0,1 0 0,-1 0-1,1 0 1,0 0 0,0-1 0,-4-3 0,6 4-25,0 1 0,0-1 0,0 1 0,1-1 0,-1 1 0,1-1 0,-1 0 0,1 1 0,0-1 1,0 0-1,0 1 0,0-1 0,0 0 0,0 0 0,0 1 0,0-1 0,1 0 0,-1 1 0,0-1 0,1 0 1,0 1-1,-1-1 0,1 1 0,0-1 0,0 1 0,0-1 0,0 1 0,0 0 0,0-1 0,0 1 1,0 0-1,1 0 0,1-2 0,9-9-99,-2 3 43,-1 0 0,0 0 0,-1-1 0,0 0 0,-1 0-1,0-1 1,0 0 0,-1 0 0,0-1 0,-1 1 0,6-24 0,12-156-503,-23 188 590,1 1-1,-1 0 1,-1 0-1,1 0 1,0-1 0,-1 1-1,1 0 1,-1 0-1,1 0 1,-1 0-1,0-1 1,0 1 0,0 1-1,0-1 1,0 0-1,-1 0 1,1 0-1,0 0 1,-1 1 0,-1-2-1,-1 0 43,0 0-1,0 1 1,0-1-1,0 1 0,0 0 1,-1 1-1,1-1 1,0 1-1,-7-2 0,-4 1 78,1 0 0,-1 1 0,-1 0-1,1 2 1,-15 1 0,26-2-102,0 1 1,1 0-1,-1 0 1,0 0-1,1 0 0,-1 0 1,1 1-1,0-1 1,0 1-1,-1 0 0,1 0 1,0 0-1,0 1 1,1-1-1,-1 1 1,1-1-1,-1 1 0,1 0 1,0 0-1,0 0 1,0 0-1,0 0 0,0 1 1,1-1-1,-1 1 1,1-1-1,-1 7 1,-2 13-1</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -11915,7 +10802,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:35:14.671"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:44:45.261"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.1" units="cm"/>
@@ -11923,7 +10810,7 @@
       <inkml:brushProperty name="color" value="#008C3A"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 1 9830,'21'9'995,"1"-1"-1,35 10 0,4 1-58,124 44 1858,2-7 1,236 38-1,-356-80-1760,0 3 0,89 35 0,-54-17-243,-69-25-757,1-1-1,1-2 1,59 4-1,105-8 18,-120-4-47,-76 1-4,0 0 0,-1 1 0,1-1 0,0-1 0,0 1 0,-1 0 0,1-1 0,0 1 0,0-1 0,-1 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,1-1 0,-1 1 0,1-1 0,-1 1 0,0-1 0,0 0 0,0 0 0,0 0 0,0 0 0,2-4 0,6-16 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 0 9830,'5'45'931,"1"-1"0,5 0 0,1 0 0,2 0 1,40 70-1,-26-54 129,34 118 0,-55-149-596,1 0 0,0-2 0,4 1 0,1 0 0,1-2 0,1 1 0,26 31 0,-11-22 247,-2 1 1,-1-1-1,-4 3 1,34 78 0,3 39 194,-7-28-405,7 103-501,-18-61 0,-37-150 0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -11943,7 +10830,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:35:15.925"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:44:48.537"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.1" units="cm"/>
@@ -11951,7 +10838,7 @@
       <inkml:brushProperty name="color" value="#008C3A"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 0 9830,'17'8'984,"-6"-1"-442,42 21 981,1-2-1,86 27 0,126 25 853,-176-53-1503,600 181 6172,-512-156-7044,-159-46 0,-1 0 0,1 0 0,0-2 0,0 0 0,37-3 0,-34 1 0,0 0 0,0 1 0,32 7 0,-37-3 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 0 9830,'201'0'2731,"-201"0"-2704,-1 0 0,1 1 0,0-1 0,0 0 0,0 0 0,-1 1 0,1-1 1,0 0-1,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,-1 1 0,1-1 0,0 0 1,0 1-1,0-1 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,0 1 0,0-1 1,1 0-1,-1 1 0,0-1 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,1 0 1,-1 1-1,0-1 0,0 0 0,0 0 0,1 1 0,-1-1 0,0 0 0,0 0 0,0 0 1,1 0-1,-1 1 0,0-1 0,1 0 0,-1 0 0,0 0 0,0 0 0,1 0 0,-1 0 1,1 0-1,-40 24 649,15-10-382,14-5-140,0 0 0,0 0 0,1 1 0,0 0 0,0 0 0,1 1 1,1 0-1,0 1 0,1 0 0,0 0 0,0 0 0,1 0 0,1 1 0,0 0 0,-3 26 1,7-36-97,0 0 0,1 1 0,-1-1 0,1 0 0,0 1 0,0-1 0,0 0 0,0 0 1,0 0-1,1 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,0-1 0,1 1 0,-1-1 0,0 1 1,1-1-1,0 0 0,-1 0 0,1 0 0,0-1 0,0 1 0,4 1 0,3 2 80,1-1 0,0 0 0,-1 0 0,1-1 0,0-1 0,13 2 0,3-2-92</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -11971,7 +10858,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:35:17.858"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:44:51.451"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.1" units="cm"/>
@@ -11979,7 +10866,8 @@
       <inkml:brushProperty name="color" value="#008C3A"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 1 9830,'17'2'327,"-1"1"0,0 0-1,0 2 1,0 0 0,-1 0-1,0 2 1,0 0 0,26 16 0,36 15 705,195 55 2474,-26-10-998,74 23 1397,-294-100-3667,0-1 0,0-2 0,0 0 0,34-2 0,-37-2-52,0 2 0,-1 0 0,1 2 0,-1 0 0,0 1 0,30 10 0,-25-6-186,0-1 0,0-1 0,1-2 0,0-1 0,0-1 0,48-2 0,-38-1 0,0 2 0,66 10 0,10 15 0,-92-21 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 68 9830,'0'4'273,"0"10"273,0 7-273,4 8 338,2 8-65,-1 2-273,0-2 0,-2-7-273</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="576.93">126 167 9830,'0'5'92,"1"-1"1,0 0-1,1 0 0,-1 0 1,1-1-1,-1 1 0,1 0 1,0 0-1,1-1 0,-1 1 1,0-1-1,1 0 0,0 0 1,0 0-1,0 0 0,0 0 1,0-1-1,1 1 0,-1-1 1,1 0-1,0 0 0,-1 0 1,8 2-1,0 0 38,-1 0 1,0 0-1,1-1 1,0 0-1,0-1 1,0 0-1,0-1 0,12 0 1,-21-1-97,0-1 0,0 1-1,0 0 1,0-1 0,0 1 0,-1-1 0,1 0-1,0 0 1,0 0 0,0 0 0,0 0 0,-1 0 0,1 0-1,0 0 1,-1-1 0,1 1 0,-1-1 0,0 1-1,1-1 1,1-2 0,-1-1-37,0 1 0,1-1 0,-1 0 0,-1 0 0,1 0 0,-1-1 0,2-9 0,-2 2-54,0 0 1,-1 0-1,-1 0 0,0 0 1,0 0-1,-4-13 0,3 20 68,1 1-1,-1 0 0,-1 0 1,1 0-1,0 0 1,-1 1-1,0-1 0,0 1 1,-1-1-1,1 1 0,-1 0 1,0 1-1,0-1 1,0 0-1,-1 1 0,1 0 1,-1 0-1,0 1 0,-9-5 1,10 6 38,0 0-1,0-1 1,0 2 0,-1-1 0,1 1 0,0-1-1,-1 1 1,1 0 0,0 1 0,-1-1 0,1 1-1,0 0 1,-1 0 0,1 0 0,0 0-1,0 1 1,0 0 0,0-1 0,0 2 0,1-1-1,-1 0 1,1 1 0,-1 0 0,1-1 0,-4 5-1,-10 12 33</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -11999,7 +10887,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:38:30.966"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:44:56.268"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.1" units="cm"/>
@@ -12007,14 +10895,8 @@
       <inkml:brushProperty name="color" value="#008C3A"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">2173 999 9830,'-4'-6'214,"-1"-1"-1,-1 1 1,1-1-1,-1 2 1,-11-10-1,13 12-129,-2-1 22,0 0-1,-1 0 0,1 1 0,-1-1 0,0 2 1,0-1-1,0 1 0,0 0 0,-1 0 1,1 1-1,-1 0 0,1 1 0,0-1 0,-1 1 1,-12 2-1,10-1 24,0 0 0,1 1-1,-1 0 1,1 0 0,-1 1 0,1 0 0,0 1 0,0 0 0,0 0 0,1 1-1,-13 9 1,17-10-55,0 1 0,0-1 0,1 1 0,-1 0 0,1 1 0,1-1-1,-1 0 1,1 1 0,0 0 0,0-1 0,0 1 0,1 0 0,0 0 0,0 0-1,0 0 1,1 0 0,0 0 0,0 0 0,1 0 0,0 0 0,1 5 0,-1-5-5,0-1 1,0 1 0,0-1 0,1 1-1,0-1 1,0 0 0,0 0 0,1 0-1,0 0 1,0 0 0,0-1 0,1 1 0,-1-1-1,1 0 1,0 0 0,0 0 0,0-1-1,1 1 1,-1-1 0,1 0 0,0 0-1,7 2 1,33 3 422,-42-8-458,-1 1 0,0-1 0,0-1 0,0 1 0,0 0 0,0 0 0,0-1 0,1 1 0,-1-1 0,0 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,0 0 0,2-3 0,-4 3-7,0 0 1,1 0-1,-1 1 1,0-1-1,0 0 0,0 0 1,0 0-1,0 0 1,0 0-1,0 0 1,0 0-1,0 0 1,0 0-1,0 1 0,0-1 1,-1 0-1,1 0 1,0 0-1,-1 0 1,1 0-1,-1 1 0,1-1 1,-1 0-1,1 0 1,-1 1-1,1-1 1,-1 0-1,0 1 1,1-1-1,-1 1 0,0-1 1,0 1-1,1-1 1,-1 1-1,0-1 1,0 1-1,0 0 0,0-1 1,0 1-1,-1 0 1,-38-17 496,40 17-516,-29-7 273,-25-6 136,52 13-383,0-1-1,0 1 0,0-1 1,0 0-1,0 0 0,1 0 1,-1 0-1,0 0 0,1 0 1,-1 0-1,0-1 1,1 1-1,-1 0 0,1-1 1,0 0-1,0 1 0,0-1 1,-1 0-1,0-2 0,4-6 195,5 3-183</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-1692.91">226 924 9830,'-1'39'1024,"0"-31"-821,0 0 0,1 0 1,0 1-1,0-1 0,1 0 0,3 13 1,-3-17-145,1-1 0,-1 0 0,1 1 0,0-1 0,0 0 0,0 0 0,1 0 0,-1 0 0,1 0 0,-1-1 0,1 1 0,0-1 0,0 0 0,0 1 1,1-1-1,-1-1 0,0 1 0,7 2 0,54 12 605,-55-15-531,0 0 0,0 1 1,-1 0-1,1 1 0,0 0 0,-1 0 0,11 6 0,-19-9-112,1 1 0,-1-1-1,0 0 1,1 1 0,-1-1-1,0 0 1,0 1 0,1-1 0,-1 1-1,0-1 1,0 0 0,0 1 0,0-1-1,0 1 1,0-1 0,1 0-1,-1 1 1,0-1 0,0 1 0,0-1-1,0 1 1,-1-1 0,1 1-1,0-1 1,0 0 0,0 1 0,0-1-1,0 1 1,0-1 0,-1 0-1,1 1 1,0-1 0,0 1 0,-1-1-1,1 0 1,0 1 0,0-1 0,-1 0-1,1 0 1,-1 1 0,1-1-1,0 0 1,-1 0 0,1 1 0,0-1-1,-1 0 1,1 0 0,-1 0-1,1 0 1,0 1 0,-1-1 0,1 0-1,-2 0 1,-24 11 517,24-11-513,-350 90 3694,344-89-3629,6 0-58,1 0-1,-1-1 1,0 0-1,1 1 1,-1-1-1,0 0 1,1 0-1,-1 0 1,0 0-1,1 0 1,-1 0-1,1-1 1,-1 1-1,0 0 1,-1-2-1,1-2 34</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-1280.64">226 999 9830,'5'0'273,"5"-4"113,5-2-113,4 1 0,4 1 0,2 1 1,0 1-1,1 1 0,0 0 0,0-3 113,-4-1-386</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4428.78">1824 1 9830,'22'0'533,"0"1"-1,0 1 1,0 1-1,32 9 1,-45-10-450,-1 1 0,0 0-1,0 0 1,0 1 0,0 0 0,0 1 0,-1 0-1,1 0 1,-2 0 0,1 1 0,0 0 0,-1 0-1,0 1 1,5 7 0,-10-13-44,0 1 1,-1-1-1,1 0 1,0 1-1,-1 0 1,1-1-1,-1 1 1,0-1-1,1 1 1,-1 0-1,0-1 1,0 1-1,0 0 1,0-1-1,0 1 1,-1 0-1,1-1 1,0 1-1,-1-1 1,1 1-1,-1-1 1,0 1-1,1-1 0,-1 1 1,0-1-1,0 1 1,-2 1-1,-40 40 818,8-9-297,30-26-433,-1 0-1,2 0 1,-1 1-1,1-1 1,0 1 0,1 0-1,0 0 1,-2 14-1,5-20-61,-1 0 0,1 0 1,1 1-1,-1-1 0,0 0 0,1 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,0 0 0,1-1 1,0 1-1,-1 0 0,1 0 0,0-1 0,0 0 0,0 1 0,1-1 0,-1 0 0,1 0 0,-1 0 0,1 0 1,0 0-1,-1-1 0,6 3 0,9 4 125,0-1 0,1-1 0,-1-1 0,1 0 0,0-2 0,32 4 0,-20-5-144</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4919.21">2298 151 9830,'-1'-1'10,"-1"0"0,1-1 1,0 1-1,-1 0 0,1 0 0,0-1 0,0 1 0,0 0 0,0-1 1,0 1-1,1-1 0,-1 1 0,0-1 0,0 0 0,1 1 0,0-1 0,-1 0 1,1 1-1,0-1 0,-1 0 0,1 0 0,0 1 0,0-1 0,1 0 1,-1 0-1,0 1 0,0-1 0,1 0 0,-1 1 0,1-1 0,0 0 1,-1 1-1,1-1 0,0 1 0,0-1 0,0 1 0,0-1 0,0 1 1,0 0-1,1 0 0,-1-1 0,0 1 0,1 0 0,-1 0 0,2-1 1,4-2 63,0 0 1,0 0-1,1 0 1,-1 1 0,1 0-1,0 1 1,0 0-1,10-2 1,10 0 243,-1 2 1,1 0 0,0 2-1,-1 1 1,30 5-1,-55-6-281,0 0 0,0 0 0,-1 1 0,1-1 0,0 1 0,-1-1 0,1 1 0,0 0 0,-1 0 0,1-1 0,-1 1 0,1 0 0,-1 0 0,1 1-1,-1-1 1,0 0 0,1 0 0,-1 1 0,0-1 0,0 1 0,0-1 0,0 1 0,0-1 0,-1 1 0,1-1 0,0 1 0,-1 0 0,1 0 0,-1-1 0,1 1 0,-1 0 0,0 0 0,0-1 0,0 1-1,0 0 1,0 0 0,-1 3 0,-2 7 206,0-1-1,-1 1 0,0-1 1,-11 21-1,-2 7 232,14-30-371,0 0 0,1 0-1,0 1 1,1-1 0,0 1-1,0-1 1,1 1-1,1-1 1,1 16 0,-1-21-23,1 1 1,-1-1-1,1 0 1,0 0-1,0 1 1,0-1-1,1 0 1,-1-1-1,1 1 0,0 0 1,0-1-1,0 1 1,1-1-1,-1 0 1,1 0-1,-1-1 1,1 1-1,0-1 1,0 1-1,1-1 1,6 2-1,20 6 473,-1-1-1,45 5 1,-30-6-462</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3199.18">152 201 9830,'10'-1'297,"1"0"0,-1-1 0,1 0 0,11-5 0,37-5 403,-53 11-591,0 1 0,1 0 1,-1 0-1,0 1 1,0-1-1,0 1 1,11 3-1,-15-3-70,-1 0 1,1 0-1,0 0 1,-1 0-1,1 0 1,-1 0-1,1 1 1,-1-1-1,0 0 1,1 1-1,-1-1 0,0 1 1,0 0-1,0-1 1,0 1-1,0 0 1,-1-1-1,1 1 1,0 0-1,-1 0 1,1 0-1,-1 0 0,0-1 1,0 1-1,1 0 1,-1 0-1,0 0 1,-1 0-1,1 3 1,-2 6 118,1 0 0,-2-1 1,1 1-1,-1 0 0,-1-1 1,0 1-1,-1-1 0,0 0 1,0-1-1,-11 16 0,-6 2 364,0 0-1,-27 24 0,48-51-492,1 1 0,-1-1-1,0 1 1,1-1 0,-1 1 0,1-1-1,-1 1 1,0 0 0,1-1 0,-1 1 0,1 0-1,0-1 1,-1 1 0,1 0 0,0 0-1,-1-1 1,1 1 0,0 0 0,0 0 0,-1 0-1,1-1 1,0 1 0,0 0 0,0 0 0,0 0-1,0-1 1,0 1 0,1 0 0,-1 0-1,0 0 1,1 1 0,0-1 19,1 0-1,-1 1 1,1-1 0,-1 0-1,1 0 1,-1-1 0,1 1-1,0 0 1,-1 0 0,1-1 0,0 1-1,0-1 1,3 1 0,71 2 713,-68-3-680,25-1-36</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3641.73">526 425 9830,'2'-17'0,"0"0"0,1 0 0,1 0 0,1 0 0,11-27 0,4-14 0,-14 36-8,-3 9 27,0-1 0,1 1 0,0 0 0,2 0 0,-1 1 0,2-1 0,10-16 0,-16 28 10,-1 1 0,1-1 0,0 1 0,-1 0 0,1-1 0,-1 1-1,1 0 1,0 0 0,-1-1 0,1 1 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,-1 0-1,1 0 1,0 0 0,0 0 0,-1 0 0,1 1 0,0-1 0,-1 0 0,1 1 0,-1-1 0,1 0 0,0 1 0,-1-1 0,1 1-1,-1-1 1,1 1 0,-1-1 0,1 1 0,-1-1 0,1 1 0,-1-1 0,1 2 0,20 29 443,-19-26-376,16 29 538,-2 1 0,-1 1 0,16 63 0,11 28 355,-29-102-667,-1-10-257</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6861.25">900 475 9830,'13'2'303,"0"1"-1,0 0 1,0 0 0,-1 2-1,1-1 1,-1 2 0,0 0-1,16 10 1,15 7 189,227 115 3148,-5-11-251,-46-35-874,-198-84-2450</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 195 9830,'0'4'273,"0"6"0,0 5 0,0 9 273,0 13 274,0 4-547,0 0 0,0-3 0,0 0 273,0-6-546</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="888.94">150 195 9830,'54'61'2049,"-37"-40"-1692,1-1 1,22 19-1,-16-21-136,-18-13-133,1 0 0,-1-1 1,0 2-1,0-1 0,-1 1 0,8 10 0,-13-16-71,1 1-1,-1 0 1,0-1-1,0 1 1,0-1-1,1 1 1,-1 0-1,0-1 1,0 1-1,0 0 1,0-1-1,0 1 1,0 0-1,0-1 1,-1 1-1,1-1 1,0 1-1,0 0 1,0-1-1,-1 1 1,1 0 0,0-1-1,-1 1 1,1-1-1,0 1 1,-1-1-1,1 1 1,-1-1-1,1 1 1,-1-1-1,1 0 1,-1 1-1,1-1 1,-1 1-1,1-1 1,-1 0-1,1 0 1,-1 1-1,0-1 1,1 0-1,-1 0 1,0 0-1,0 1 1,-37 8 469,29-7-334,5-1-91,0 1 0,0-2 0,-1 1 0,1 0 0,-1-1 0,1 0 0,0 0-1,-1 0 1,1 0 0,-1-1 0,1 0 0,0 0 0,-8-2 0,10 1-66,0 1 1,0-1 0,-1 0 0,1 0-1,0 0 1,1 0 0,-1-1-1,0 1 1,1 0 0,-1-1-1,1 1 1,0-1 0,0 0 0,0 1-1,0-1 1,0 0 0,0 0-1,1 1 1,-1-1 0,1 0-1,0 0 1,0-4 0,-1-11-86,1 0 0,0 1 0,2-1 0,0 0 0,0 1 0,2 0 0,0-1 0,1 1 0,10-21 0,-11 27 10,0-1-1,0 0 1,-1 0-1,-1-1 1,0 1-1,0-16 1,-1 25 86,-1 0 1,0 0 0,0 0-1,0 0 1,0 0 0,0 1 0,-1-1-1,1 0 1,-1 0 0,1 0-1,-1 0 1,0 1 0,-1-1-1,1 0 1,0 1 0,-1-1 0,1 1-1,-1 0 1,0-1 0,0 1-1,0 0 1,0 0 0,0 0-1,0 0 1,0 1 0,-1-1-1,1 0 1,-1 1 0,1 0 0,-1-1-1,0 1 1,-3-1 0,5 2 22,-1 0-1,1 0 1,0 0 0,-1 1 0,1-1 0,-1 0 0,1 0-1,0 1 1,-1-1 0,1 1 0,0 0 0,-1-1 0,1 1-1,0 0 1,0-1 0,0 1 0,0 0 0,0 0 0,0 0 0,0 0-1,0 0 1,0 0 0,0 1 0,0-1 0,1 0 0,-1 0-1,0 1 1,1-1 0,-1 2 0,-11 23 71</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -12034,7 +10916,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:40:51.221"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:45:00.289"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.1" units="cm"/>
@@ -12042,7 +10924,8 @@
       <inkml:brushProperty name="color" value="#008C3A"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">73 0 9830,'-1'0'47,"-1"1"-1,0-1 1,0 0-1,0 1 0,1 0 1,-1-1-1,0 1 1,1 0-1,-1 0 1,0 0-1,1 0 1,-1 0-1,1 0 1,0 0-1,-1 0 1,1 1-1,0-1 1,0 1-1,-1-1 0,1 1 1,1-1-1,-1 1 1,0-1-1,0 1 1,0 0-1,1 0 1,-1-1-1,1 1 1,-1 3-1,0-1 17,0 0 0,1 0 0,-1 0 1,1 0-1,0 0 0,0-1 0,0 1 0,1 0 0,0 0 0,-1 0 0,1 0 0,0-1 0,2 5 0,1-2 63,1 0-1,0 0 0,0-1 1,0 1-1,1-1 0,-1 0 0,1-1 1,0 1-1,1-1 0,-1-1 1,11 6-1,79 28 1111,-93-36-1199,3 1 30,69 20 544,-68-21-537,-1 0 0,1 0 1,-1 0-1,1-1 1,0 0-1,-1 0 0,1 0 1,-1-1-1,10-2 1,-15 2-79,1 1 1,0-1 0,0 0 0,0 0-1,0 0 1,-1 0 0,1 0-1,-1 0 1,1-1 0,-1 1 0,1 0-1,-1-1 1,1 1 0,-1-1 0,0 0-1,0 1 1,0-1 0,0 0-1,0 0 1,0 0 0,-1 0 0,1 1-1,-1-1 1,1 0 0,-1 0 0,0 0-1,1 0 1,-1 0 0,0 0 0,-1 0-1,1 0 1,0 0 0,0 0-1,-1 0 1,1 0 0,-1 0 0,-1-4-1,-1-1-58,1 0 0,-2 0 0,1 0 0,-1 0 0,0 0 0,0 1 0,-1 0-1,-7-8 1,2 5 130,0 1-1,0 0 0,-1 1 1,0 0-1,-1 1 0,1 1 1,-1-1-1,0 2 0,-1-1 1,1 2-1,-21-4 0,11 4 118,-1 0 0,1 2 0,-1 0 0,0 2 0,-39 5 0,36-2-155</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 181 9830,'1'-5'24,"-1"1"-1,1-1 1,0 0 0,0 0-1,0 0 1,1 1 0,-1-1-1,1 1 1,0-1 0,1 1-1,-1 0 1,1-1 0,0 1-1,0 0 1,0 1 0,0-1-1,1 1 1,-1-1 0,6-3-1,-2 3 30,-1-1 1,1 1-1,0 1 0,0-1 0,0 1 0,1 0 0,-1 1 1,0 0-1,1 0 0,0 0 0,11 0 0,-17 2-25,-1 0 0,0 0-1,0 0 1,0 0 0,0 0-1,0 0 1,0 1 0,0-1-1,0 0 1,0 0 0,0 1-1,0-1 1,0 1 0,0-1-1,0 1 1,0-1 0,0 1-1,0 0 1,-1-1 0,1 1-1,0 0 1,0 0 0,-1-1 0,1 1-1,0 0 1,-1 0 0,1 0-1,-1 0 1,1 0 0,-1 0-1,0 0 1,1 0 0,-1 0-1,0 0 1,0 0 0,0 0-1,1 0 1,-1 0 0,0 0-1,-1 1 1,1-1 0,0 0-1,0 0 1,0 0 0,-1 0-1,1 0 1,0 0 0,-1 1-1,-3 10 161,1 1-1,-2-1 1,-7 15-1,5-12-61,-5 11 146,8-18-120,0 0 1,0 1-1,1-1 1,-4 16-1,7-22-98,0 1 0,0-1-1,-1 1 1,1 0 0,1-1-1,-1 1 1,0-1 0,1 1-1,-1 0 1,1-1 0,0 1-1,0-1 1,0 0 0,0 1-1,0-1 1,0 0 0,1 1-1,-1-1 1,1 0 0,3 3-1,4 3 92,1 0 0,0-1 0,0-1 0,0 0 0,1 0 0,0-1 0,0 0 0,0-1 0,1 0 0,-1-1 0,1 0 0,0-1 0,0-1 0,0 0 0,21 0 0,-30-2-133,0 1 0,0-1 0,-1 0 0,1 0 0,0 0 0,-1 0-1,1-1 1,0 1 0,-1-1 0,1 1 0,-1-1 0,0 0 0,0 0 0,3-3 0,6-11-34</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="980.82">549 7 9830,'0'0'11,"0"0"-1,0 1 1,0-1 0,0 0-1,-1 1 1,1-1 0,0 0 0,0 1-1,-1-1 1,1 0 0,0 1-1,-1-1 1,1 0 0,0 0-1,-1 0 1,1 1 0,0-1-1,-1 0 1,1 0 0,0 0-1,-1 0 1,1 0 0,-1 1-1,1-1 1,0 0 0,-1 0-1,1 0 1,-1 0 0,1 0-1,0 0 1,-1 0 0,1-1 0,-1 1-1,1 0 1,0 0 0,-1 0-1,1 0 1,0 0 0,-1-1-1,1 1 1,0 0 0,-1 0-1,1-1 1,0 1 0,-1 0-1,1 0 1,0-1 0,0 1-1,-1 0 1,1-1 0,0 1-1,0 0 1,0-1 0,-1 1-1,1 0 1,0-1 0,0 1 0,0-1-1,0 1 1,0 0 0,0-1-1,0 1 1,0-1 0,0 1-1,0 0 1,0-1 0,0 1-1,0-1 1,-21 27 947,14-9-705,1-1 0,0 1 1,1 1-1,1-1 0,-3 26 1,6-39-206,1-1 1,0 1 0,0 0-1,0 0 1,0-1-1,0 1 1,1 0 0,-1-1-1,1 1 1,0 0 0,0-1-1,1 1 1,-1-1 0,1 1-1,0-1 1,-1 0-1,1 0 1,1 0 0,-1 0-1,0 0 1,1 0 0,0 0-1,-1-1 1,1 1 0,0-1-1,0 0 1,1 0-1,-1 0 1,0 0 0,1-1-1,-1 0 1,5 2 0,-2-2 19,0 1-1,0-1 1,0 0 0,0-1 0,0 0 0,0 0 0,1 0 0,-1-1 0,0 1 0,0-2 0,9-1-1,-13 2-67,1 0 0,-1 0-1,1 0 1,-1 0-1,0 0 1,0-1 0,1 1-1,-1-1 1,0 0-1,0 1 1,0-1-1,-1 0 1,1 0 0,0 0-1,-1 0 1,1 0-1,-1-1 1,0 1 0,1 0-1,-1-1 1,0 1-1,-1-1 1,1 1-1,0-1 1,-1 0 0,1 1-1,-1-1 1,0 1-1,0-4 1,0 4 13,0 1 0,-1 0 0,1-1 0,0 1-1,-1 0 1,1-1 0,-1 1 0,1 0 0,-1-1 0,1 1 0,-1 0 0,0 0 0,0 0 0,0 0-1,0 0 1,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,-2-1 0,-11-5 17</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -12062,7 +10945,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:40:51.995"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:46:13.227"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.1" units="cm"/>
@@ -12070,7 +10953,14 @@
       <inkml:brushProperty name="color" value="#008C3A"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 255 9830,'4'-5'0,"1"-4"0,9-7 0,6-3 0,8-12 0,4-5 0,0-1 0,-5-2 0,-7 1 0,-3 16 0,0 20 611,-3 22 208,1 18-209,1 5-223,3 5 223,-2 2-64,-4-3-273,-4-9-273</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">717 92 9830,'4'1'116,"1"1"-1,-2 1 1,2-1 0,-2 1-1,1-1 1,-1 1-1,1-1 1,-1 1 0,-1 1-1,2-1 1,-2 0-1,1 0 1,0 1 0,1 4-1,4 2 118,313 431 7469,-231-311-6204,-43-59-930,-16-23 32,2-2 0,55 60-1,-6-43 542,-72-52-1095</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1248.14">1368 21 9830,'7'2'133,"-1"0"-1,-1-1 0,1 1 1,0 1-1,-2 0 1,2 0-1,-2 0 1,2-1-1,-1 2 0,-1-1 1,1 1-1,-2 0 1,7 7-1,-5-7 19,29 29 451,-2 0 0,-2 2 0,-1 1 0,25 44 0,-53-79-578,0 0-1,-1 0 1,2-1 0,-2 1-1,1 1 1,-1-1 0,1 0-1,-1 0 1,0 0 0,0 1-1,1-1 1,-1 0 0,0 0-1,0 0 1,0 1 0,0-1-1,-1 0 1,1-1 0,0 2 0,0-1-1,-1 0 1,1 0 0,-1 0-1,1 0 1,-2 1 0,2-1-1,-1 0 1,-1 1 0,0-1 19,-1 1 1,1-1 0,0 0 0,-2 0-1,2 0 1,0 0 0,-1 0-1,0 0 1,0-1 0,1 1-1,-2-1 1,-4 1 0,-11 0 179,0-2 0,-1 1 0,-20-5 0,36 5-186,1 0-19,-1 0 0,1-1 0,0 1-1,-1-1 1,1 0 0,0 1 0,0-1 0,0 0-1,-1-1 1,2 1 0,-1-1 0,-1 1-1,2-1 1,0 0 0,-2 0 0,2 0 0,0 1-1,-1-2 1,1 1 0,0 0 0,1-1-1,-2 1 1,0-3 0,3 2-26,-1 1-1,1-1 1,-1 1-1,1-1 1,0 1-1,0 0 1,1 0-1,-1-1 1,0 1-1,1-1 1,-1 1 0,1-1-1,0 2 1,0-1-1,1-1 1,-1 1-1,0 0 1,1 0-1,-1 0 1,2-1-1,-2 2 1,1 0 0,0-1-1,-1 0 1,2 0-1,-1 1 1,5-3-1,2-1-13,-1-1-1,1 0 0,-1 0 1,-1-1-1,0-1 1,0 2-1,0-2 0,8-12 1,-13 15-9,0 1-1,0-1 1,0 2 0,-1-2 0,0 1-1,-1-1 1,1 1 0,-1 0 0,0-1-1,0 0 1,0 2 0,0-2 0,-1 0-1,0 1 1,0 0 0,0 0 0,-2-1-1,2 1 1,-1 1 0,-5-8 0,4 7 17,-1-1 0,1 0 0,-2 0 1,1 2-1,-1-2 0,1 1 1,-2 0-1,2 1 0,-2-1 1,0 1-1,-6-4 0,-12-2 42</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3290.54">1453 916 9830,'6'8'611,"10"14"373,8 17-120,9 12 120,4 10-120,-5 0-591,-7-9 0,-8-11-273</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3789.02">1680 1058 9830,'5'0'273,"6"0"0,2-5 0,2 0 0,5 0 0,-2 5 0,-3 6 1,-10 6 112,-6 6-113,-1 3 0,8 3 337,7-4-337,9-4 0,3-6 1,2-4-1,-2-4-273</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6327.66">66 68 9830,'8'0'136,"-2"1"0,1-1 0,1 1 0,-1 0 0,0 0 0,1 1 0,-1-1 0,-1 1 0,1 1 0,-1-1 0,1 1-1,-1 0 1,0 1 0,7 3 0,-11-5-79,1 1 0,1 0-1,-2-1 1,1 1-1,0 0 1,-1 0 0,0 1-1,0-1 1,1 0-1,-2 0 1,1 1 0,-1 0-1,0-1 1,0 0-1,-1 1 1,2 0 0,-2 0-1,1-1 1,-1 1-1,-1 0 1,1 0 0,0-1-1,-2 0 1,0 7-1,-2-2 96,-1 1-1,-1-1 1,2 1 0,-3-2-1,1 1 1,0-1-1,-2 1 1,1-1-1,-1-1 1,0 1-1,-1-2 1,0 1 0,-17 9-1,11-6-6,1-1 0,1 2 0,0 0-1,-14 14 1,26-24-118,0 1-1,0 0 0,1 0 1,-1 0-1,1 0 0,-2 0 0,2 0 1,-1-1-1,1 1 0,-1 0 1,1 1-1,0-1 0,-1 0 1,1 0-1,0 0 0,0 0 0,0 0 1,0-1-1,0 1 0,0 0 1,0 0-1,0 0 0,1 0 1,-1 0-1,0 0 0,1 0 0,-1 0 1,0 0-1,1 0 0,2 2 1,-1-1 38,0-1 1,0 1 0,2 0 0,-2 0 0,2-1 0,-1 1 0,-1-1-1,2 1 1,-1-1 0,7 1 0,8 2 262,1-1 1,34 3-1,-45-5-248,0 0 0,0 0-1,0-1 1,0 0 0,0 0-1,1-1 1,-1 0 0,-1 0-1,1 0 1,0-1-1,-1 0 1,1-1 0,0 0-1,-1 1 1,9-5 0,1-8 11</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6935.56">321 92 9830,'2'17'444,"0"-1"1,3 1-1,0 0 1,12 27-1,-11-27-236,-2-9-87,-1 0 1,1-1-1,0 1 1,1 0-1,0-1 1,1 0 0,0 0-1,10 9 1,-15-15-113,1 1 1,-1-1-1,1 0 1,0 0 0,0 0-1,-1 1 1,1-2-1,0 1 1,1 0 0,-1 0-1,-1 0 1,1-1-1,1 0 1,-1 0-1,0 0 1,0 1 0,1-1-1,-1 0 1,0 0-1,1 0 1,-1 0-1,0-1 1,0 1 0,1 0-1,-1 0 1,0-1-1,-1 1 1,2-1-1,-1 0 1,0 0 0,-1 0-1,2 0 1,-1 0-1,-1 0 1,1-1-1,-1 1 1,2 0 0,-2-1-1,0 1 1,0-1-1,1 2 1,-1-2-1,2-2 1,3-5-125,-2 6 141,-1-1 1,1 0 0,-1 1-1,0-1 1,2 2 0,5-6-1,-9 7-13,-1 1 1,2 0-1,-1-1 0,-1 1 0,1 0 1,-1 0-1,1 0 0,-1 0 0,1-1 0,0 1 1,-1 0-1,1 0 0,-1 0 0,1 0 0,1 0 1,-2 0-1,1 0 0,-1 1 0,1-1 0,0 0 1,-1 0-1,1 0 0,0 1 0,14 18 365,5 34 167,-8-21 4,29 53 1,-32-66-375,-1-3-140</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9532.21">122 963 9830,'56'10'1420,"-15"-2"-928,-32-7-392,-1 0 1,0 0-1,1 1 1,-1 0-1,0 1 1,0-1 0,0 0-1,0 2 1,-2-1-1,2 1 1,9 5 0,-14-7-57,-1 1 0,0-1 0,0 1 0,0-1-1,0 0 1,0 0 0,-1 1 0,0 0 0,1 0 0,-1 0 0,0-1 0,0 1 0,0 0 0,-1 0 0,1 0 0,-1 0 0,0-1 0,0 1 0,0 0 0,0 0 0,-1 0 0,1 0 0,-1-1 0,0 1 0,0 0 0,0 0 0,-1 0 0,1-1 0,-1 0 0,-3 5 0,4-5-8,0-1 0,0 1 0,0-1 0,0 1 1,0-2-1,-1 2 0,2 0 0,-1 0 0,0-1 0,1 1 0,0 0 0,-1 0 0,1 0 0,0 0 0,0-2 0,0 2 0,0 0 1,0 0-1,1 0 0,-1 0 0,0-1 0,1 1 0,0 1 0,3-1 23,-2-1 0,0 1-1,1-1 1,0 0 0,-1 0 0,2 0 0,-2 0 0,1 0-1,0-1 1,0 1 0,1-1 0,-2 0 0,1 1 0,1-1-1,-2 0 1,5-1 0,9 2 146,1-1 0,-2-1-1,34-5 1,-26 0-159</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10076.49">603 916 9830,'109'77'2837,"4"3"-1619,-102-70-1033,0 0-1,0 1 1,-1-1 0,-1 2 0,-1-1-1,13 23 1,-19-33-155,-1 1 1,0-1-1,-1 1 1,1-1-1,0 0 1,-1 1-1,0-1 1,1 1-1,-1 0 1,0-1-1,0 1 1,0 0-1,0 0 1,0-1-1,0 0 1,0 1-1,0-1 1,-1 1-1,1 0 1,-1-1-1,1 1 1,-1-1-1,0 1 0,-2 1 1,1-2 14,1 1 0,-1-1 1,-1 0-1,1 0 0,0 0 0,0 0 0,-1 0 0,1-1 1,0 1-1,0-1 0,-1 1 0,1-1 0,0 0 0,-1 1 1,1-1-1,-5-1 0,-3 1 10,-1-1 0,1-1 0,-1 1 0,1-1 0,0-1 0,1 0 0,-19-7 0,22 8-80,0-1 1,2 1 0,-2-2 0,1 1-1,1-1 1,-1 1 0,1 0-1,-1-2 1,2 1 0,-2 0-1,2 0 1,0-1 0,0 0-1,0 0 1,1 1 0,-1-1-1,1 0 1,0 1 0,-2-12-1,3 2-81,1-1-1,1 1 1,1-1-1,0 1 0,6-22 1,5-42-334,-13 73 449,0 1 0,0-1 1,-1 2-1,1-2 0,-1 1 1,0 0-1,-1 0 0,1 0 1,-2 0-1,1 0 0,0 1 0,-1-1 1,1 0-1,-1 0 0,-1 1 1,1 0-1,0 0 0,-1-1 1,1 1-1,-1 0 0,0 2 0,-1-2 1,-7-4-1,-6 0 21</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -12090,7 +10980,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:40:58.396"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:49:19.092"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.1" units="cm"/>
@@ -12098,8 +10988,7 @@
       <inkml:brushProperty name="color" value="#008C3A"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">26 1 9830,'-4'0'273,"-2"8"273,1 16 273,1 12-272,0 9-1,3 5 0,0-2-273,0-5 0,1-10-273</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="948.2">276 100 9830,'-10'0'222,"0"0"1,0 0-1,0 1 0,0 1 0,0-1 0,1 2 1,-1-1-1,-11 6 0,17-6-166,1 0-1,-1 0 1,1 1-1,-1-1 1,1 1-1,0 0 1,0 0-1,1 0 1,-1 0-1,1 1 1,-1-1-1,1 1 1,0 0-1,0-1 1,0 1-1,1 0 1,0 0-1,-1 0 1,1 0-1,1 0 1,-1 0-1,0 6 1,1-4 31,-1 1 0,1-1 1,0 1-1,0 0 0,1-1 0,0 1 1,0-1-1,1 0 0,2 9 0,-3-13-56,0 0 0,0 0 0,0 0 0,0-1 0,0 1 0,0 0 0,0-1 0,0 1 0,1-1 0,-1 0 0,1 1 0,-1-1 0,1 0 0,-1 0 0,1 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,0-1 0,0 1 0,0 0 0,0-1 0,0 0 0,-1 0 0,1 1 0,0-1 0,0 0 0,0 0 0,0-1 0,0 1 0,0 0 0,0-1 0,3 0 0,-5 1-21,0 0 1,-1 0 0,1-1-1,0 1 1,0 0 0,0 0-1,0 0 1,-1 0 0,1 0-1,0-1 1,0 1 0,0 0-1,0 0 1,0 0 0,0 0 0,-1-1-1,1 1 1,0 0 0,0 0-1,0 0 1,0-1 0,0 1-1,0 0 1,0 0 0,0 0-1,0-1 1,0 1 0,0 0-1,0 0 1,0 0 0,0-1-1,0 1 1,0 0 0,0 0-1,0 0 1,0-1 0,1 1-1,-1 0 1,0 0 0,0 0-1,0-1 1,0 1 0,0 0-1,0 0 1,1 0 0,-1 0-1,0 0 1,0-1 0,0 1-1,0 0 1,1 0 0,-1 0-1,0 0 1,0 0 0,0 0-1,1 0 1,-1 0 0,0 0 0,0 0-1,0 0 1,1 0 0,-1 0-1,0 0 1,0 0 0,0 0-1,1 0 1,-1 0 0,0 0-1,-14-7 255,-2 3-220</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 1 9830,'10'0'218,"0"0"1,0 1-1,0 0 0,-1 0 1,1 1-1,0 1 0,-1-1 1,13 6-1,-18-6-170,-1 0 0,1 1 0,-1-1 0,0 0 0,1 1 0,-1 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,-1 0 0,0 1 0,1 0 0,-1-1 0,-1 1-1,1 0 1,-1 0 0,1 0 0,-1 0 0,0 0 0,0 0 0,0 4 0,-1 1 106,1-1 1,1 0-1,0 1 0,0-1 0,0 0 0,1 0 0,0-1 1,1 1-1,0-1 0,0 1 0,1-1 0,-1 0 1,1-1-1,1 1 0,-1-1 0,1 0 0,13 9 0,70 47 906,-29-22-539,-57-38-475,0 0 0,0 1 1,-1-1-1,1 0 0,-1 1 1,1 0-1,-1-1 0,0 1 1,0 0-1,-1 0 0,1 1 1,0-1-1,1 5 0,-3-7-22,0 1 1,0-1-1,0 0 0,0 1 0,0-1 1,0 0-1,0 1 0,-1-1 0,1 0 1,0 1-1,-1-1 0,1 0 0,-1 1 1,0-1-1,1 0 0,-1 0 0,0 0 0,0 0 1,1 1-1,-1-1 0,0 0 0,0-1 1,0 1-1,-1 0 0,1 0 0,0 0 1,0-1-1,0 1 0,0 0 0,-1-1 1,1 1-1,0-1 0,-1 1 0,1-1 0,0 0 1,-1 0-1,-2 1 0,-126 21 1706,99-18-1639</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -12147,7 +11036,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:40:56.917"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:49:22.792"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.1" units="cm"/>
@@ -12155,9 +11044,9 @@
       <inkml:brushProperty name="color" value="#008C3A"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 9830,'0'8'546,"0"16"273,0 12-272,0 5-274,0 3 273,0-2-273,0 6 546,0-2-546,0-4 0,0-10-273</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="652.37">126 175 9830,'19'-9'52,"11"-7"408,2 2 1,36-12-1,27-13 769,-95 39-1192,1 0-1,0 0 1,0 0 0,0 0 0,0 1 0,0-1-1,0 0 1,0 0 0,0 1 0,0-1 0,0 0 0,0 1-1,-1-1 1,1 1 0,0-1 0,0 1 0,-1-1-1,1 1 1,0 0 0,-1-1 0,1 1 0,0 0 0,-1 0-1,1-1 1,-1 1 0,1 0 0,-1 0 0,1 0-1,-1 0 1,0 0 0,0-1 0,1 1 0,-1 1 0,7 35 654,-7-33-586,3 244 2405,-4-176-2017,0-35-447</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="902.67">275 450 9830,'5'0'273,"5"0"0,5 0 0,4 0 0,0 0-273</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 125 9830,'0'4'273,"4"6"113,1 6-113,5-1 0,0 2 0,-1 2 1,-3-2-274</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="889.37">450 25 9830,'-1'-1'22,"1"0"0,-1 0 0,0 0 0,0 0 0,1 0 0,-1 0 0,0 0 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,0 1 0,-1-1 0,1 1 0,0-1 0,0 1 0,0 0 0,-1-1 0,1 1 0,0 0 0,0 0 0,-2 0 0,-37-6 786,37 6-755,-7-1 93,-1 0 1,0 1 0,1 0-1,-1 0 1,0 1-1,1 1 1,-1 0 0,-11 4-1,19-5-104,0 0-1,-1 1 1,1 0 0,0-1-1,1 1 1,-1 0-1,0 1 1,0-1-1,1 0 1,-1 1 0,1-1-1,0 1 1,0 0-1,0 0 1,0 0-1,0 0 1,1 0 0,-1 0-1,1 0 1,0 1-1,0-1 1,0 0 0,0 1-1,1-1 1,-1 1-1,1-1 1,0 1-1,0 5 1,0-7-7,0 0-1,0 0 1,0 1-1,1-1 1,-1 0-1,1 0 1,-1 0 0,1 0-1,-1 0 1,1 0-1,0 0 1,0 0 0,0 0-1,0 0 1,1-1-1,-1 1 1,0 0-1,1-1 1,-1 1 0,1-1-1,-1 1 1,1-1-1,0 0 1,0 0 0,-1 0-1,1 0 1,0 0-1,0 0 1,0 0-1,0 0 1,0-1 0,0 1-1,1-1 1,-1 0-1,4 1 1,-1-1 13,0 0 1,1-1 0,-1 1-1,0-1 1,0 0-1,0 0 1,0-1 0,0 1-1,0-1 1,0 0-1,0-1 1,-1 1 0,7-5-1,-9 6-22,-1 0 0,1 0 0,0 0-1,0 0 1,-1 1 0,1-1 0,0 1 0,0-1 0,0 1-1,0 0 1,-1 0 0,1-1 0,0 1 0,0 1-1,0-1 1,0 0 0,0 0 0,0 1 0,-1-1-1,1 1 1,0-1 0,0 1 0,0 0 0,-1 0 0,1 0-1,-1 0 1,1 0 0,0 0 0,-1 0 0,0 0-1,1 1 1,-1-1 0,0 1 0,0-1 0,0 1 0,2 2-1,7 8 125,-1 2 0,0 0 0,8 18 0,-11-20-97,-2-6-3,-1 1-1,0-1 0,0 1 0,-1-1 0,1 1 0,-2 0 0,3 8 0,-4-13-30,0-1 0,0 1 0,-1 0 0,1-1 0,0 1 0,0 0 0,-1-1 0,1 1-1,-1-1 1,1 1 0,-1-1 0,0 1 0,0-1 0,0 1 0,1-1 0,-1 1 0,-1-1 0,1 0 0,0 0 0,0 0 0,0 0 0,-1 1 0,1-2 0,0 1-1,-1 0 1,1 0 0,-1 0 0,1-1 0,-1 1 0,1 0 0,-1-1 0,0 0 0,1 1 0,-1-1 0,-3 0 0,-51 4 305,30-5-294</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1402.46">50 125 9830,'0'4'273,"0"6"0,0 6 0,0 3 0,0 4 0,5 6 338,0 2-338,1 0 0,2-4 0,1-4 0,-2-1 0,-1-4-273</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -12177,7 +11066,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:43:22.162"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:49:26.614"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.1" units="cm"/>
@@ -12185,8 +11074,8 @@
       <inkml:brushProperty name="color" value="#008C3A"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 9830,'4'8'611,"2"8"-338,3 9 337,1 9-64,-1 11 274,1 2-434,0-2-113,-2-5 0,-3-9-273</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="620.62">76 151 9830,'0'-2'0,"0"0"0,1 0 0,-1 1 0,1-1 0,-1 0 0,1 1 0,0-1 0,0 0 0,-1 1 0,1-1 0,0 1 0,0-1 0,1 1 0,-1 0 0,0-1 0,0 1 0,1 0 0,2-2 0,33-19 0,-19 12 0,5-5 67,61-36 758,-76 48-746,0-1 1,0 1-1,0 0 0,0 1 0,0 0 0,1 0 0,-1 1 1,1 0-1,9 0 0,-14 2-22,-1-1 0,0 1-1,0 0 1,0 0 0,1 0 0,-1 1 0,0-1-1,-1 1 1,1-1 0,0 1 0,0 0 0,-1 0-1,1 0 1,-1 1 0,1-1 0,-1 1 0,0-1 0,0 1-1,0 0 1,-1-1 0,1 1 0,0 0 0,-1 0-1,0 0 1,0 1 0,0-1 0,0 0 0,0 4-1,2 3 141,-2 1 0,1-1 0,-1 0 0,0 1-1,-1-1 1,-1 0 0,-2 20 0,-10 18 494,-2-1 0,-33 70-1,41-102-552,6-14-98,1 1-1,-1-1 1,0 1-1,0-1 1,1 1 0,-1 0-1,1-1 1,0 1-1,-1 0 1,1-1 0,0 1-1,0 0 1,0 0 0,0-1-1,0 1 1,1 0-1,-1-1 1,0 1 0,1 0-1,-1-1 1,1 1-1,0-1 1,-1 1 0,1-1-1,0 1 1,0-1-1,0 1 1,0-1 0,0 0-1,0 1 1,1-1 0,-1 0-1,0 0 1,0 0-1,1 0 1,-1 0 0,1 0-1,-1-1 1,1 1-1,0 0 1,-1-1 0,1 1-1,-1-1 1,1 1-1,0-1 1,3 0 0,11 3 194,0-2 1,0 0-1,1-1 1,17-1 0,-15 0-20,13-1 96,0-1 0,33-7-1,-35 3-264</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 1 9830,'0'4'273,"0"6"0,0 5 0,0 5 0,0 2 0,0 3 0,0 1 1,0-5-274</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="841.68">200 26 9830,'0'4'273,"0"6"0,0 5 0,0 5 0,0 2 0,0 3 0,0 1 1,0 4 272,0 2-273,0-5-273</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -12206,7 +11095,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:43:21.090"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:49:39.380"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.1" units="cm"/>
@@ -12214,8 +11103,7 @@
       <inkml:brushProperty name="color" value="#008C3A"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 0 9830,'4'0'273,"2"4"0,-1 6 0,4 6 113,-1 12 434,4 6-434,-1 1-113,2 4 337,-1-2-337,1-1 114,-1 0 159,-2-5-546</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="374.52">225 25 9830,'0'4'273,"9"19"948,6 18-357,2 14-45,-3 7-273,-4-3-273,-3-7 0,-3-9 0,-2-11-273</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 0 9830,'3'23'731,"1"-1"0,1 0 0,2-1 0,1 1 0,18 35-1,-4-12 33,372 789 8075,-233-462-6440,-140-313-2398,-3 2 0,-5 0 0,6 107 0,-19-142 0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -12235,7 +11123,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:43:29.363"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:49:43.388"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.1" units="cm"/>
@@ -12243,9 +11131,9 @@
       <inkml:brushProperty name="color" value="#008C3A"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 136 9830,'1'-3'24,"-1"1"0,1 0 0,0 0 0,0-1 0,0 1 0,0 0 0,0 0 0,0 0-1,1 0 1,-1 0 0,1 0 0,-1 1 0,1-1 0,0 0 0,0 1 0,0-1 0,0 1 0,0 0 0,0 0 0,0-1 0,0 2 0,0-1 0,1 0-1,-1 0 1,0 1 0,1-1 0,-1 1 0,4-1 0,6-1 201,0 0 0,1 0-1,24 1 1,-35 1-178,1 0 0,0-1 0,-1 2 0,1-1 0,-1 0-1,1 0 1,-1 1 0,1 0 0,-1-1 0,1 1 0,-1 0 0,1 0 0,-1 0 0,0 1 0,0-1 0,1 0 0,-1 1-1,0 0 1,0-1 0,-1 1 0,1 0 0,0 0 0,0 0 0,-1 0 0,0 0 0,1 1 0,-1-1 0,0 0 0,0 1-1,0-1 1,0 0 0,0 1 0,-1-1 0,1 1 0,-1 0 0,0-1 0,1 1 0,-1-1 0,-1 5 0,-1 11 193,-1-1 0,-1 0 0,0 1 1,-1-2-1,-8 18 0,-4 18 80,16-49-278,0-1 1,1 1-1,-1 0 0,1-1 0,-1 1 0,1 0 1,0 0-1,0-1 0,0 1 0,0 0 0,0 0 0,1-1 1,-1 1-1,1 0 0,0-1 0,0 1 0,0-1 1,0 1-1,0-1 0,0 1 0,1-1 0,-1 0 1,1 1-1,0-1 0,0 0 0,0 0 0,0 0 1,0 0-1,0-1 0,0 1 0,0-1 0,1 1 1,-1-1-1,1 0 0,-1 0 0,1 0 0,-1 0 1,1 0-1,0 0 0,-1-1 0,6 1 0,7 0 137,0-1 0,-1 0 1,1-1-1,0 0 0,-1-1 0,20-6 0,-10 2-134</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="483.65">475 111 9830,'2'-3'0,"-1"1"0,1 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 1 0,1-1 0,-1 0 0,0 1 0,1 0 0,-1 0 0,1 0 0,3-1 0,-3 0 0,37-16 216,1 2 0,1 2 1,85-17-1,-122 30-132,-1 1 0,1 0 0,0 0 0,0 1 1,0-1-1,0 1 0,-1 0 0,1 0 0,0 1 0,-1-1 1,1 1-1,-1 0 0,1 0 0,-1 1 0,0-1 0,0 1 1,0 0-1,0 0 0,-1 0 0,1 1 0,-1-1 0,0 1 1,0 0-1,0 0 0,0 0 0,-1 0 0,4 9 0,5 11 309,0 1 0,-2 0 0,11 48 0,-13-44-326,14 35 498,-18-58-308,-4-8-222,-6-12-137,-2 1 86</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="736.29">750 285 9830,'8'0'546,"8"0"-273,9 0 273,4 0-273,7 0 274,0 0-274,-1 0 0,-2 0 0,-7 0-273</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 1 9830,'23'-1'403,"0"2"0,0 0 0,-1 1 1,1 1-1,-1 0 0,33 11 0,-47-12-315,0 1 1,-1 0 0,1 0-1,-1 1 1,-1 0-1,1 0 1,-1 0 0,1 1-1,-1 0 1,-1 0-1,1-1 1,0 2 0,-2 0-1,1 0 1,-1-1-1,0 2 1,-1-1 0,1 0-1,-1 1 1,-1 0-1,4 8 1,-5-11-27,0 0 0,-1 0-1,2 0 1,-2 0 0,0 1 0,0-2 0,0 1 0,0 1-1,-2-1 1,1 0 0,0 0 0,0 0 0,0 0-1,-1 0 1,-1 0 0,2-1 0,-5 6 0,-2 0 141,-1-1 1,1 1 0,-1-2-1,-21 14 1,20-14-76,1-1 0,1 0-1,-1 1 1,1 1 0,0-1 0,1 1-1,-8 11 1,14-17-83,0 1 0,0-1 0,1 0-1,-1-1 1,1 2 0,0-1 0,-2 0-1,2 1 1,0-1 0,0 0 0,2 1-1,-2-2 1,0 1 0,1 1 0,-1-1 0,1 0-1,0 0 1,0 0 0,0 0 0,0 0-1,1 0 1,-1-1 0,1 1 0,-1 0 0,1 0-1,0 0 1,0-1 0,0 1 0,0-1-1,0 1 1,0-1 0,0 0 0,0 0 0,1 0-1,4 1 1,10 6 280,1-1-1,-1-1 1,31 8-1,-39-12-226,30 7 430,79 10 1,-79-15-483</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="589.89">570 72 9830,'11'0'546,"16"0"273,25 0 274,16-4-230,8-1-317,-6-1-273,-8 6 113,-10 11 225,-16 7-338,-12 8 273,-6 10 65,-5 1-338,-6 2 273,-4 0-273,3 0 338,0-2-338,-2-8-273</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="898.8">799 262 9830,'5'0'273,"6"0"0,16 0 546,9 0-546,7 0 274,1 0-274,4 0 273,-3 0-273,-3 0 0,-5 0 0,-2 4 113,-9 1-386</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -12265,7 +11153,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:43:27.648"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:51:52.368"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.1" units="cm"/>
@@ -12273,8 +11161,7 @@
       <inkml:brushProperty name="color" value="#008C3A"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 280 9830,'0'0'5,"0"0"0,0-1-1,0 1 1,0 0 0,0 0-1,0 0 1,0 0 0,0-1 0,0 1-1,0 0 1,0 0 0,0 0 0,0 0-1,1-1 1,-1 1 0,0 0-1,0 0 1,0 0 0,0 0 0,0 0-1,0 0 1,0-1 0,1 1 0,-1 0-1,0 0 1,0 0 0,0 0-1,0 0 1,0 0 0,1 0 0,-1 0-1,0 0 1,0 0 0,0 0-1,0 0 1,1 0 0,-1 0 0,0 0-1,0 0 1,0 0 0,0 0 0,1 0-1,-1 0 1,0 0 0,0 0-1,0 0 1,1 0 0,12 6 524,13 13 527,-25-18-1015,17 12 376,-8-6-241,0 1 0,0 0 0,14 15 0,-22-21-124,-1 0 0,1 0 0,-1 0-1,1 0 1,-1 1 0,1-1 0,-1 0 0,0 1-1,0-1 1,-1 0 0,1 1 0,0-1 0,-1 1-1,1 0 1,-1-1 0,0 1 0,0-1 0,0 1-1,0-1 1,0 1 0,-1 0 0,1-1 0,-2 5-1,-32 58 892,27-55-826,1 1 1,0 0 0,1 0 0,0 0 0,0 1 0,1 0-1,1 0 1,-3 15 0,6-26-95,-1 0 0,1 0 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,0 0 0,0 0 0,0 1 0,0-1 0,1 0 0,-1 0-1,1 0 1,-1 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,1 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,0-1 0,0 1 0,0 0 0,0 0 0,0-1 0,0 1 0,0-1 0,0 1 0,0-1-1,0 0 1,0 1 0,1-1 0,-1 0 0,0 0 0,0 0 0,0 0 0,1 0 0,-1 0 0,0 0 0,0 0 0,0 0 0,0 0 0,1-1 0,-1 1 0,0-1 0,0 1 0,2-2 0,8-1-64,-1-1 0,0-1 1,1 0-1,10-8 0,15-10-20</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="639.83">400 355 9830,'9'0'200,"0"1"1,-1 1-1,1 0 1,-1 0-1,0 0 0,1 1 1,-1 0-1,0 1 1,12 7-1,-15-8-115,0 0-1,0 0 1,0 1 0,0 0 0,0 0 0,-1 0-1,1 1 1,-1-1 0,-1 1 0,1 0-1,0 0 1,-1 1 0,0-1 0,2 7-1,-4-11-55,-1 0 0,0 1 0,1-1 0,-1 0 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,0 0 0,0 1 0,-1-1 0,1 0 0,0 0 0,-1 0 0,1 0 0,-1 1 0,1-1 0,-1 0 0,1 0 0,-1 0 0,0 0 0,1 0 0,-1 0 0,0-1 0,-2 2 0,0 1 41,0-2 0,0 1 0,0 0 0,0-1 0,-1 0 0,1 1-1,-1-1 1,1-1 0,-6 2 0,-3-1 129,-1 0 0,1 0 1,0-2-1,-20-2 0,28 3-188,0-1-1,0 0 1,0 0 0,0 0 0,1-1-1,-1 1 1,0-1 0,1 0 0,-1 0-1,1 0 1,0 0 0,0-1 0,-4-3 0,6 4-25,0 1 0,0-1 0,0 1 0,1-1 0,-1 1 0,1-1 0,-1 0 0,1 1 0,0-1 1,0 0-1,0 1 0,0-1 0,0 0 0,0 0 0,0 1 0,0-1 0,1 0 0,-1 1 0,0-1 0,1 0 1,0 1-1,-1-1 0,1 1 0,0-1 0,0 1 0,0-1 0,0 1 0,0 0 0,0-1 0,0 1 1,0 0-1,1 0 0,1-2 0,9-9-99,-2 3 43,-1 0 0,0 0 0,-1-1 0,0 0 0,-1 0-1,0-1 1,0 0 0,-1 0 0,0-1 0,-1 1 0,6-24 0,12-156-503,-23 188 590,1 1-1,-1 0 1,-1 0-1,1 0 1,0-1 0,-1 1-1,1 0 1,-1 0-1,1 0 1,-1 0-1,0-1 1,0 1 0,0 1-1,0-1 1,0 0-1,-1 0 1,1 0-1,0 0 1,-1 1 0,-1-2-1,-1 0 43,0 0-1,0 1 1,0-1-1,0 1 0,0 0 1,-1 1-1,1-1 1,0 1-1,-7-2 0,-4 1 78,1 0 0,-1 1 0,-1 0-1,1 2 1,-15 1 0,26-2-102,0 1 1,1 0-1,-1 0 1,0 0-1,1 0 0,-1 0 1,1 1-1,0-1 1,0 1-1,-1 0 0,1 0 1,0 0-1,0 1 1,1-1-1,-1 1 1,1-1-1,-1 1 0,1 0 1,0 0-1,0 0 1,0 0-1,0 0 0,0 1 1,1-1-1,-1 1 1,1-1-1,-1 7 1,-2 13-1</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 0 9830,'2'1'75,"0"-1"1,0 1-1,0-1 1,0 1-1,0 0 0,0 0 1,0 0-1,-1 0 1,1 0-1,0 0 0,-1 0 1,1 0-1,0 1 1,-1-1-1,0 1 0,3 2 1,22 33 558,-17-24-262,12 19 96,2 0-1,1-2 1,1-1-1,1-1 1,2-1-1,32 24 1,-51-45-259,-1 1 1,0 1-1,0-1 0,12 17 1,-11-13-165</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -12294,7 +11181,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:44:45.261"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:51:53.243"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.1" units="cm"/>
@@ -12302,7 +11189,7 @@
       <inkml:brushProperty name="color" value="#008C3A"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 0 9830,'4'48'931,"1"-2"0,3 1 0,2-1 0,1 0 1,31 75-1,-20-58 129,27 125 0,-44-157-596,1-1 0,1-1 0,2 1 0,1-1 0,1-1 0,1 0 0,20 33 0,-8-23 247,-2 1 1,-1 0-1,-3 2 1,27 82 0,2 42 194,-6-30-405,6 109-501,-14-64 0,-29-159 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 9830,'4'8'611,"10"8"-1,11 9 163,6 0-500,2 1 113,-1-5-113,-2-1 113,-1 0 0,-1 0 0,2 2 225,-3 6-65,-2 1-160,-6 1-113,-5-1 0,-2-5 0,2-2 114,-1-1-114,-4-4-273</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -12322,7 +11209,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:44:48.537"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:51:55.731"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.1" units="cm"/>
@@ -12330,7 +11217,7 @@
       <inkml:brushProperty name="color" value="#008C3A"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 0 9830,'201'0'2731,"-201"0"-2704,-1 0 0,1 1 0,0-1 0,0 0 0,0 0 0,-1 1 0,1-1 1,0 0-1,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,-1 1 0,1-1 0,0 0 1,0 1-1,0-1 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,0 1 0,0-1 1,1 0-1,-1 1 0,0-1 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,1 0 1,-1 1-1,0-1 0,0 0 0,0 0 0,1 1 0,-1-1 0,0 0 0,0 0 0,0 0 1,1 0-1,-1 1 0,0-1 0,1 0 0,-1 0 0,0 0 0,0 0 0,1 0 0,-1 0 1,1 0-1,-40 24 649,15-10-382,14-5-140,0 0 0,0 0 0,1 1 0,0 0 0,0 0 0,1 1 1,1 0-1,0 1 0,1 0 0,0 0 0,0 0 0,1 0 0,1 1 0,0 0 0,-3 26 1,7-36-97,0 0 0,1 1 0,-1-1 0,1 0 0,0 1 0,0-1 0,0 0 0,0 0 1,0 0-1,1 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,0-1 0,1 1 0,-1-1 0,0 1 1,1-1-1,0 0 0,-1 0 0,1 0 0,0-1 0,0 1 0,4 1 0,3 2 80,1-1 0,0 0 0,-1 0 0,1-1 0,0-1 0,13 2 0,3-2-92</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 9830,'4'0'273,"2"4"0,4 2 0,4 8 338,4 10-1,8 9 163,3 9-163,6 0 1,5 2 161,4-7-226,-1-1 65,-3-6-338,-5-9 0,-4-3 113,-3 3 225,-2 3-225,-5-3-386</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -12350,7 +11237,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:44:51.451"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:51:56.582"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.1" units="cm"/>
@@ -12358,8 +11245,7 @@
       <inkml:brushProperty name="color" value="#008C3A"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 68 9830,'0'4'273,"0"10"273,0 7-273,4 8 338,2 8-65,-1 2-273,0-2 0,-2-7-273</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="576.94">126 167 9830,'0'5'92,"1"-1"1,0 0-1,1 0 0,-1 0 1,1-1-1,-1 1 0,1 0 1,0 0-1,1-1 0,-1 1 1,0-1-1,1 0 0,0 0 1,0 0-1,0 0 0,0 0 1,0-1-1,1 1 0,-1-1 1,1 0-1,0 0 0,-1 0 1,8 2-1,0 0 38,-1 0 1,0 0-1,1-1 1,0 0-1,0-1 1,0 0-1,0-1 0,12 0 1,-21-1-97,0-1 0,0 1-1,0 0 1,0-1 0,0 1 0,-1-1 0,1 0-1,0 0 1,0 0 0,0 0 0,0 0 0,-1 0 0,1 0-1,0 0 1,-1-1 0,1 1 0,-1-1 0,0 1-1,1-1 1,1-2 0,-1-1-37,0 1 0,1-1 0,-1 0 0,-1 0 0,1 0 0,-1-1 0,2-9 0,-2 2-54,0 0 1,-1 0-1,-1 0 0,0 0 1,0 0-1,-4-13 0,3 20 68,1 1-1,-1 0 0,-1 0 1,1 0-1,0 0 1,-1 1-1,0-1 0,0 1 1,-1-1-1,1 1 0,-1 0 1,0 1-1,0-1 1,0 0-1,-1 1 0,1 0 1,-1 0-1,0 1 0,-9-5 1,10 6 38,0 0-1,0-1 1,0 2 0,-1-1 0,1 1 0,0-1-1,-1 1 1,1 0 0,0 1 0,-1-1 0,1 1-1,0 0 1,-1 0 0,1 0 0,0 0-1,0 1 1,0 0 0,0-1 0,0 2 0,1-1-1,-1 0 1,1 1 0,-1 0 0,1-1 0,-4 5-1,-10 12 33</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 0 9830,'0'9'546,"0"6"-273,4 10 338,10 9 161,7 7-161,8 9 373,8 5-211,2 2-163,3-10-64,2-3 227,-2-6-387,-3-4 0,-5-9-113,-7-4 0,-10-5-273</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -12379,7 +11265,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:44:56.268"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:52:04.185"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.1" units="cm"/>
@@ -12387,8 +11273,7 @@
       <inkml:brushProperty name="color" value="#008C3A"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 195 9830,'0'4'273,"0"6"0,0 5 0,0 9 273,0 13 274,0 4-547,0 0 0,0-3 0,0 0 273,0-6-546</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="888.94">150 195 9830,'54'61'2049,"-37"-40"-1692,1-1 1,22 19-1,-16-21-136,-18-13-133,1 0 0,-1-1 1,0 2-1,0-1 0,-1 1 0,8 10 0,-13-16-71,1 1-1,-1 0 1,0-1-1,0 1 1,0-1-1,1 1 1,-1 0-1,0-1 1,0 1-1,0 0 1,0-1-1,0 1 1,0 0-1,0-1 1,-1 1-1,1-1 1,0 1-1,0 0 1,0-1-1,-1 1 1,1 0 0,0-1-1,-1 1 1,1-1-1,0 1 1,-1-1-1,1 1 1,-1-1-1,1 1 1,-1-1-1,1 0 1,-1 1-1,1-1 1,-1 1-1,1-1 1,-1 0-1,1 0 1,-1 1-1,0-1 1,1 0-1,-1 0 1,0 0-1,0 1 1,-37 8 469,29-7-334,5-1-91,0 1 0,0-2 0,-1 1 0,1 0 0,-1-1 0,1 0 0,0 0-1,-1 0 1,1 0 0,-1-1 0,1 0 0,0 0 0,-8-2 0,10 1-66,0 1 1,0-1 0,-1 0 0,1 0-1,0 0 1,1 0 0,-1-1-1,0 1 1,1 0 0,-1-1-1,1 1 1,0-1 0,0 0 0,0 1-1,0-1 1,0 0 0,0 0-1,1 1 1,-1-1 0,1 0-1,0 0 1,0-4 0,-1-11-86,1 0 0,0 1 0,2-1 0,0 0 0,0 1 0,2 0 0,0-1 0,1 1 0,10-21 0,-11 27 10,0-1-1,0 0 1,-1 0-1,-1-1 1,0 1-1,0-16 1,-1 25 86,-1 0 1,0 0 0,0 0-1,0 0 1,0 0 0,0 1 0,-1-1-1,1 0 1,-1 0 0,1 0-1,-1 0 1,0 1 0,-1-1-1,1 0 1,0 1 0,-1-1 0,1 1-1,-1 0 1,0-1 0,0 1-1,0 0 1,0 0 0,0 0-1,0 0 1,0 1 0,-1-1-1,1 0 1,-1 1 0,1 0 0,-1-1-1,0 1 1,-3-1 0,5 2 22,-1 0-1,1 0 1,0 0 0,-1 1 0,1-1 0,-1 0 0,1 0-1,0 1 1,-1-1 0,1 1 0,0 0 0,-1-1 0,1 1-1,0 0 1,0-1 0,0 1 0,0 0 0,0 0 0,0 0 0,0 0-1,0 0 1,0 0 0,0 1 0,0-1 0,1 0 0,-1 0-1,0 1 1,1-1 0,-1 2 0,-11 23 71</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 71 9830,'4'0'273,"6"0"0,1-4 0,3-2 0,3-4 113,3-4-420,-1-4 9,-1 0 0,-2 17 775,-5 13-500,-4 8-1,1 9 310,0 9-59,-3 1-250,-1-1-1,-1-7-249</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -12408,7 +11293,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:45:00.289"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-29T14:52:05.329"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.1" units="cm"/>
@@ -12416,8 +11301,7 @@
       <inkml:brushProperty name="color" value="#008C3A"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 181 9830,'1'-5'24,"-1"1"-1,1-1 1,0 0 0,0 0-1,0 0 1,1 1 0,-1-1-1,1 1 1,0-1 0,1 1-1,-1 0 1,1-1 0,0 1-1,0 0 1,0 1 0,0-1-1,1 1 1,-1-1 0,6-3-1,-2 3 30,-1-1 1,1 1-1,0 1 0,0-1 0,0 1 0,1 0 0,-1 1 1,0 0-1,1 0 0,0 0 0,11 0 0,-17 2-25,-1 0 0,0 0-1,0 0 1,0 0 0,0 0-1,0 0 1,0 1 0,0-1-1,0 0 1,0 0 0,0 1-1,0-1 1,0 1 0,0-1-1,0 1 1,0-1 0,0 1-1,0 0 1,-1-1 0,1 1-1,0 0 1,0 0 0,-1-1 0,1 1-1,0 0 1,-1 0 0,1 0-1,-1 0 1,1 0 0,-1 0-1,0 0 1,1 0 0,-1 0-1,0 0 1,0 0 0,0 0-1,1 0 1,-1 0 0,0 0-1,-1 1 1,1-1 0,0 0-1,0 0 1,0 0 0,-1 0-1,1 0 1,0 0 0,-1 1-1,-3 10 161,1 1-1,-2-1 1,-7 15-1,5-12-61,-5 11 146,8-18-120,0 0 1,0 1-1,1-1 1,-4 16-1,7-22-98,0 1 0,0-1-1,-1 1 1,1 0 0,1-1-1,-1 1 1,0-1 0,1 1-1,-1 0 1,1-1 0,0 1-1,0-1 1,0 0 0,0 1-1,0-1 1,0 0 0,1 1-1,-1-1 1,1 0 0,3 3-1,4 3 92,1 0 0,0-1 0,0-1 0,0 0 0,1 0 0,0-1 0,0 0 0,0-1 0,1 0 0,-1-1 0,1 0 0,0-1 0,0-1 0,0 0 0,21 0 0,-30-2-133,0 1 0,0-1 0,-1 0 0,1 0 0,0 0 0,-1 0-1,1-1 1,0 1 0,-1-1 0,1 1 0,-1-1 0,0 0 0,0 0 0,3-3 0,6-11-34</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="980.82">549 7 9830,'0'0'11,"0"0"-1,0 1 1,0-1 0,0 0-1,-1 1 1,1-1 0,0 0 0,0 1-1,-1-1 1,1 0 0,0 1-1,-1-1 1,1 0 0,0 0-1,-1 0 1,1 1 0,0-1-1,-1 0 1,1 0 0,0 0-1,-1 0 1,1 0 0,-1 1-1,1-1 1,0 0 0,-1 0-1,1 0 1,-1 0 0,1 0-1,0 0 1,-1 0 0,1-1 0,-1 1-1,1 0 1,0 0 0,-1 0-1,1 0 1,0 0 0,-1-1-1,1 1 1,0 0 0,-1 0-1,1-1 1,0 1 0,-1 0-1,1 0 1,0-1 0,0 1-1,-1 0 1,1-1 0,0 1-1,0 0 1,0-1 0,-1 1-1,1 0 1,0-1 0,0 1 0,0-1-1,0 1 1,0 0 0,0-1-1,0 1 1,0-1 0,0 1-1,0 0 1,0-1 0,0 1-1,0-1 1,-21 27 947,14-9-705,1-1 0,0 1 1,1 1-1,1-1 0,-3 26 1,6-39-206,1-1 1,0 1 0,0 0-1,0 0 1,0-1-1,0 1 1,1 0 0,-1-1-1,1 1 1,0 0 0,0-1-1,1 1 1,-1-1 0,1 1-1,0-1 1,-1 0-1,1 0 1,1 0 0,-1 0-1,0 0 1,1 0 0,0 0-1,-1-1 1,1 1 0,0-1-1,0 0 1,1 0-1,-1 0 1,0 0 0,1-1-1,-1 0 1,5 2 0,-2-2 19,0 1-1,0-1 1,0 0 0,0-1 0,0 0 0,0 0 0,1 0 0,-1-1 0,0 1 0,0-2 0,9-1-1,-13 2-67,1 0 0,-1 0-1,1 0 1,-1 0-1,0 0 1,0-1 0,1 1-1,-1-1 1,0 0-1,0 1 1,0-1-1,-1 0 1,1 0 0,0 0-1,-1 0 1,1 0-1,-1-1 1,0 1 0,1 0-1,-1-1 1,0 1-1,-1-1 1,1 1-1,0-1 1,-1 0 0,1 1-1,-1-1 1,0 1-1,0-4 1,0 4 13,0 1 0,-1 0 0,1-1 0,0 1-1,-1 0 1,1-1 0,-1 1 0,1 0 0,-1-1 0,1 1 0,-1 0 0,0 0 0,0 0 0,0 0-1,0 0 1,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,-2-1 0,-11-5 17</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 1 9830,'0'4'273,"5"2"0,0 3 0,5 1 0,4-1 0,5-3 0,-2-6 1,1 1 112,-3 4-113,-3 6 0,-1 10 337,-1 9-64,2 0-272,-2 3 272,-2 1-273,-2-2 0,-3-6-273</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -12739,26 +11623,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C88DF4A-B980-46AE-A8F7-558C5528EBCA}">
   <dimension ref="A1:BP35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="16" width="2.7109375" customWidth="1"/>
-    <col min="17" max="17" width="2.140625" customWidth="1"/>
-    <col min="18" max="18" width="3.28515625" customWidth="1"/>
-    <col min="19" max="27" width="2.7109375" customWidth="1"/>
-    <col min="28" max="28" width="3.42578125" customWidth="1"/>
-    <col min="29" max="52" width="2.7109375" customWidth="1"/>
-    <col min="53" max="54" width="3.85546875" customWidth="1"/>
+    <col min="1" max="16" width="2.75" customWidth="1"/>
+    <col min="17" max="17" width="2.125" customWidth="1"/>
+    <col min="18" max="18" width="3.25" customWidth="1"/>
+    <col min="19" max="27" width="2.75" customWidth="1"/>
+    <col min="28" max="28" width="3.375" customWidth="1"/>
+    <col min="29" max="52" width="2.75" customWidth="1"/>
+    <col min="53" max="54" width="3.875" customWidth="1"/>
     <col min="55" max="55" width="4" customWidth="1"/>
-    <col min="56" max="56" width="5.7109375" customWidth="1"/>
-    <col min="57" max="57" width="4.140625" customWidth="1"/>
+    <col min="56" max="56" width="5.75" customWidth="1"/>
+    <col min="57" max="57" width="4.125" customWidth="1"/>
     <col min="58" max="58" width="4" customWidth="1"/>
-    <col min="59" max="70" width="2.7109375" customWidth="1"/>
+    <col min="59" max="70" width="2.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68">
       <c r="A1" s="1"/>
     </row>
-    <row r="2" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:68">
       <c r="S2" t="s">
         <v>2</v>
       </c>
@@ -12773,7 +11657,7 @@
       <c r="BO2" s="23"/>
       <c r="BP2" s="23"/>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68">
       <c r="S3" t="s">
         <v>0</v>
       </c>
@@ -12790,7 +11674,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68">
       <c r="R4">
         <v>0</v>
       </c>
@@ -12816,7 +11700,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68">
       <c r="R5">
         <v>1</v>
       </c>
@@ -12856,7 +11740,7 @@
       <c r="BO5" s="23"/>
       <c r="BP5" s="23"/>
     </row>
-    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:68">
       <c r="H6" s="3"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
@@ -12898,7 +11782,7 @@
       </c>
       <c r="BJ6" s="22"/>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68">
       <c r="H7" s="7"/>
       <c r="R7">
         <v>3</v>
@@ -12935,7 +11819,7 @@
       </c>
       <c r="BJ7" s="22"/>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68">
       <c r="H8" s="7"/>
       <c r="J8" s="20"/>
       <c r="K8" s="5"/>
@@ -12976,7 +11860,7 @@
       </c>
       <c r="BJ8" s="22"/>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68">
       <c r="H9" s="7"/>
       <c r="M9" s="7"/>
       <c r="R9">
@@ -13013,7 +11897,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68">
       <c r="H10" s="7"/>
       <c r="M10" s="7"/>
       <c r="R10">
@@ -13051,7 +11935,7 @@
       </c>
       <c r="BJ10" s="23"/>
     </row>
-    <row r="11" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:68">
       <c r="H11" s="4"/>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
@@ -13097,7 +11981,7 @@
       <c r="BO11" s="23"/>
       <c r="BP11" s="23"/>
     </row>
-    <row r="12" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:68">
       <c r="R12">
         <v>8</v>
       </c>
@@ -13132,7 +12016,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:68">
       <c r="H13" s="15"/>
       <c r="I13" s="16"/>
       <c r="J13" s="16"/>
@@ -13172,7 +12056,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:68">
       <c r="H14" s="14"/>
       <c r="I14" s="18"/>
       <c r="J14" s="2"/>
@@ -13212,7 +12096,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:68">
       <c r="I15" s="12"/>
       <c r="J15" s="10"/>
       <c r="K15" s="8"/>
@@ -13253,7 +12137,7 @@
       <c r="BM15" s="23"/>
       <c r="BN15" s="23"/>
     </row>
-    <row r="16" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:68">
       <c r="I16" s="13"/>
       <c r="J16" s="10"/>
       <c r="K16" s="8"/>
@@ -13279,7 +12163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="9:68" x14ac:dyDescent="0.25">
+    <row r="17" spans="9:68">
       <c r="I17" s="13"/>
       <c r="J17" s="10"/>
       <c r="K17" s="8"/>
@@ -13306,7 +12190,7 @@
       </c>
       <c r="BG17" s="23"/>
     </row>
-    <row r="18" spans="9:68" x14ac:dyDescent="0.25">
+    <row r="18" spans="9:68">
       <c r="I18" s="14"/>
       <c r="J18" s="11"/>
       <c r="K18" s="9"/>
@@ -13333,7 +12217,7 @@
       </c>
       <c r="BG18" s="23"/>
     </row>
-    <row r="19" spans="9:68" x14ac:dyDescent="0.25">
+    <row r="19" spans="9:68">
       <c r="R19">
         <v>15</v>
       </c>
@@ -13357,7 +12241,7 @@
       </c>
       <c r="BG19" s="23"/>
     </row>
-    <row r="20" spans="9:68" x14ac:dyDescent="0.25">
+    <row r="20" spans="9:68">
       <c r="AB20">
         <v>16</v>
       </c>
@@ -13374,7 +12258,7 @@
       <c r="BN20" s="23"/>
       <c r="BO20" s="23"/>
     </row>
-    <row r="21" spans="9:68" x14ac:dyDescent="0.25">
+    <row r="21" spans="9:68">
       <c r="AB21">
         <v>17</v>
       </c>
@@ -13388,7 +12272,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="9:68" x14ac:dyDescent="0.25">
+    <row r="22" spans="9:68">
       <c r="AB22">
         <v>18</v>
       </c>
@@ -13402,7 +12286,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="23" spans="9:68" x14ac:dyDescent="0.25">
+    <row r="23" spans="9:68">
       <c r="AB23">
         <v>19</v>
       </c>
@@ -13419,7 +12303,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="9:68" x14ac:dyDescent="0.25">
+    <row r="24" spans="9:68">
       <c r="AB24">
         <v>20</v>
       </c>
@@ -13449,7 +12333,7 @@
       <c r="BO24" s="23"/>
       <c r="BP24" s="23"/>
     </row>
-    <row r="25" spans="9:68" x14ac:dyDescent="0.25">
+    <row r="25" spans="9:68">
       <c r="AB25">
         <v>21</v>
       </c>
@@ -13475,7 +12359,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="9:68" x14ac:dyDescent="0.25">
+    <row r="26" spans="9:68">
       <c r="AB26">
         <v>22</v>
       </c>
@@ -13501,7 +12385,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="9:68" x14ac:dyDescent="0.25">
+    <row r="27" spans="9:68">
       <c r="AB27">
         <v>23</v>
       </c>
@@ -13527,7 +12411,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="9:68" x14ac:dyDescent="0.25">
+    <row r="28" spans="9:68">
       <c r="AB28">
         <v>24</v>
       </c>
@@ -13555,7 +12439,7 @@
       <c r="BJ28" s="23"/>
       <c r="BN28" s="23"/>
     </row>
-    <row r="29" spans="9:68" x14ac:dyDescent="0.25">
+    <row r="29" spans="9:68">
       <c r="AB29">
         <v>25</v>
       </c>
@@ -13581,7 +12465,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="9:68" x14ac:dyDescent="0.25">
+    <row r="30" spans="9:68">
       <c r="AB30">
         <v>26</v>
       </c>
@@ -13607,7 +12491,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="9:68" x14ac:dyDescent="0.25">
+    <row r="31" spans="9:68">
       <c r="AB31">
         <v>27</v>
       </c>
@@ -13635,7 +12519,7 @@
       <c r="BJ31" s="23"/>
       <c r="BN31" s="23"/>
     </row>
-    <row r="32" spans="9:68" x14ac:dyDescent="0.25">
+    <row r="32" spans="9:68">
       <c r="AB32">
         <v>28</v>
       </c>
@@ -13661,7 +12545,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="28:66" x14ac:dyDescent="0.25">
+    <row r="33" spans="28:66">
       <c r="AB33">
         <v>29</v>
       </c>
@@ -13687,7 +12571,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="34" spans="28:66" x14ac:dyDescent="0.25">
+    <row r="34" spans="28:66">
       <c r="AB34">
         <v>30</v>
       </c>
@@ -13715,7 +12599,7 @@
       <c r="BJ34" s="23"/>
       <c r="BN34" s="23"/>
     </row>
-    <row r="35" spans="28:66" x14ac:dyDescent="0.25">
+    <row r="35" spans="28:66">
       <c r="AB35">
         <v>31</v>
       </c>
